--- a/research/traditional_assets/database/data/bulgaria/bulgaria_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_retail_automotive.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bul_pet" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0199</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="G2">
-        <v>0.00695904313156941</v>
+        <v>0.01119614512471655</v>
       </c>
       <c r="H2">
-        <v>0.00695904313156941</v>
+        <v>0.01119614512471655</v>
       </c>
       <c r="I2">
-        <v>-0.003124320405944183</v>
+        <v>0.01235827664399093</v>
       </c>
       <c r="J2">
-        <v>-0.003124320405944183</v>
+        <v>0.0118774098485049</v>
       </c>
       <c r="K2">
-        <v>-1.25</v>
+        <v>1.9</v>
       </c>
       <c r="L2">
-        <v>-0.004530627038782168</v>
+        <v>0.005385487528344671</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="V2">
-        <v>0.3705263157894737</v>
+        <v>0.3952702702702702</v>
       </c>
       <c r="W2">
-        <v>-0.06345177664974619</v>
+        <v>0.1117647058823529</v>
       </c>
       <c r="X2">
-        <v>0.3648351740137705</v>
+        <v>0.6446563816308131</v>
       </c>
       <c r="Y2">
-        <v>-0.4282869506635167</v>
+        <v>-0.5328916757484601</v>
       </c>
       <c r="Z2">
-        <v>6.617893979371551</v>
+        <v>9.954853273137699</v>
       </c>
       <c r="AA2">
-        <v>-0.02067642120412569</v>
+        <v>0.118237872306787</v>
       </c>
       <c r="AB2">
-        <v>0.1058109160912657</v>
+        <v>0.2025672413402094</v>
       </c>
       <c r="AC2">
-        <v>-0.1264873372953914</v>
+        <v>-0.08432936903342245</v>
       </c>
       <c r="AD2">
-        <v>32</v>
+        <v>28.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>28.5</v>
       </c>
       <c r="AG2">
-        <v>30.24</v>
+        <v>27.33</v>
       </c>
       <c r="AH2">
-        <v>0.8707482993197279</v>
+        <v>0.9059122695486331</v>
       </c>
       <c r="AI2">
-        <v>0.6517311608961304</v>
+        <v>0.8469539375928677</v>
       </c>
       <c r="AJ2">
-        <v>0.8642469276936269</v>
+        <v>0.9022779795311984</v>
       </c>
       <c r="AK2">
-        <v>0.6387832699619771</v>
+        <v>0.8414408866995075</v>
       </c>
       <c r="AL2">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AM2">
-        <v>1.598</v>
+        <v>1.309</v>
       </c>
       <c r="AN2">
-        <v>13.4453781512605</v>
+        <v>3.97489539748954</v>
       </c>
       <c r="AO2">
-        <v>-0.3448</v>
+        <v>2.169154228855722</v>
       </c>
       <c r="AP2">
-        <v>12.70588235294118</v>
+        <v>3.811715481171548</v>
       </c>
       <c r="AQ2">
-        <v>-0.5394242803504381</v>
+        <v>3.330786860198626</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0199</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="G3">
-        <v>0.00695904313156941</v>
+        <v>0.01119614512471655</v>
       </c>
       <c r="H3">
-        <v>0.00695904313156941</v>
+        <v>0.01119614512471655</v>
       </c>
       <c r="I3">
-        <v>-0.003124320405944183</v>
+        <v>0.01235827664399093</v>
       </c>
       <c r="J3">
-        <v>-0.003124320405944183</v>
+        <v>0.0118774098485049</v>
       </c>
       <c r="K3">
-        <v>-1.25</v>
+        <v>1.9</v>
       </c>
       <c r="L3">
-        <v>-0.004530627038782168</v>
+        <v>0.005385487528344671</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="V3">
-        <v>0.3705263157894737</v>
+        <v>0.3952702702702702</v>
       </c>
       <c r="W3">
-        <v>-0.06345177664974619</v>
+        <v>0.1117647058823529</v>
       </c>
       <c r="X3">
-        <v>0.3648351740137705</v>
+        <v>0.6446563816308131</v>
       </c>
       <c r="Y3">
-        <v>-0.4282869506635167</v>
+        <v>-0.5328916757484601</v>
       </c>
       <c r="Z3">
-        <v>6.617893979371551</v>
+        <v>9.954853273137699</v>
       </c>
       <c r="AA3">
-        <v>-0.02067642120412569</v>
+        <v>0.118237872306787</v>
       </c>
       <c r="AB3">
-        <v>0.1058109160912657</v>
+        <v>0.2025672413402094</v>
       </c>
       <c r="AC3">
-        <v>-0.1264873372953914</v>
+        <v>-0.08432936903342245</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>28.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>32</v>
+        <v>28.5</v>
       </c>
       <c r="AG3">
-        <v>30.24</v>
+        <v>27.33</v>
       </c>
       <c r="AH3">
-        <v>0.8707482993197279</v>
+        <v>0.9059122695486331</v>
       </c>
       <c r="AI3">
-        <v>0.6517311608961304</v>
+        <v>0.8469539375928677</v>
       </c>
       <c r="AJ3">
-        <v>0.8642469276936269</v>
+        <v>0.9022779795311984</v>
       </c>
       <c r="AK3">
-        <v>0.6387832699619771</v>
+        <v>0.8414408866995075</v>
       </c>
       <c r="AL3">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AM3">
-        <v>1.598</v>
+        <v>1.309</v>
       </c>
       <c r="AN3">
-        <v>13.4453781512605</v>
+        <v>3.97489539748954</v>
       </c>
       <c r="AO3">
-        <v>-0.3448</v>
+        <v>2.169154228855722</v>
       </c>
       <c r="AP3">
-        <v>12.70588235294118</v>
+        <v>3.811715481171548</v>
       </c>
       <c r="AQ3">
-        <v>-0.5394242803504381</v>
+        <v>3.330786860198626</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Petrol AD (BUL:PET)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUL:PET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (Automotive)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.905912269548633</v>
+      </c>
+      <c r="F2">
+        <v>0.23</v>
+      </c>
+      <c r="G2">
+        <v>2.96</v>
+      </c>
+      <c r="H2">
+        <v>60.365417336196</v>
+      </c>
+      <c r="I2">
+        <v>30.29</v>
+      </c>
+      <c r="J2">
+        <v>66.431217336196</v>
+      </c>
+      <c r="K2">
+        <v>28.5</v>
+      </c>
+      <c r="L2">
+        <v>7.2358</v>
+      </c>
+      <c r="M2">
+        <v>0.202567241340209</v>
+      </c>
+      <c r="N2">
+        <v>0.10057631199461</v>
+      </c>
+      <c r="O2">
+        <v>0.156652018348624</v>
+      </c>
+      <c r="P2">
+        <v>0.04113</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.644656381630813</v>
+      </c>
+      <c r="T2">
+        <v>0.118333002590402</v>
+      </c>
+      <c r="U2">
+        <v>6.98545598626056</v>
+      </c>
+      <c r="V2">
+        <v>0.917006580924236</v>
+      </c>
+      <c r="W2">
+        <v>13.18510931816473</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2.96</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.1740577981651376</v>
+      </c>
+      <c r="AD2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>7.17</v>
+      </c>
+      <c r="AH2">
+        <v>2.81</v>
+      </c>
+      <c r="AI2">
+        <v>1.14</v>
+      </c>
+      <c r="AJ2">
+        <v>28.5</v>
+      </c>
+      <c r="AK2">
+        <v>28.5</v>
+      </c>
+      <c r="AL2">
+        <v>2.01</v>
+      </c>
+      <c r="AM2">
+        <v>28.5</v>
+      </c>
+      <c r="AN2">
+        <v>1.17</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1014821003015451</v>
+      </c>
+      <c r="C2">
+        <v>66.90465013697475</v>
+      </c>
+      <c r="D2">
+        <v>65.73465013697475</v>
+      </c>
+      <c r="E2">
+        <v>-28.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.17</v>
+      </c>
+      <c r="H2">
+        <v>2.96</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>7.17</v>
+      </c>
+      <c r="K2">
+        <v>2.81</v>
+      </c>
+      <c r="L2">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.4359999999999998</v>
+      </c>
+      <c r="P2">
+        <v>3.923999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>6.734</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1014821003015451</v>
+      </c>
+      <c r="T2">
+        <v>0.7227175714551295</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W2">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1014427182012436</v>
+      </c>
+      <c r="C3">
+        <v>66.62003177565025</v>
+      </c>
+      <c r="D3">
+        <v>65.76463177565024</v>
+      </c>
+      <c r="E3">
+        <v>-28.1854</v>
+      </c>
+      <c r="F3">
+        <v>0.3146</v>
+      </c>
+      <c r="G3">
+        <v>1.17</v>
+      </c>
+      <c r="H3">
+        <v>2.96</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>7.17</v>
+      </c>
+      <c r="K3">
+        <v>2.81</v>
+      </c>
+      <c r="L3">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.01437722</v>
+      </c>
+      <c r="N3">
+        <v>4.345622779999999</v>
+      </c>
+      <c r="O3">
+        <v>0.4345622779999999</v>
+      </c>
+      <c r="P3">
+        <v>3.911060501999999</v>
+      </c>
+      <c r="Q3">
+        <v>6.721060501999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1020519375770137</v>
+      </c>
+      <c r="T3">
+        <v>0.7292877311956306</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W3">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>303.2575143177888</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1014033361009421</v>
+      </c>
+      <c r="C4">
+        <v>66.33544077611535</v>
+      </c>
+      <c r="D4">
+        <v>65.79464077611534</v>
+      </c>
+      <c r="E4">
+        <v>-27.8708</v>
+      </c>
+      <c r="F4">
+        <v>0.6292</v>
+      </c>
+      <c r="G4">
+        <v>1.17</v>
+      </c>
+      <c r="H4">
+        <v>2.96</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>7.17</v>
+      </c>
+      <c r="K4">
+        <v>2.81</v>
+      </c>
+      <c r="L4">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.02875444</v>
+      </c>
+      <c r="N4">
+        <v>4.331245559999999</v>
+      </c>
+      <c r="O4">
+        <v>0.4331245559999998</v>
+      </c>
+      <c r="P4">
+        <v>3.898121004</v>
+      </c>
+      <c r="Q4">
+        <v>6.708121004</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1026334041846347</v>
+      </c>
+      <c r="T4">
+        <v>0.7359919758287952</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W4">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>151.6287571588944</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1013639540006405</v>
+      </c>
+      <c r="C5">
+        <v>66.05087717584347</v>
+      </c>
+      <c r="D5">
+        <v>65.82467717584346</v>
+      </c>
+      <c r="E5">
+        <v>-27.5562</v>
+      </c>
+      <c r="F5">
+        <v>0.9438</v>
+      </c>
+      <c r="G5">
+        <v>1.17</v>
+      </c>
+      <c r="H5">
+        <v>2.96</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>7.17</v>
+      </c>
+      <c r="K5">
+        <v>2.81</v>
+      </c>
+      <c r="L5">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.04313166</v>
+      </c>
+      <c r="N5">
+        <v>4.316868339999999</v>
+      </c>
+      <c r="O5">
+        <v>0.4316868339999998</v>
+      </c>
+      <c r="P5">
+        <v>3.885181505999999</v>
+      </c>
+      <c r="Q5">
+        <v>6.695181505999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1032268597944747</v>
+      </c>
+      <c r="T5">
+        <v>0.7428344523100661</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W5">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>101.0858381059296</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.101324571900339</v>
+      </c>
+      <c r="C6">
+        <v>65.76634101237642</v>
+      </c>
+      <c r="D6">
+        <v>65.85474101237641</v>
+      </c>
+      <c r="E6">
+        <v>-27.2416</v>
+      </c>
+      <c r="F6">
+        <v>1.2584</v>
+      </c>
+      <c r="G6">
+        <v>1.17</v>
+      </c>
+      <c r="H6">
+        <v>2.96</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>7.17</v>
+      </c>
+      <c r="K6">
+        <v>2.81</v>
+      </c>
+      <c r="L6">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.05750888000000001</v>
+      </c>
+      <c r="N6">
+        <v>4.302491119999999</v>
+      </c>
+      <c r="O6">
+        <v>0.4302491119999998</v>
+      </c>
+      <c r="P6">
+        <v>3.872242007999999</v>
+      </c>
+      <c r="Q6">
+        <v>6.682242007999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1038326790628531</v>
+      </c>
+      <c r="T6">
+        <v>0.7498194803846969</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W6">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>75.81437857944718</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1012851898000374</v>
+      </c>
+      <c r="C7">
+        <v>65.48183232332474</v>
+      </c>
+      <c r="D7">
+        <v>65.88483232332473</v>
+      </c>
+      <c r="E7">
+        <v>-26.927</v>
+      </c>
+      <c r="F7">
+        <v>1.573</v>
+      </c>
+      <c r="G7">
+        <v>1.17</v>
+      </c>
+      <c r="H7">
+        <v>2.96</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>7.17</v>
+      </c>
+      <c r="K7">
+        <v>2.81</v>
+      </c>
+      <c r="L7">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.07188610000000001</v>
+      </c>
+      <c r="N7">
+        <v>4.288113899999999</v>
+      </c>
+      <c r="O7">
+        <v>0.4288113899999998</v>
+      </c>
+      <c r="P7">
+        <v>3.859302509999999</v>
+      </c>
+      <c r="Q7">
+        <v>6.66930251</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.104451252421092</v>
+      </c>
+      <c r="T7">
+        <v>0.7569515616819513</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W7">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>60.65150286355775</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1012458076997359</v>
+      </c>
+      <c r="C8">
+        <v>65.19735114636762</v>
+      </c>
+      <c r="D8">
+        <v>65.91495114636763</v>
+      </c>
+      <c r="E8">
+        <v>-26.6124</v>
+      </c>
+      <c r="F8">
+        <v>1.8876</v>
+      </c>
+      <c r="G8">
+        <v>1.17</v>
+      </c>
+      <c r="H8">
+        <v>2.96</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>7.17</v>
+      </c>
+      <c r="K8">
+        <v>2.81</v>
+      </c>
+      <c r="L8">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.08626332</v>
+      </c>
+      <c r="N8">
+        <v>4.27373668</v>
+      </c>
+      <c r="O8">
+        <v>0.4273736679999999</v>
+      </c>
+      <c r="P8">
+        <v>3.846363012</v>
+      </c>
+      <c r="Q8">
+        <v>6.656363012</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1050829869146126</v>
+      </c>
+      <c r="T8">
+        <v>0.7642353893897859</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W8">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>50.5429190529648</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1012064255994343</v>
+      </c>
+      <c r="C9">
+        <v>64.91289751925329</v>
+      </c>
+      <c r="D9">
+        <v>65.9450975192533</v>
+      </c>
+      <c r="E9">
+        <v>-26.2978</v>
+      </c>
+      <c r="F9">
+        <v>2.2022</v>
+      </c>
+      <c r="G9">
+        <v>1.17</v>
+      </c>
+      <c r="H9">
+        <v>2.96</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>7.17</v>
+      </c>
+      <c r="K9">
+        <v>2.81</v>
+      </c>
+      <c r="L9">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.10064054</v>
+      </c>
+      <c r="N9">
+        <v>4.25935946</v>
+      </c>
+      <c r="O9">
+        <v>0.4259359459999999</v>
+      </c>
+      <c r="P9">
+        <v>3.833423514</v>
+      </c>
+      <c r="Q9">
+        <v>6.643423514</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.105728307096166</v>
+      </c>
+      <c r="T9">
+        <v>0.7716758585537029</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W9">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>43.32250204539839</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1011670434991328</v>
+      </c>
+      <c r="C10">
+        <v>64.62847147979902</v>
+      </c>
+      <c r="D10">
+        <v>65.97527147979902</v>
+      </c>
+      <c r="E10">
+        <v>-25.9832</v>
+      </c>
+      <c r="F10">
+        <v>2.5168</v>
+      </c>
+      <c r="G10">
+        <v>1.17</v>
+      </c>
+      <c r="H10">
+        <v>2.96</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>7.17</v>
+      </c>
+      <c r="K10">
+        <v>2.81</v>
+      </c>
+      <c r="L10">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.11501776</v>
+      </c>
+      <c r="N10">
+        <v>4.24498224</v>
+      </c>
+      <c r="O10">
+        <v>0.4244982239999999</v>
+      </c>
+      <c r="P10">
+        <v>3.820484016</v>
+      </c>
+      <c r="Q10">
+        <v>6.630484016</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1063876559773182</v>
+      </c>
+      <c r="T10">
+        <v>0.77927807704727</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W10">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>37.9071892897236</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1011276613988312</v>
+      </c>
+      <c r="C11">
+        <v>64.34407306589131</v>
+      </c>
+      <c r="D11">
+        <v>66.00547306589131</v>
+      </c>
+      <c r="E11">
+        <v>-25.6686</v>
+      </c>
+      <c r="F11">
+        <v>2.8314</v>
+      </c>
+      <c r="G11">
+        <v>1.17</v>
+      </c>
+      <c r="H11">
+        <v>2.96</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>7.17</v>
+      </c>
+      <c r="K11">
+        <v>2.81</v>
+      </c>
+      <c r="L11">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.12939498</v>
+      </c>
+      <c r="N11">
+        <v>4.23060502</v>
+      </c>
+      <c r="O11">
+        <v>0.4230605019999999</v>
+      </c>
+      <c r="P11">
+        <v>3.807544518</v>
+      </c>
+      <c r="Q11">
+        <v>6.617544518</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1070614960426717</v>
+      </c>
+      <c r="T11">
+        <v>0.7870473772659706</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W11">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>33.6952793686432</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1010882792985297</v>
+      </c>
+      <c r="C12">
+        <v>64.05970231548606</v>
+      </c>
+      <c r="D12">
+        <v>66.03570231548606</v>
+      </c>
+      <c r="E12">
+        <v>-25.354</v>
+      </c>
+      <c r="F12">
+        <v>3.146</v>
+      </c>
+      <c r="G12">
+        <v>1.17</v>
+      </c>
+      <c r="H12">
+        <v>2.96</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>7.17</v>
+      </c>
+      <c r="K12">
+        <v>2.81</v>
+      </c>
+      <c r="L12">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.1437722</v>
+      </c>
+      <c r="N12">
+        <v>4.2162278</v>
+      </c>
+      <c r="O12">
+        <v>0.4216227799999999</v>
+      </c>
+      <c r="P12">
+        <v>3.79460502</v>
+      </c>
+      <c r="Q12">
+        <v>6.604605019999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1077503103316997</v>
+      </c>
+      <c r="T12">
+        <v>0.7949893286006425</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W12">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>30.32575143177888</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1010488971982281</v>
+      </c>
+      <c r="C13">
+        <v>63.77535926660883</v>
+      </c>
+      <c r="D13">
+        <v>66.06595926660883</v>
+      </c>
+      <c r="E13">
+        <v>-25.0394</v>
+      </c>
+      <c r="F13">
+        <v>3.4606</v>
+      </c>
+      <c r="G13">
+        <v>1.17</v>
+      </c>
+      <c r="H13">
+        <v>2.96</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>7.17</v>
+      </c>
+      <c r="K13">
+        <v>2.81</v>
+      </c>
+      <c r="L13">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.15814942</v>
+      </c>
+      <c r="N13">
+        <v>4.201850579999999</v>
+      </c>
+      <c r="O13">
+        <v>0.4201850579999998</v>
+      </c>
+      <c r="P13">
+        <v>3.781665522</v>
+      </c>
+      <c r="Q13">
+        <v>6.591665522</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1084546035935148</v>
+      </c>
+      <c r="T13">
+        <v>0.8031097507518236</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W13">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>27.5688649379808</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1010095150979266</v>
+      </c>
+      <c r="C14">
+        <v>63.49104395735476</v>
+      </c>
+      <c r="D14">
+        <v>66.09624395735476</v>
+      </c>
+      <c r="E14">
+        <v>-24.7248</v>
+      </c>
+      <c r="F14">
+        <v>3.7752</v>
+      </c>
+      <c r="G14">
+        <v>1.17</v>
+      </c>
+      <c r="H14">
+        <v>2.96</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>7.17</v>
+      </c>
+      <c r="K14">
+        <v>2.81</v>
+      </c>
+      <c r="L14">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M14">
+        <v>0.17252664</v>
+      </c>
+      <c r="N14">
+        <v>4.187473359999999</v>
+      </c>
+      <c r="O14">
+        <v>0.4187473359999999</v>
+      </c>
+      <c r="P14">
+        <v>3.768726023999999</v>
+      </c>
+      <c r="Q14">
+        <v>6.578726024</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1091749035203711</v>
+      </c>
+      <c r="T14">
+        <v>0.8114147279518954</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W14">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>25.2714595264824</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1009701329976251</v>
+      </c>
+      <c r="C15">
+        <v>63.20675642588898</v>
+      </c>
+      <c r="D15">
+        <v>66.12655642588898</v>
+      </c>
+      <c r="E15">
+        <v>-24.4102</v>
+      </c>
+      <c r="F15">
+        <v>4.0898</v>
+      </c>
+      <c r="G15">
+        <v>1.17</v>
+      </c>
+      <c r="H15">
+        <v>2.96</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>7.17</v>
+      </c>
+      <c r="K15">
+        <v>2.81</v>
+      </c>
+      <c r="L15">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M15">
+        <v>0.18690386</v>
+      </c>
+      <c r="N15">
+        <v>4.173096139999999</v>
+      </c>
+      <c r="O15">
+        <v>0.4173096139999998</v>
+      </c>
+      <c r="P15">
+        <v>3.755786526</v>
+      </c>
+      <c r="Q15">
+        <v>6.565786526</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1099117620662357</v>
+      </c>
+      <c r="T15">
+        <v>0.8199106241680607</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W15">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>23.32750110136837</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1009307508973235</v>
+      </c>
+      <c r="C16">
+        <v>62.9224967104466</v>
+      </c>
+      <c r="D16">
+        <v>66.1568967104466</v>
+      </c>
+      <c r="E16">
+        <v>-24.0956</v>
+      </c>
+      <c r="F16">
+        <v>4.404400000000001</v>
+      </c>
+      <c r="G16">
+        <v>1.17</v>
+      </c>
+      <c r="H16">
+        <v>2.96</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>7.17</v>
+      </c>
+      <c r="K16">
+        <v>2.81</v>
+      </c>
+      <c r="L16">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M16">
+        <v>0.2012810800000001</v>
+      </c>
+      <c r="N16">
+        <v>4.158718919999999</v>
+      </c>
+      <c r="O16">
+        <v>0.4158718919999999</v>
+      </c>
+      <c r="P16">
+        <v>3.742847027999999</v>
+      </c>
+      <c r="Q16">
+        <v>6.552847028</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1106657568573529</v>
+      </c>
+      <c r="T16">
+        <v>0.8286040993659972</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W16">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>21.66125102269919</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.100891368797022</v>
+      </c>
+      <c r="C17">
+        <v>62.63826484933298</v>
+      </c>
+      <c r="D17">
+        <v>66.18726484933298</v>
+      </c>
+      <c r="E17">
+        <v>-23.781</v>
+      </c>
+      <c r="F17">
+        <v>4.719</v>
+      </c>
+      <c r="G17">
+        <v>1.17</v>
+      </c>
+      <c r="H17">
+        <v>2.96</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>7.17</v>
+      </c>
+      <c r="K17">
+        <v>2.81</v>
+      </c>
+      <c r="L17">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M17">
+        <v>0.2156583</v>
+      </c>
+      <c r="N17">
+        <v>4.144341699999999</v>
+      </c>
+      <c r="O17">
+        <v>0.4144341699999998</v>
+      </c>
+      <c r="P17">
+        <v>3.729907529999999</v>
+      </c>
+      <c r="Q17">
+        <v>6.539907529999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1114374927023788</v>
+      </c>
+      <c r="T17">
+        <v>0.8375021269215325</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W17">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>20.21716762118592</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1008519866967204</v>
+      </c>
+      <c r="C18">
+        <v>62.35406088092383</v>
+      </c>
+      <c r="D18">
+        <v>66.21766088092383</v>
+      </c>
+      <c r="E18">
+        <v>-23.4664</v>
+      </c>
+      <c r="F18">
+        <v>5.0336</v>
+      </c>
+      <c r="G18">
+        <v>1.17</v>
+      </c>
+      <c r="H18">
+        <v>2.96</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>7.17</v>
+      </c>
+      <c r="K18">
+        <v>2.81</v>
+      </c>
+      <c r="L18">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M18">
+        <v>0.23003552</v>
+      </c>
+      <c r="N18">
+        <v>4.129964479999999</v>
+      </c>
+      <c r="O18">
+        <v>0.4129964479999998</v>
+      </c>
+      <c r="P18">
+        <v>3.716968031999999</v>
+      </c>
+      <c r="Q18">
+        <v>6.526968031999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1122276032103815</v>
+      </c>
+      <c r="T18">
+        <v>0.8466120122760089</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W18">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>18.95359464486179</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1008126045964189</v>
+      </c>
+      <c r="C19">
+        <v>62.06988484366538</v>
+      </c>
+      <c r="D19">
+        <v>66.24808484366538</v>
+      </c>
+      <c r="E19">
+        <v>-23.1518</v>
+      </c>
+      <c r="F19">
+        <v>5.3482</v>
+      </c>
+      <c r="G19">
+        <v>1.17</v>
+      </c>
+      <c r="H19">
+        <v>2.96</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>7.17</v>
+      </c>
+      <c r="K19">
+        <v>2.81</v>
+      </c>
+      <c r="L19">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M19">
+        <v>0.24441274</v>
+      </c>
+      <c r="N19">
+        <v>4.115587259999999</v>
+      </c>
+      <c r="O19">
+        <v>0.4115587259999998</v>
+      </c>
+      <c r="P19">
+        <v>3.704028533999999</v>
+      </c>
+      <c r="Q19">
+        <v>6.514028533999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1130367525258059</v>
+      </c>
+      <c r="T19">
+        <v>0.8559414129402317</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W19">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>17.8386773128111</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1007732224961173</v>
+      </c>
+      <c r="C20">
+        <v>61.78573677607456</v>
+      </c>
+      <c r="D20">
+        <v>66.27853677607456</v>
+      </c>
+      <c r="E20">
+        <v>-22.8372</v>
+      </c>
+      <c r="F20">
+        <v>5.6628</v>
+      </c>
+      <c r="G20">
+        <v>1.17</v>
+      </c>
+      <c r="H20">
+        <v>2.96</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>7.17</v>
+      </c>
+      <c r="K20">
+        <v>2.81</v>
+      </c>
+      <c r="L20">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M20">
+        <v>0.25878996</v>
+      </c>
+      <c r="N20">
+        <v>4.10121004</v>
+      </c>
+      <c r="O20">
+        <v>0.4101210039999999</v>
+      </c>
+      <c r="P20">
+        <v>3.691089036</v>
+      </c>
+      <c r="Q20">
+        <v>6.501089036</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.113865637190387</v>
+      </c>
+      <c r="T20">
+        <v>0.8654983599621184</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W20">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>16.8476396843216</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1007338403958158</v>
+      </c>
+      <c r="C21">
+        <v>61.50161671673914</v>
+      </c>
+      <c r="D21">
+        <v>66.30901671673914</v>
+      </c>
+      <c r="E21">
+        <v>-22.5226</v>
+      </c>
+      <c r="F21">
+        <v>5.9774</v>
+      </c>
+      <c r="G21">
+        <v>1.17</v>
+      </c>
+      <c r="H21">
+        <v>2.96</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>7.17</v>
+      </c>
+      <c r="K21">
+        <v>2.81</v>
+      </c>
+      <c r="L21">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M21">
+        <v>0.2731671800000001</v>
+      </c>
+      <c r="N21">
+        <v>4.08683282</v>
+      </c>
+      <c r="O21">
+        <v>0.4086832819999999</v>
+      </c>
+      <c r="P21">
+        <v>3.678149538</v>
+      </c>
+      <c r="Q21">
+        <v>6.488149538</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1147149881429824</v>
+      </c>
+      <c r="T21">
+        <v>0.8752912809845457</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W21">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>15.96092180619941</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1006944582955143</v>
+      </c>
+      <c r="C22">
+        <v>61.21752470431791</v>
+      </c>
+      <c r="D22">
+        <v>66.33952470431791</v>
+      </c>
+      <c r="E22">
+        <v>-22.208</v>
+      </c>
+      <c r="F22">
+        <v>6.292000000000001</v>
+      </c>
+      <c r="G22">
+        <v>1.17</v>
+      </c>
+      <c r="H22">
+        <v>2.96</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>7.17</v>
+      </c>
+      <c r="K22">
+        <v>2.81</v>
+      </c>
+      <c r="L22">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M22">
+        <v>0.2875444</v>
+      </c>
+      <c r="N22">
+        <v>4.0724556</v>
+      </c>
+      <c r="O22">
+        <v>0.4072455599999999</v>
+      </c>
+      <c r="P22">
+        <v>3.66521004</v>
+      </c>
+      <c r="Q22">
+        <v>6.47521004</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1155855728693928</v>
+      </c>
+      <c r="T22">
+        <v>0.8853290250325337</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W22">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>15.16287571588944</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1006550761952127</v>
+      </c>
+      <c r="C23">
+        <v>60.93346077754089</v>
+      </c>
+      <c r="D23">
+        <v>66.37006077754089</v>
+      </c>
+      <c r="E23">
+        <v>-21.8934</v>
+      </c>
+      <c r="F23">
+        <v>6.6066</v>
+      </c>
+      <c r="G23">
+        <v>1.17</v>
+      </c>
+      <c r="H23">
+        <v>2.96</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>7.17</v>
+      </c>
+      <c r="K23">
+        <v>2.81</v>
+      </c>
+      <c r="L23">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M23">
+        <v>0.3019216200000001</v>
+      </c>
+      <c r="N23">
+        <v>4.05807838</v>
+      </c>
+      <c r="O23">
+        <v>0.4058078379999999</v>
+      </c>
+      <c r="P23">
+        <v>3.652270542</v>
+      </c>
+      <c r="Q23">
+        <v>6.462270542</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1164781977154591</v>
+      </c>
+      <c r="T23">
+        <v>0.8956208891830022</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W23">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>14.4408340151328</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1006156940949112</v>
+      </c>
+      <c r="C24">
+        <v>60.6494249752093</v>
+      </c>
+      <c r="D24">
+        <v>66.4006249752093</v>
+      </c>
+      <c r="E24">
+        <v>-21.5788</v>
+      </c>
+      <c r="F24">
+        <v>6.9212</v>
+      </c>
+      <c r="G24">
+        <v>1.17</v>
+      </c>
+      <c r="H24">
+        <v>2.96</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>7.17</v>
+      </c>
+      <c r="K24">
+        <v>2.81</v>
+      </c>
+      <c r="L24">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M24">
+        <v>0.31629884</v>
+      </c>
+      <c r="N24">
+        <v>4.043701159999999</v>
+      </c>
+      <c r="O24">
+        <v>0.4043701159999998</v>
+      </c>
+      <c r="P24">
+        <v>3.639331044</v>
+      </c>
+      <c r="Q24">
+        <v>6.449331043999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1173937103780912</v>
+      </c>
+      <c r="T24">
+        <v>0.906176647286047</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W24">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>13.7844324689904</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1005763119946096</v>
+      </c>
+      <c r="C25">
+        <v>60.36541733619605</v>
+      </c>
+      <c r="D25">
+        <v>66.43121733619604</v>
+      </c>
+      <c r="E25">
+        <v>-21.2642</v>
+      </c>
+      <c r="F25">
+        <v>7.2358</v>
+      </c>
+      <c r="G25">
+        <v>1.17</v>
+      </c>
+      <c r="H25">
+        <v>2.96</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>7.17</v>
+      </c>
+      <c r="K25">
+        <v>2.81</v>
+      </c>
+      <c r="L25">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M25">
+        <v>0.33067606</v>
+      </c>
+      <c r="N25">
+        <v>4.029323939999999</v>
+      </c>
+      <c r="O25">
+        <v>0.4029323939999999</v>
+      </c>
+      <c r="P25">
+        <v>3.626391545999999</v>
+      </c>
+      <c r="Q25">
+        <v>6.436391545999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1183330025904021</v>
+      </c>
+      <c r="T25">
+        <v>0.9170065809242357</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W25">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>13.18510931816473</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1008825298943081</v>
+      </c>
+      <c r="C26">
+        <v>59.81368449345159</v>
+      </c>
+      <c r="D26">
+        <v>66.19408449345158</v>
+      </c>
+      <c r="E26">
+        <v>-20.9496</v>
+      </c>
+      <c r="F26">
+        <v>7.5504</v>
+      </c>
+      <c r="G26">
+        <v>1.17</v>
+      </c>
+      <c r="H26">
+        <v>2.96</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>7.17</v>
+      </c>
+      <c r="K26">
+        <v>2.81</v>
+      </c>
+      <c r="L26">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M26">
+        <v>0.35713392</v>
+      </c>
+      <c r="N26">
+        <v>4.00286608</v>
+      </c>
+      <c r="O26">
+        <v>0.4002866079999999</v>
+      </c>
+      <c r="P26">
+        <v>3.602579472</v>
+      </c>
+      <c r="Q26">
+        <v>6.412579471999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1192970130188264</v>
+      </c>
+      <c r="T26">
+        <v>0.928121512816061</v>
+      </c>
+      <c r="U26">
+        <v>0.0473</v>
+      </c>
+      <c r="V26">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W26">
+        <v>0.04257</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>12.20830550063685</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1008575477940065</v>
+      </c>
+      <c r="C27">
+        <v>59.51836700249587</v>
+      </c>
+      <c r="D27">
+        <v>66.21336700249587</v>
+      </c>
+      <c r="E27">
+        <v>-20.635</v>
+      </c>
+      <c r="F27">
+        <v>7.865</v>
+      </c>
+      <c r="G27">
+        <v>1.17</v>
+      </c>
+      <c r="H27">
+        <v>2.96</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>7.17</v>
+      </c>
+      <c r="K27">
+        <v>2.81</v>
+      </c>
+      <c r="L27">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M27">
+        <v>0.3720145</v>
+      </c>
+      <c r="N27">
+        <v>3.987985499999999</v>
+      </c>
+      <c r="O27">
+        <v>0.3987985499999999</v>
+      </c>
+      <c r="P27">
+        <v>3.589186949999999</v>
+      </c>
+      <c r="Q27">
+        <v>6.399186949999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1202867303920087</v>
+      </c>
+      <c r="T27">
+        <v>0.9395328428916684</v>
+      </c>
+      <c r="U27">
+        <v>0.0473</v>
+      </c>
+      <c r="V27">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W27">
+        <v>0.04257</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>11.71997328061137</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.100832565693705</v>
+      </c>
+      <c r="C28">
+        <v>59.22306074890376</v>
+      </c>
+      <c r="D28">
+        <v>66.23266074890375</v>
+      </c>
+      <c r="E28">
+        <v>-20.3204</v>
+      </c>
+      <c r="F28">
+        <v>8.179600000000001</v>
+      </c>
+      <c r="G28">
+        <v>1.17</v>
+      </c>
+      <c r="H28">
+        <v>2.96</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>7.17</v>
+      </c>
+      <c r="K28">
+        <v>2.81</v>
+      </c>
+      <c r="L28">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M28">
+        <v>0.3868950800000001</v>
+      </c>
+      <c r="N28">
+        <v>3.973104919999999</v>
+      </c>
+      <c r="O28">
+        <v>0.3973104919999998</v>
+      </c>
+      <c r="P28">
+        <v>3.575794428</v>
+      </c>
+      <c r="Q28">
+        <v>6.385794428</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1213031968833851</v>
+      </c>
+      <c r="T28">
+        <v>0.9512525872936435</v>
+      </c>
+      <c r="U28">
+        <v>0.0473</v>
+      </c>
+      <c r="V28">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W28">
+        <v>0.04257</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>11.26920507751093</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1008075835934034</v>
+      </c>
+      <c r="C29">
+        <v>58.92776574250137</v>
+      </c>
+      <c r="D29">
+        <v>66.25196574250137</v>
+      </c>
+      <c r="E29">
+        <v>-20.0058</v>
+      </c>
+      <c r="F29">
+        <v>8.494200000000001</v>
+      </c>
+      <c r="G29">
+        <v>1.17</v>
+      </c>
+      <c r="H29">
+        <v>2.96</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>7.17</v>
+      </c>
+      <c r="K29">
+        <v>2.81</v>
+      </c>
+      <c r="L29">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M29">
+        <v>0.4017756600000001</v>
+      </c>
+      <c r="N29">
+        <v>3.958224339999999</v>
+      </c>
+      <c r="O29">
+        <v>0.3958224339999998</v>
+      </c>
+      <c r="P29">
+        <v>3.562401905999999</v>
+      </c>
+      <c r="Q29">
+        <v>6.372401905999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1223475117717855</v>
+      </c>
+      <c r="T29">
+        <v>0.9632934205833439</v>
+      </c>
+      <c r="U29">
+        <v>0.0473</v>
+      </c>
+      <c r="V29">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W29">
+        <v>0.04257</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>10.85182711167719</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1007826014931019</v>
+      </c>
+      <c r="C30">
+        <v>58.63248199312631</v>
+      </c>
+      <c r="D30">
+        <v>66.27128199312631</v>
+      </c>
+      <c r="E30">
+        <v>-19.6912</v>
+      </c>
+      <c r="F30">
+        <v>8.808800000000002</v>
+      </c>
+      <c r="G30">
+        <v>1.17</v>
+      </c>
+      <c r="H30">
+        <v>2.96</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>7.17</v>
+      </c>
+      <c r="K30">
+        <v>2.81</v>
+      </c>
+      <c r="L30">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M30">
+        <v>0.4166562400000001</v>
+      </c>
+      <c r="N30">
+        <v>3.943343759999999</v>
+      </c>
+      <c r="O30">
+        <v>0.3943343759999999</v>
+      </c>
+      <c r="P30">
+        <v>3.549009384</v>
+      </c>
+      <c r="Q30">
+        <v>6.359009384</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1234208354070859</v>
+      </c>
+      <c r="T30">
+        <v>0.9756687214644248</v>
+      </c>
+      <c r="U30">
+        <v>0.0473</v>
+      </c>
+      <c r="V30">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W30">
+        <v>0.04257</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>10.46426185768872</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1017494193928003</v>
+      </c>
+      <c r="C31">
+        <v>57.57846012032897</v>
+      </c>
+      <c r="D31">
+        <v>65.53186012032897</v>
+      </c>
+      <c r="E31">
+        <v>-19.3766</v>
+      </c>
+      <c r="F31">
+        <v>9.1234</v>
+      </c>
+      <c r="G31">
+        <v>1.17</v>
+      </c>
+      <c r="H31">
+        <v>2.96</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>7.17</v>
+      </c>
+      <c r="K31">
+        <v>2.81</v>
+      </c>
+      <c r="L31">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M31">
+        <v>0.46620574</v>
+      </c>
+      <c r="N31">
+        <v>3.89379426</v>
+      </c>
+      <c r="O31">
+        <v>0.3893794259999999</v>
+      </c>
+      <c r="P31">
+        <v>3.504414833999999</v>
+      </c>
+      <c r="Q31">
+        <v>6.314414833999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1245243935109864</v>
+      </c>
+      <c r="T31">
+        <v>0.988392622370325</v>
+      </c>
+      <c r="U31">
+        <v>0.0511</v>
+      </c>
+      <c r="V31">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W31">
+        <v>0.04599</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>9.352094206304709</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1017586372924988</v>
+      </c>
+      <c r="C32">
+        <v>57.2568896751558</v>
+      </c>
+      <c r="D32">
+        <v>65.5248896751558</v>
+      </c>
+      <c r="E32">
+        <v>-19.062</v>
+      </c>
+      <c r="F32">
+        <v>9.438000000000001</v>
+      </c>
+      <c r="G32">
+        <v>1.17</v>
+      </c>
+      <c r="H32">
+        <v>2.96</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>7.17</v>
+      </c>
+      <c r="K32">
+        <v>2.81</v>
+      </c>
+      <c r="L32">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M32">
+        <v>0.4822818</v>
+      </c>
+      <c r="N32">
+        <v>3.877718199999999</v>
+      </c>
+      <c r="O32">
+        <v>0.3877718199999999</v>
+      </c>
+      <c r="P32">
+        <v>3.48994638</v>
+      </c>
+      <c r="Q32">
+        <v>6.29994638</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1256594818464268</v>
+      </c>
+      <c r="T32">
+        <v>1.001480063302108</v>
+      </c>
+      <c r="U32">
+        <v>0.0511</v>
+      </c>
+      <c r="V32">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W32">
+        <v>0.04599</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>9.040357732761217</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1017678551921972</v>
+      </c>
+      <c r="C33">
+        <v>56.93532071267941</v>
+      </c>
+      <c r="D33">
+        <v>65.51792071267941</v>
+      </c>
+      <c r="E33">
+        <v>-18.7474</v>
+      </c>
+      <c r="F33">
+        <v>9.752600000000001</v>
+      </c>
+      <c r="G33">
+        <v>1.17</v>
+      </c>
+      <c r="H33">
+        <v>2.96</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>7.17</v>
+      </c>
+      <c r="K33">
+        <v>2.81</v>
+      </c>
+      <c r="L33">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M33">
+        <v>0.49835786</v>
+      </c>
+      <c r="N33">
+        <v>3.861642139999999</v>
+      </c>
+      <c r="O33">
+        <v>0.3861642139999998</v>
+      </c>
+      <c r="P33">
+        <v>3.475477925999999</v>
+      </c>
+      <c r="Q33">
+        <v>6.285477926</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1268274712930395</v>
+      </c>
+      <c r="T33">
+        <v>1.014946850347856</v>
+      </c>
+      <c r="U33">
+        <v>0.0511</v>
+      </c>
+      <c r="V33">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W33">
+        <v>0.04599</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.748733289768921</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1017770730918957</v>
+      </c>
+      <c r="C34">
+        <v>56.61375323242676</v>
+      </c>
+      <c r="D34">
+        <v>65.51095323242676</v>
+      </c>
+      <c r="E34">
+        <v>-18.4328</v>
+      </c>
+      <c r="F34">
+        <v>10.0672</v>
+      </c>
+      <c r="G34">
+        <v>1.17</v>
+      </c>
+      <c r="H34">
+        <v>2.96</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>7.17</v>
+      </c>
+      <c r="K34">
+        <v>2.81</v>
+      </c>
+      <c r="L34">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M34">
+        <v>0.51443392</v>
+      </c>
+      <c r="N34">
+        <v>3.845566079999999</v>
+      </c>
+      <c r="O34">
+        <v>0.3845566079999999</v>
+      </c>
+      <c r="P34">
+        <v>3.461009471999999</v>
+      </c>
+      <c r="Q34">
+        <v>6.271009471999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1280298133704348</v>
+      </c>
+      <c r="T34">
+        <v>1.028809719365537</v>
+      </c>
+      <c r="U34">
+        <v>0.0511</v>
+      </c>
+      <c r="V34">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W34">
+        <v>0.04599</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>8.475335374463643</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1017862909915941</v>
+      </c>
+      <c r="C35">
+        <v>56.29218723392501</v>
+      </c>
+      <c r="D35">
+        <v>65.503987233925</v>
+      </c>
+      <c r="E35">
+        <v>-18.1182</v>
+      </c>
+      <c r="F35">
+        <v>10.3818</v>
+      </c>
+      <c r="G35">
+        <v>1.17</v>
+      </c>
+      <c r="H35">
+        <v>2.96</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>7.17</v>
+      </c>
+      <c r="K35">
+        <v>2.81</v>
+      </c>
+      <c r="L35">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M35">
+        <v>0.53050998</v>
+      </c>
+      <c r="N35">
+        <v>3.829490019999999</v>
+      </c>
+      <c r="O35">
+        <v>0.3829490019999998</v>
+      </c>
+      <c r="P35">
+        <v>3.446541018</v>
+      </c>
+      <c r="Q35">
+        <v>6.256541018</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1292680462561107</v>
+      </c>
+      <c r="T35">
+        <v>1.043086405368821</v>
+      </c>
+      <c r="U35">
+        <v>0.0511</v>
+      </c>
+      <c r="V35">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W35">
+        <v>0.04599</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>8.218507029782925</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1017955088912926</v>
+      </c>
+      <c r="C36">
+        <v>55.9706227167015</v>
+      </c>
+      <c r="D36">
+        <v>65.49702271670149</v>
+      </c>
+      <c r="E36">
+        <v>-17.8036</v>
+      </c>
+      <c r="F36">
+        <v>10.6964</v>
+      </c>
+      <c r="G36">
+        <v>1.17</v>
+      </c>
+      <c r="H36">
+        <v>2.96</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>7.17</v>
+      </c>
+      <c r="K36">
+        <v>2.81</v>
+      </c>
+      <c r="L36">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M36">
+        <v>0.54658604</v>
+      </c>
+      <c r="N36">
+        <v>3.813413959999999</v>
+      </c>
+      <c r="O36">
+        <v>0.3813413959999998</v>
+      </c>
+      <c r="P36">
+        <v>3.432072563999999</v>
+      </c>
+      <c r="Q36">
+        <v>6.242072563999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1305438013504434</v>
+      </c>
+      <c r="T36">
+        <v>1.05779571822069</v>
+      </c>
+      <c r="U36">
+        <v>0.0511</v>
+      </c>
+      <c r="V36">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W36">
+        <v>0.04599</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.97678623478931</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1024032267909911</v>
+      </c>
+      <c r="C37">
+        <v>55.20011044956664</v>
+      </c>
+      <c r="D37">
+        <v>65.04111044956665</v>
+      </c>
+      <c r="E37">
+        <v>-17.489</v>
+      </c>
+      <c r="F37">
+        <v>11.011</v>
+      </c>
+      <c r="G37">
+        <v>1.17</v>
+      </c>
+      <c r="H37">
+        <v>2.96</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>7.17</v>
+      </c>
+      <c r="K37">
+        <v>2.81</v>
+      </c>
+      <c r="L37">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M37">
+        <v>0.5835830000000001</v>
+      </c>
+      <c r="N37">
+        <v>3.776416999999999</v>
+      </c>
+      <c r="O37">
+        <v>0.3776416999999999</v>
+      </c>
+      <c r="P37">
+        <v>3.3987753</v>
+      </c>
+      <c r="Q37">
+        <v>6.208775299999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1318588104476786</v>
+      </c>
+      <c r="T37">
+        <v>1.072957625314154</v>
+      </c>
+      <c r="U37">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W37">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>7.471088088583799</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1024295446906895</v>
+      </c>
+      <c r="C38">
+        <v>54.86591000286671</v>
+      </c>
+      <c r="D38">
+        <v>65.02151000286671</v>
+      </c>
+      <c r="E38">
+        <v>-17.1744</v>
+      </c>
+      <c r="F38">
+        <v>11.3256</v>
+      </c>
+      <c r="G38">
+        <v>1.17</v>
+      </c>
+      <c r="H38">
+        <v>2.96</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>7.17</v>
+      </c>
+      <c r="K38">
+        <v>2.81</v>
+      </c>
+      <c r="L38">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M38">
+        <v>0.6002568</v>
+      </c>
+      <c r="N38">
+        <v>3.7597432</v>
+      </c>
+      <c r="O38">
+        <v>0.3759743199999999</v>
+      </c>
+      <c r="P38">
+        <v>3.38376888</v>
+      </c>
+      <c r="Q38">
+        <v>6.19376888</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1332149135792024</v>
+      </c>
+      <c r="T38">
+        <v>1.088593342004289</v>
+      </c>
+      <c r="U38">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W38">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>7.263557863900916</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.102455862590388</v>
+      </c>
+      <c r="C39">
+        <v>54.53172136598275</v>
+      </c>
+      <c r="D39">
+        <v>65.00192136598275</v>
+      </c>
+      <c r="E39">
+        <v>-16.8598</v>
+      </c>
+      <c r="F39">
+        <v>11.6402</v>
+      </c>
+      <c r="G39">
+        <v>1.17</v>
+      </c>
+      <c r="H39">
+        <v>2.96</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>7.17</v>
+      </c>
+      <c r="K39">
+        <v>2.81</v>
+      </c>
+      <c r="L39">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M39">
+        <v>0.6169306000000001</v>
+      </c>
+      <c r="N39">
+        <v>3.7430694</v>
+      </c>
+      <c r="O39">
+        <v>0.3743069399999999</v>
+      </c>
+      <c r="P39">
+        <v>3.36876246</v>
+      </c>
+      <c r="Q39">
+        <v>6.17876246</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1346140676037904</v>
+      </c>
+      <c r="T39">
+        <v>1.104725430652841</v>
+      </c>
+      <c r="U39">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W39">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>7.06724548920089</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1024821804900864</v>
+      </c>
+      <c r="C40">
+        <v>54.1975445282443</v>
+      </c>
+      <c r="D40">
+        <v>64.9823445282443</v>
+      </c>
+      <c r="E40">
+        <v>-16.5452</v>
+      </c>
+      <c r="F40">
+        <v>11.9548</v>
+      </c>
+      <c r="G40">
+        <v>1.17</v>
+      </c>
+      <c r="H40">
+        <v>2.96</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>7.17</v>
+      </c>
+      <c r="K40">
+        <v>2.81</v>
+      </c>
+      <c r="L40">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M40">
+        <v>0.6336044000000001</v>
+      </c>
+      <c r="N40">
+        <v>3.726395599999999</v>
+      </c>
+      <c r="O40">
+        <v>0.3726395599999998</v>
+      </c>
+      <c r="P40">
+        <v>3.353756039999999</v>
+      </c>
+      <c r="Q40">
+        <v>6.163756039999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1360583556291717</v>
+      </c>
+      <c r="T40">
+        <v>1.121377909257798</v>
+      </c>
+      <c r="U40">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W40">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.881265344748235</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1025084983897849</v>
+      </c>
+      <c r="C41">
+        <v>53.86337947899389</v>
+      </c>
+      <c r="D41">
+        <v>64.96277947899389</v>
+      </c>
+      <c r="E41">
+        <v>-16.2306</v>
+      </c>
+      <c r="F41">
+        <v>12.2694</v>
+      </c>
+      <c r="G41">
+        <v>1.17</v>
+      </c>
+      <c r="H41">
+        <v>2.96</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>7.17</v>
+      </c>
+      <c r="K41">
+        <v>2.81</v>
+      </c>
+      <c r="L41">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M41">
+        <v>0.6502782000000001</v>
+      </c>
+      <c r="N41">
+        <v>3.709721799999999</v>
+      </c>
+      <c r="O41">
+        <v>0.3709721799999998</v>
+      </c>
+      <c r="P41">
+        <v>3.338749619999999</v>
+      </c>
+      <c r="Q41">
+        <v>6.148749619999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1375499973603031</v>
+      </c>
+      <c r="T41">
+        <v>1.138576370767835</v>
+      </c>
+      <c r="U41">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W41">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.704822643600844</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1025348162894833</v>
+      </c>
+      <c r="C42">
+        <v>53.52922620758677</v>
+      </c>
+      <c r="D42">
+        <v>64.94322620758678</v>
+      </c>
+      <c r="E42">
+        <v>-15.916</v>
+      </c>
+      <c r="F42">
+        <v>12.584</v>
+      </c>
+      <c r="G42">
+        <v>1.17</v>
+      </c>
+      <c r="H42">
+        <v>2.96</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>7.17</v>
+      </c>
+      <c r="K42">
+        <v>2.81</v>
+      </c>
+      <c r="L42">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M42">
+        <v>0.6669520000000001</v>
+      </c>
+      <c r="N42">
+        <v>3.693047999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.3693047999999998</v>
+      </c>
+      <c r="P42">
+        <v>3.3237432</v>
+      </c>
+      <c r="Q42">
+        <v>6.1337432</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1390913604824722</v>
+      </c>
+      <c r="T42">
+        <v>1.156348114328207</v>
+      </c>
+      <c r="U42">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W42">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>6.537202077510823</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1025611341891818</v>
+      </c>
+      <c r="C43">
+        <v>53.19508470339103</v>
+      </c>
+      <c r="D43">
+        <v>64.92368470339103</v>
+      </c>
+      <c r="E43">
+        <v>-15.6014</v>
+      </c>
+      <c r="F43">
+        <v>12.8986</v>
+      </c>
+      <c r="G43">
+        <v>1.17</v>
+      </c>
+      <c r="H43">
+        <v>2.96</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>7.17</v>
+      </c>
+      <c r="K43">
+        <v>2.81</v>
+      </c>
+      <c r="L43">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M43">
+        <v>0.6836258000000002</v>
+      </c>
+      <c r="N43">
+        <v>3.676374199999999</v>
+      </c>
+      <c r="O43">
+        <v>0.3676374199999998</v>
+      </c>
+      <c r="P43">
+        <v>3.308736779999999</v>
+      </c>
+      <c r="Q43">
+        <v>6.118736779999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.140684973202003</v>
+      </c>
+      <c r="T43">
+        <v>1.174722289873677</v>
+      </c>
+      <c r="U43">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W43">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>6.377758124400803</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1033434520888802</v>
+      </c>
+      <c r="C44">
+        <v>52.30492278378786</v>
+      </c>
+      <c r="D44">
+        <v>64.34812278378786</v>
+      </c>
+      <c r="E44">
+        <v>-15.2868</v>
+      </c>
+      <c r="F44">
+        <v>13.2132</v>
+      </c>
+      <c r="G44">
+        <v>1.17</v>
+      </c>
+      <c r="H44">
+        <v>2.96</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>7.17</v>
+      </c>
+      <c r="K44">
+        <v>2.81</v>
+      </c>
+      <c r="L44">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M44">
+        <v>0.726726</v>
+      </c>
+      <c r="N44">
+        <v>3.633273999999999</v>
+      </c>
+      <c r="O44">
+        <v>0.3633273999999999</v>
+      </c>
+      <c r="P44">
+        <v>3.269946599999999</v>
+      </c>
+      <c r="Q44">
+        <v>6.0799466</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1423335380842763</v>
+      </c>
+      <c r="T44">
+        <v>1.193730057679334</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W44">
+        <v>0.0495</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.999510131741536</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1033877699885787</v>
+      </c>
+      <c r="C45">
+        <v>51.95802277612864</v>
+      </c>
+      <c r="D45">
+        <v>64.31582277612864</v>
+      </c>
+      <c r="E45">
+        <v>-14.9722</v>
+      </c>
+      <c r="F45">
+        <v>13.5278</v>
+      </c>
+      <c r="G45">
+        <v>1.17</v>
+      </c>
+      <c r="H45">
+        <v>2.96</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>7.17</v>
+      </c>
+      <c r="K45">
+        <v>2.81</v>
+      </c>
+      <c r="L45">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M45">
+        <v>0.7440290000000001</v>
+      </c>
+      <c r="N45">
+        <v>3.615970999999999</v>
+      </c>
+      <c r="O45">
+        <v>0.3615970999999998</v>
+      </c>
+      <c r="P45">
+        <v>3.254373899999999</v>
+      </c>
+      <c r="Q45">
+        <v>6.0643739</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1440399473483837</v>
+      </c>
+      <c r="T45">
+        <v>1.213404764706244</v>
+      </c>
+      <c r="U45">
+        <v>0.055</v>
+      </c>
+      <c r="V45">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W45">
+        <v>0.0495</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.859986640305686</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1034320878882772</v>
+      </c>
+      <c r="C46">
+        <v>51.61115517864782</v>
+      </c>
+      <c r="D46">
+        <v>64.28355517864782</v>
+      </c>
+      <c r="E46">
+        <v>-14.6576</v>
+      </c>
+      <c r="F46">
+        <v>13.8424</v>
+      </c>
+      <c r="G46">
+        <v>1.17</v>
+      </c>
+      <c r="H46">
+        <v>2.96</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>7.17</v>
+      </c>
+      <c r="K46">
+        <v>2.81</v>
+      </c>
+      <c r="L46">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M46">
+        <v>0.761332</v>
+      </c>
+      <c r="N46">
+        <v>3.598668</v>
+      </c>
+      <c r="O46">
+        <v>0.3598667999999999</v>
+      </c>
+      <c r="P46">
+        <v>3.2388012</v>
+      </c>
+      <c r="Q46">
+        <v>6.0488012</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1458072998004949</v>
+      </c>
+      <c r="T46">
+        <v>1.233782139841257</v>
+      </c>
+      <c r="U46">
+        <v>0.055</v>
+      </c>
+      <c r="V46">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W46">
+        <v>0.0495</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.726805125753284</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1034764057879756</v>
+      </c>
+      <c r="C47">
+        <v>51.26431994258883</v>
+      </c>
+      <c r="D47">
+        <v>64.25131994258882</v>
+      </c>
+      <c r="E47">
+        <v>-14.343</v>
+      </c>
+      <c r="F47">
+        <v>14.157</v>
+      </c>
+      <c r="G47">
+        <v>1.17</v>
+      </c>
+      <c r="H47">
+        <v>2.96</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>7.17</v>
+      </c>
+      <c r="K47">
+        <v>2.81</v>
+      </c>
+      <c r="L47">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M47">
+        <v>0.778635</v>
+      </c>
+      <c r="N47">
+        <v>3.581364999999999</v>
+      </c>
+      <c r="O47">
+        <v>0.3581364999999999</v>
+      </c>
+      <c r="P47">
+        <v>3.223228499999999</v>
+      </c>
+      <c r="Q47">
+        <v>6.0332285</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1476389196145011</v>
+      </c>
+      <c r="T47">
+        <v>1.254900510435725</v>
+      </c>
+      <c r="U47">
+        <v>0.055</v>
+      </c>
+      <c r="V47">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W47">
+        <v>0.0495</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.599542789625434</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1035207236876741</v>
+      </c>
+      <c r="C48">
+        <v>50.91751701929274</v>
+      </c>
+      <c r="D48">
+        <v>64.21911701929274</v>
+      </c>
+      <c r="E48">
+        <v>-14.0284</v>
+      </c>
+      <c r="F48">
+        <v>14.4716</v>
+      </c>
+      <c r="G48">
+        <v>1.17</v>
+      </c>
+      <c r="H48">
+        <v>2.96</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>7.17</v>
+      </c>
+      <c r="K48">
+        <v>2.81</v>
+      </c>
+      <c r="L48">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M48">
+        <v>0.795938</v>
+      </c>
+      <c r="N48">
+        <v>3.564061999999999</v>
+      </c>
+      <c r="O48">
+        <v>0.3564061999999998</v>
+      </c>
+      <c r="P48">
+        <v>3.2076558</v>
+      </c>
+      <c r="Q48">
+        <v>6.0176558</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1495383771993964</v>
+      </c>
+      <c r="T48">
+        <v>1.276801042904062</v>
+      </c>
+      <c r="U48">
+        <v>0.055</v>
+      </c>
+      <c r="V48">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W48">
+        <v>0.0495</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.47781359854662</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1035650415873725</v>
+      </c>
+      <c r="C49">
+        <v>50.57074636019819</v>
+      </c>
+      <c r="D49">
+        <v>64.18694636019819</v>
+      </c>
+      <c r="E49">
+        <v>-13.7138</v>
+      </c>
+      <c r="F49">
+        <v>14.7862</v>
+      </c>
+      <c r="G49">
+        <v>1.17</v>
+      </c>
+      <c r="H49">
+        <v>2.96</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>7.17</v>
+      </c>
+      <c r="K49">
+        <v>2.81</v>
+      </c>
+      <c r="L49">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M49">
+        <v>0.8132410000000001</v>
+      </c>
+      <c r="N49">
+        <v>3.546758999999999</v>
+      </c>
+      <c r="O49">
+        <v>0.3546758999999999</v>
+      </c>
+      <c r="P49">
+        <v>3.1920831</v>
+      </c>
+      <c r="Q49">
+        <v>6.0020831</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1515095124290048</v>
+      </c>
+      <c r="T49">
+        <v>1.299528010559884</v>
+      </c>
+      <c r="U49">
+        <v>0.055</v>
+      </c>
+      <c r="V49">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W49">
+        <v>0.0495</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.361264373045628</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.103609359487071</v>
+      </c>
+      <c r="C50">
+        <v>50.22400791684108</v>
+      </c>
+      <c r="D50">
+        <v>64.15480791684108</v>
+      </c>
+      <c r="E50">
+        <v>-13.3992</v>
+      </c>
+      <c r="F50">
+        <v>15.1008</v>
+      </c>
+      <c r="G50">
+        <v>1.17</v>
+      </c>
+      <c r="H50">
+        <v>2.96</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>7.17</v>
+      </c>
+      <c r="K50">
+        <v>2.81</v>
+      </c>
+      <c r="L50">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M50">
+        <v>0.8305439999999999</v>
+      </c>
+      <c r="N50">
+        <v>3.529456</v>
+      </c>
+      <c r="O50">
+        <v>0.3529455999999999</v>
+      </c>
+      <c r="P50">
+        <v>3.1765104</v>
+      </c>
+      <c r="Q50">
+        <v>5.9865104</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1535564605520596</v>
+      </c>
+      <c r="T50">
+        <v>1.323129092356314</v>
+      </c>
+      <c r="U50">
+        <v>0.055</v>
+      </c>
+      <c r="V50">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W50">
+        <v>0.0495</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.249571365273844</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1036536773867694</v>
+      </c>
+      <c r="C51">
+        <v>49.87730164085431</v>
+      </c>
+      <c r="D51">
+        <v>64.1227016408543</v>
+      </c>
+      <c r="E51">
+        <v>-13.0846</v>
+      </c>
+      <c r="F51">
+        <v>15.4154</v>
+      </c>
+      <c r="G51">
+        <v>1.17</v>
+      </c>
+      <c r="H51">
+        <v>2.96</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>7.17</v>
+      </c>
+      <c r="K51">
+        <v>2.81</v>
+      </c>
+      <c r="L51">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M51">
+        <v>0.847847</v>
+      </c>
+      <c r="N51">
+        <v>3.512153</v>
+      </c>
+      <c r="O51">
+        <v>0.3512152999999999</v>
+      </c>
+      <c r="P51">
+        <v>3.1609377</v>
+      </c>
+      <c r="Q51">
+        <v>5.9709377</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1556836811505283</v>
+      </c>
+      <c r="T51">
+        <v>1.347655706772212</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W51">
+        <v>0.0495</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.14243725577846</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1036979952864679</v>
+      </c>
+      <c r="C52">
+        <v>49.53062748396748</v>
+      </c>
+      <c r="D52">
+        <v>64.09062748396748</v>
+      </c>
+      <c r="E52">
+        <v>-12.77</v>
+      </c>
+      <c r="F52">
+        <v>15.73</v>
+      </c>
+      <c r="G52">
+        <v>1.17</v>
+      </c>
+      <c r="H52">
+        <v>2.96</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>7.17</v>
+      </c>
+      <c r="K52">
+        <v>2.81</v>
+      </c>
+      <c r="L52">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M52">
+        <v>0.86515</v>
+      </c>
+      <c r="N52">
+        <v>3.49485</v>
+      </c>
+      <c r="O52">
+        <v>0.3494849999999999</v>
+      </c>
+      <c r="P52">
+        <v>3.145365</v>
+      </c>
+      <c r="Q52">
+        <v>5.955365</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1578959905729358</v>
+      </c>
+      <c r="T52">
+        <v>1.373163385764746</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W52">
+        <v>0.0495</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>5.039588510662891</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1037423131861663</v>
+      </c>
+      <c r="C53">
+        <v>49.1839853980069</v>
+      </c>
+      <c r="D53">
+        <v>64.0585853980069</v>
+      </c>
+      <c r="E53">
+        <v>-12.4554</v>
+      </c>
+      <c r="F53">
+        <v>16.0446</v>
+      </c>
+      <c r="G53">
+        <v>1.17</v>
+      </c>
+      <c r="H53">
+        <v>2.96</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>7.17</v>
+      </c>
+      <c r="K53">
+        <v>2.81</v>
+      </c>
+      <c r="L53">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M53">
+        <v>0.8824529999999999</v>
+      </c>
+      <c r="N53">
+        <v>3.477546999999999</v>
+      </c>
+      <c r="O53">
+        <v>0.3477546999999999</v>
+      </c>
+      <c r="P53">
+        <v>3.1297923</v>
+      </c>
+      <c r="Q53">
+        <v>5.9397923</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.160198598339115</v>
+      </c>
+      <c r="T53">
+        <v>1.399712194512077</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W53">
+        <v>0.0495</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.940773049669501</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1037866310858648</v>
+      </c>
+      <c r="C54">
+        <v>48.837375334895</v>
+      </c>
+      <c r="D54">
+        <v>64.026575334895</v>
+      </c>
+      <c r="E54">
+        <v>-12.1408</v>
+      </c>
+      <c r="F54">
+        <v>16.3592</v>
+      </c>
+      <c r="G54">
+        <v>1.17</v>
+      </c>
+      <c r="H54">
+        <v>2.96</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>7.17</v>
+      </c>
+      <c r="K54">
+        <v>2.81</v>
+      </c>
+      <c r="L54">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M54">
+        <v>0.8997560000000001</v>
+      </c>
+      <c r="N54">
+        <v>3.460243999999999</v>
+      </c>
+      <c r="O54">
+        <v>0.3460243999999998</v>
+      </c>
+      <c r="P54">
+        <v>3.1142196</v>
+      </c>
+      <c r="Q54">
+        <v>5.9242196</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1625971480955517</v>
+      </c>
+      <c r="T54">
+        <v>1.427367203623881</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W54">
+        <v>0.0495</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.845758183329702</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1038309489855632</v>
+      </c>
+      <c r="C55">
+        <v>48.49079724665035</v>
+      </c>
+      <c r="D55">
+        <v>63.99459724665035</v>
+      </c>
+      <c r="E55">
+        <v>-11.8262</v>
+      </c>
+      <c r="F55">
+        <v>16.6738</v>
+      </c>
+      <c r="G55">
+        <v>1.17</v>
+      </c>
+      <c r="H55">
+        <v>2.96</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>7.17</v>
+      </c>
+      <c r="K55">
+        <v>2.81</v>
+      </c>
+      <c r="L55">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M55">
+        <v>0.917059</v>
+      </c>
+      <c r="N55">
+        <v>3.442940999999999</v>
+      </c>
+      <c r="O55">
+        <v>0.3442940999999999</v>
+      </c>
+      <c r="P55">
+        <v>3.098646899999999</v>
+      </c>
+      <c r="Q55">
+        <v>5.908646899999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1650977637990707</v>
+      </c>
+      <c r="T55">
+        <v>1.456199021634059</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W55">
+        <v>0.0495</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.754328783644237</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1038752668852617</v>
+      </c>
+      <c r="C56">
+        <v>48.14425108538724</v>
+      </c>
+      <c r="D56">
+        <v>63.96265108538724</v>
+      </c>
+      <c r="E56">
+        <v>-11.5116</v>
+      </c>
+      <c r="F56">
+        <v>16.9884</v>
+      </c>
+      <c r="G56">
+        <v>1.17</v>
+      </c>
+      <c r="H56">
+        <v>2.96</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>7.17</v>
+      </c>
+      <c r="K56">
+        <v>2.81</v>
+      </c>
+      <c r="L56">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M56">
+        <v>0.9343620000000001</v>
+      </c>
+      <c r="N56">
+        <v>3.425637999999999</v>
+      </c>
+      <c r="O56">
+        <v>0.3425637999999999</v>
+      </c>
+      <c r="P56">
+        <v>3.0830742</v>
+      </c>
+      <c r="Q56">
+        <v>5.893074199999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.167707101924482</v>
+      </c>
+      <c r="T56">
+        <v>1.486284396949027</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W56">
+        <v>0.0495</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.666285658021193</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1039195847849602</v>
+      </c>
+      <c r="C57">
+        <v>47.79773680331569</v>
+      </c>
+      <c r="D57">
+        <v>63.93073680331568</v>
+      </c>
+      <c r="E57">
+        <v>-11.197</v>
+      </c>
+      <c r="F57">
+        <v>17.303</v>
+      </c>
+      <c r="G57">
+        <v>1.17</v>
+      </c>
+      <c r="H57">
+        <v>2.96</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>7.17</v>
+      </c>
+      <c r="K57">
+        <v>2.81</v>
+      </c>
+      <c r="L57">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M57">
+        <v>0.9516650000000001</v>
+      </c>
+      <c r="N57">
+        <v>3.408334999999999</v>
+      </c>
+      <c r="O57">
+        <v>0.3408334999999998</v>
+      </c>
+      <c r="P57">
+        <v>3.067501499999999</v>
+      </c>
+      <c r="Q57">
+        <v>5.877501499999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1704324106332448</v>
+      </c>
+      <c r="T57">
+        <v>1.517706900055772</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W57">
+        <v>0.0495</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.581444100602627</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1058791026846586</v>
+      </c>
+      <c r="C58">
+        <v>46.10319266596083</v>
+      </c>
+      <c r="D58">
+        <v>62.55079266596083</v>
+      </c>
+      <c r="E58">
+        <v>-10.8824</v>
+      </c>
+      <c r="F58">
+        <v>17.6176</v>
+      </c>
+      <c r="G58">
+        <v>1.17</v>
+      </c>
+      <c r="H58">
+        <v>2.96</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>7.17</v>
+      </c>
+      <c r="K58">
+        <v>2.81</v>
+      </c>
+      <c r="L58">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M58">
+        <v>1.03591488</v>
+      </c>
+      <c r="N58">
+        <v>3.324085119999999</v>
+      </c>
+      <c r="O58">
+        <v>0.3324085119999999</v>
+      </c>
+      <c r="P58">
+        <v>2.991676608</v>
+      </c>
+      <c r="Q58">
+        <v>5.801676607999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1732815970105878</v>
+      </c>
+      <c r="T58">
+        <v>1.550557698758278</v>
+      </c>
+      <c r="U58">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W58">
+        <v>0.05292000000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.208840015890107</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1059576205843571</v>
+      </c>
+      <c r="C59">
+        <v>45.73453857239703</v>
+      </c>
+      <c r="D59">
+        <v>62.49673857239703</v>
+      </c>
+      <c r="E59">
+        <v>-10.5678</v>
+      </c>
+      <c r="F59">
+        <v>17.9322</v>
+      </c>
+      <c r="G59">
+        <v>1.17</v>
+      </c>
+      <c r="H59">
+        <v>2.96</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>7.17</v>
+      </c>
+      <c r="K59">
+        <v>2.81</v>
+      </c>
+      <c r="L59">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M59">
+        <v>1.05441336</v>
+      </c>
+      <c r="N59">
+        <v>3.305586639999999</v>
+      </c>
+      <c r="O59">
+        <v>0.3305586639999998</v>
+      </c>
+      <c r="P59">
+        <v>2.975027975999999</v>
+      </c>
+      <c r="Q59">
+        <v>5.785027975999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1762633036845513</v>
+      </c>
+      <c r="T59">
+        <v>1.584936441586482</v>
+      </c>
+      <c r="U59">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W59">
+        <v>0.05292000000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.135000717365719</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1060361384840555</v>
+      </c>
+      <c r="C60">
+        <v>45.36597782128776</v>
+      </c>
+      <c r="D60">
+        <v>62.44277782128776</v>
+      </c>
+      <c r="E60">
+        <v>-10.2532</v>
+      </c>
+      <c r="F60">
+        <v>18.2468</v>
+      </c>
+      <c r="G60">
+        <v>1.17</v>
+      </c>
+      <c r="H60">
+        <v>2.96</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>7.17</v>
+      </c>
+      <c r="K60">
+        <v>2.81</v>
+      </c>
+      <c r="L60">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M60">
+        <v>1.07291184</v>
+      </c>
+      <c r="N60">
+        <v>3.287088159999999</v>
+      </c>
+      <c r="O60">
+        <v>0.3287088159999998</v>
+      </c>
+      <c r="P60">
+        <v>2.958379343999999</v>
+      </c>
+      <c r="Q60">
+        <v>5.768379344</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1793869963906084</v>
+      </c>
+      <c r="T60">
+        <v>1.620952267406505</v>
+      </c>
+      <c r="U60">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W60">
+        <v>0.05292000000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>4.063707601549069</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.108344856383754</v>
+      </c>
+      <c r="C61">
+        <v>43.50535125422635</v>
+      </c>
+      <c r="D61">
+        <v>60.89675125422634</v>
+      </c>
+      <c r="E61">
+        <v>-9.938600000000001</v>
+      </c>
+      <c r="F61">
+        <v>18.5614</v>
+      </c>
+      <c r="G61">
+        <v>1.17</v>
+      </c>
+      <c r="H61">
+        <v>2.96</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>7.17</v>
+      </c>
+      <c r="K61">
+        <v>2.81</v>
+      </c>
+      <c r="L61">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M61">
+        <v>1.1693682</v>
+      </c>
+      <c r="N61">
+        <v>3.190631799999999</v>
+      </c>
+      <c r="O61">
+        <v>0.3190631799999999</v>
+      </c>
+      <c r="P61">
+        <v>2.87156862</v>
+      </c>
+      <c r="Q61">
+        <v>5.68156862</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1826630643506194</v>
+      </c>
+      <c r="T61">
+        <v>1.658724962778724</v>
+      </c>
+      <c r="U61">
+        <v>0.063</v>
+      </c>
+      <c r="V61">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W61">
+        <v>0.0567</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.728509121421294</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1084611742834524</v>
+      </c>
+      <c r="C62">
+        <v>43.1148824679165</v>
+      </c>
+      <c r="D62">
+        <v>60.8208824679165</v>
+      </c>
+      <c r="E62">
+        <v>-9.623999999999999</v>
+      </c>
+      <c r="F62">
+        <v>18.876</v>
+      </c>
+      <c r="G62">
+        <v>1.17</v>
+      </c>
+      <c r="H62">
+        <v>2.96</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>7.17</v>
+      </c>
+      <c r="K62">
+        <v>2.81</v>
+      </c>
+      <c r="L62">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M62">
+        <v>1.189188</v>
+      </c>
+      <c r="N62">
+        <v>3.170811999999999</v>
+      </c>
+      <c r="O62">
+        <v>0.3170811999999998</v>
+      </c>
+      <c r="P62">
+        <v>2.853730799999999</v>
+      </c>
+      <c r="Q62">
+        <v>5.6637308</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1861029357086311</v>
+      </c>
+      <c r="T62">
+        <v>1.698386292919554</v>
+      </c>
+      <c r="U62">
+        <v>0.063</v>
+      </c>
+      <c r="V62">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W62">
+        <v>0.0567</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.666367302730938</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1085774921831509</v>
+      </c>
+      <c r="C63">
+        <v>42.7246024900499</v>
+      </c>
+      <c r="D63">
+        <v>60.74520249004991</v>
+      </c>
+      <c r="E63">
+        <v>-9.3094</v>
+      </c>
+      <c r="F63">
+        <v>19.1906</v>
+      </c>
+      <c r="G63">
+        <v>1.17</v>
+      </c>
+      <c r="H63">
+        <v>2.96</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>7.17</v>
+      </c>
+      <c r="K63">
+        <v>2.81</v>
+      </c>
+      <c r="L63">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M63">
+        <v>1.2090078</v>
+      </c>
+      <c r="N63">
+        <v>3.150992199999999</v>
+      </c>
+      <c r="O63">
+        <v>0.3150992199999998</v>
+      </c>
+      <c r="P63">
+        <v>2.835892979999999</v>
+      </c>
+      <c r="Q63">
+        <v>5.645892979999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1897192107260279</v>
+      </c>
+      <c r="T63">
+        <v>1.740081537426581</v>
+      </c>
+      <c r="U63">
+        <v>0.063</v>
+      </c>
+      <c r="V63">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W63">
+        <v>0.0567</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.606262920718956</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1086938100828493</v>
+      </c>
+      <c r="C64">
+        <v>42.33451061669435</v>
+      </c>
+      <c r="D64">
+        <v>60.66971061669435</v>
+      </c>
+      <c r="E64">
+        <v>-8.994799999999998</v>
+      </c>
+      <c r="F64">
+        <v>19.5052</v>
+      </c>
+      <c r="G64">
+        <v>1.17</v>
+      </c>
+      <c r="H64">
+        <v>2.96</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>7.17</v>
+      </c>
+      <c r="K64">
+        <v>2.81</v>
+      </c>
+      <c r="L64">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M64">
+        <v>1.2288276</v>
+      </c>
+      <c r="N64">
+        <v>3.131172399999999</v>
+      </c>
+      <c r="O64">
+        <v>0.3131172399999999</v>
+      </c>
+      <c r="P64">
+        <v>2.818055159999999</v>
+      </c>
+      <c r="Q64">
+        <v>5.628055159999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1935258160074983</v>
+      </c>
+      <c r="T64">
+        <v>1.783971268486609</v>
+      </c>
+      <c r="U64">
+        <v>0.063</v>
+      </c>
+      <c r="V64">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W64">
+        <v>0.0567</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.548097389739617</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1128358279825478</v>
+      </c>
+      <c r="C65">
+        <v>39.44880825512763</v>
+      </c>
+      <c r="D65">
+        <v>58.09860825512763</v>
+      </c>
+      <c r="E65">
+        <v>-8.680199999999999</v>
+      </c>
+      <c r="F65">
+        <v>19.8198</v>
+      </c>
+      <c r="G65">
+        <v>1.17</v>
+      </c>
+      <c r="H65">
+        <v>2.96</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>7.17</v>
+      </c>
+      <c r="K65">
+        <v>2.81</v>
+      </c>
+      <c r="L65">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M65">
+        <v>1.38936798</v>
+      </c>
+      <c r="N65">
+        <v>2.970632019999999</v>
+      </c>
+      <c r="O65">
+        <v>0.2970632019999999</v>
+      </c>
+      <c r="P65">
+        <v>2.673568817999999</v>
+      </c>
+      <c r="Q65">
+        <v>5.483568817999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1975381837366156</v>
+      </c>
+      <c r="T65">
+        <v>1.830233417441774</v>
+      </c>
+      <c r="U65">
+        <v>0.0701</v>
+      </c>
+      <c r="V65">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W65">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.138117520169134</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1130160458822462</v>
+      </c>
+      <c r="C66">
+        <v>39.02727837631859</v>
+      </c>
+      <c r="D66">
+        <v>57.99167837631859</v>
+      </c>
+      <c r="E66">
+        <v>-8.365600000000001</v>
+      </c>
+      <c r="F66">
+        <v>20.1344</v>
+      </c>
+      <c r="G66">
+        <v>1.17</v>
+      </c>
+      <c r="H66">
+        <v>2.96</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>7.17</v>
+      </c>
+      <c r="K66">
+        <v>2.81</v>
+      </c>
+      <c r="L66">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M66">
+        <v>1.41142144</v>
+      </c>
+      <c r="N66">
+        <v>2.94857856</v>
+      </c>
+      <c r="O66">
+        <v>0.2948578559999999</v>
+      </c>
+      <c r="P66">
+        <v>2.653720703999999</v>
+      </c>
+      <c r="Q66">
+        <v>5.463720704</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2017734607840174</v>
+      </c>
+      <c r="T66">
+        <v>1.879065685783337</v>
+      </c>
+      <c r="U66">
+        <v>0.0701</v>
+      </c>
+      <c r="V66">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W66">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.089084433916492</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1131962637819447</v>
+      </c>
+      <c r="C67">
+        <v>38.60614138105117</v>
+      </c>
+      <c r="D67">
+        <v>57.88514138105118</v>
+      </c>
+      <c r="E67">
+        <v>-8.050999999999998</v>
+      </c>
+      <c r="F67">
+        <v>20.449</v>
+      </c>
+      <c r="G67">
+        <v>1.17</v>
+      </c>
+      <c r="H67">
+        <v>2.96</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>7.17</v>
+      </c>
+      <c r="K67">
+        <v>2.81</v>
+      </c>
+      <c r="L67">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M67">
+        <v>1.4334749</v>
+      </c>
+      <c r="N67">
+        <v>2.926525099999999</v>
+      </c>
+      <c r="O67">
+        <v>0.2926525099999999</v>
+      </c>
+      <c r="P67">
+        <v>2.633872589999999</v>
+      </c>
+      <c r="Q67">
+        <v>5.44387259</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2062507536626992</v>
+      </c>
+      <c r="T67">
+        <v>1.930688369458703</v>
+      </c>
+      <c r="U67">
+        <v>0.0701</v>
+      </c>
+      <c r="V67">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W67">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>3.041560058010084</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1260286816816432</v>
+      </c>
+      <c r="C68">
+        <v>31.59543590102712</v>
+      </c>
+      <c r="D68">
+        <v>51.18903590102712</v>
+      </c>
+      <c r="E68">
+        <v>-7.7364</v>
+      </c>
+      <c r="F68">
+        <v>20.7636</v>
+      </c>
+      <c r="G68">
+        <v>1.17</v>
+      </c>
+      <c r="H68">
+        <v>2.96</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>7.17</v>
+      </c>
+      <c r="K68">
+        <v>2.81</v>
+      </c>
+      <c r="L68">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M68">
+        <v>1.89779304</v>
+      </c>
+      <c r="N68">
+        <v>2.462206959999999</v>
+      </c>
+      <c r="O68">
+        <v>0.2462206959999999</v>
+      </c>
+      <c r="P68">
+        <v>2.215986263999999</v>
+      </c>
+      <c r="Q68">
+        <v>5.025986263999999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2109914167107152</v>
+      </c>
+      <c r="T68">
+        <v>1.985347681585562</v>
+      </c>
+      <c r="U68">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W68">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.2974054114984</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1264005995813416</v>
+      </c>
+      <c r="C69">
+        <v>31.10978825427853</v>
+      </c>
+      <c r="D69">
+        <v>51.01798825427854</v>
+      </c>
+      <c r="E69">
+        <v>-7.421799999999998</v>
+      </c>
+      <c r="F69">
+        <v>21.0782</v>
+      </c>
+      <c r="G69">
+        <v>1.17</v>
+      </c>
+      <c r="H69">
+        <v>2.96</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>7.17</v>
+      </c>
+      <c r="K69">
+        <v>2.81</v>
+      </c>
+      <c r="L69">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M69">
+        <v>1.92654748</v>
+      </c>
+      <c r="N69">
+        <v>2.433452519999999</v>
+      </c>
+      <c r="O69">
+        <v>0.2433452519999998</v>
+      </c>
+      <c r="P69">
+        <v>2.190107267999999</v>
+      </c>
+      <c r="Q69">
+        <v>5.000107267999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2160193926707322</v>
+      </c>
+      <c r="T69">
+        <v>2.043319679295867</v>
+      </c>
+      <c r="U69">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W69">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.263115778490961</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1267725174810401</v>
+      </c>
+      <c r="C70">
+        <v>30.62527990853717</v>
+      </c>
+      <c r="D70">
+        <v>50.84807990853717</v>
+      </c>
+      <c r="E70">
+        <v>-7.107199999999999</v>
+      </c>
+      <c r="F70">
+        <v>21.3928</v>
+      </c>
+      <c r="G70">
+        <v>1.17</v>
+      </c>
+      <c r="H70">
+        <v>2.96</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>7.17</v>
+      </c>
+      <c r="K70">
+        <v>2.81</v>
+      </c>
+      <c r="L70">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M70">
+        <v>1.95530192</v>
+      </c>
+      <c r="N70">
+        <v>2.404698079999999</v>
+      </c>
+      <c r="O70">
+        <v>0.2404698079999999</v>
+      </c>
+      <c r="P70">
+        <v>2.164228271999999</v>
+      </c>
+      <c r="Q70">
+        <v>4.974228272</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2213616171282503</v>
+      </c>
+      <c r="T70">
+        <v>2.104914926863065</v>
+      </c>
+      <c r="U70">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W70">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.229834664101388</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1271444353807386</v>
+      </c>
+      <c r="C71">
+        <v>30.14189951873344</v>
+      </c>
+      <c r="D71">
+        <v>50.67929951873344</v>
+      </c>
+      <c r="E71">
+        <v>-6.792599999999997</v>
+      </c>
+      <c r="F71">
+        <v>21.7074</v>
+      </c>
+      <c r="G71">
+        <v>1.17</v>
+      </c>
+      <c r="H71">
+        <v>2.96</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>7.17</v>
+      </c>
+      <c r="K71">
+        <v>2.81</v>
+      </c>
+      <c r="L71">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M71">
+        <v>1.984056360000001</v>
+      </c>
+      <c r="N71">
+        <v>2.375943639999999</v>
+      </c>
+      <c r="O71">
+        <v>0.2375943639999999</v>
+      </c>
+      <c r="P71">
+        <v>2.138349275999999</v>
+      </c>
+      <c r="Q71">
+        <v>4.948349275999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2270485012281888</v>
+      </c>
+      <c r="T71">
+        <v>2.170484061370083</v>
+      </c>
+      <c r="U71">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W71">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.197518219694121</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.127516353280437</v>
+      </c>
+      <c r="C72">
+        <v>29.65963588993053</v>
+      </c>
+      <c r="D72">
+        <v>50.51163588993053</v>
+      </c>
+      <c r="E72">
+        <v>-6.477999999999998</v>
+      </c>
+      <c r="F72">
+        <v>22.022</v>
+      </c>
+      <c r="G72">
+        <v>1.17</v>
+      </c>
+      <c r="H72">
+        <v>2.96</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>7.17</v>
+      </c>
+      <c r="K72">
+        <v>2.81</v>
+      </c>
+      <c r="L72">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M72">
+        <v>2.0128108</v>
+      </c>
+      <c r="N72">
+        <v>2.347189199999999</v>
+      </c>
+      <c r="O72">
+        <v>0.2347189199999999</v>
+      </c>
+      <c r="P72">
+        <v>2.112470279999999</v>
+      </c>
+      <c r="Q72">
+        <v>4.922470279999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.23311451093479</v>
+      </c>
+      <c r="T72">
+        <v>2.240424471510902</v>
+      </c>
+      <c r="U72">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W72">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.16612510226992</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1278882711801355</v>
+      </c>
+      <c r="C73">
+        <v>29.17847797484906</v>
+      </c>
+      <c r="D73">
+        <v>50.34507797484905</v>
+      </c>
+      <c r="E73">
+        <v>-6.163399999999999</v>
+      </c>
+      <c r="F73">
+        <v>22.3366</v>
+      </c>
+      <c r="G73">
+        <v>1.17</v>
+      </c>
+      <c r="H73">
+        <v>2.96</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>7.17</v>
+      </c>
+      <c r="K73">
+        <v>2.81</v>
+      </c>
+      <c r="L73">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M73">
+        <v>2.04156524</v>
+      </c>
+      <c r="N73">
+        <v>2.318434759999999</v>
+      </c>
+      <c r="O73">
+        <v>0.2318434759999999</v>
+      </c>
+      <c r="P73">
+        <v>2.086591283999999</v>
+      </c>
+      <c r="Q73">
+        <v>4.896591283999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.239598866138398</v>
+      </c>
+      <c r="T73">
+        <v>2.315188358213156</v>
+      </c>
+      <c r="U73">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W73">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.135616298012597</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1282601890798339</v>
+      </c>
+      <c r="C74">
+        <v>28.69841487144076</v>
+      </c>
+      <c r="D74">
+        <v>50.17961487144076</v>
+      </c>
+      <c r="E74">
+        <v>-5.848800000000001</v>
+      </c>
+      <c r="F74">
+        <v>22.6512</v>
+      </c>
+      <c r="G74">
+        <v>1.17</v>
+      </c>
+      <c r="H74">
+        <v>2.96</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>7.17</v>
+      </c>
+      <c r="K74">
+        <v>2.81</v>
+      </c>
+      <c r="L74">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M74">
+        <v>2.07031968</v>
+      </c>
+      <c r="N74">
+        <v>2.289680319999999</v>
+      </c>
+      <c r="O74">
+        <v>0.2289680319999998</v>
+      </c>
+      <c r="P74">
+        <v>2.060712287999999</v>
+      </c>
+      <c r="Q74">
+        <v>4.870712287999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2465463895708353</v>
+      </c>
+      <c r="T74">
+        <v>2.395292522537</v>
+      </c>
+      <c r="U74">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W74">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.1059549605402</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1286321069795323</v>
+      </c>
+      <c r="C75">
+        <v>28.21943582050963</v>
+      </c>
+      <c r="D75">
+        <v>50.01523582050963</v>
+      </c>
+      <c r="E75">
+        <v>-5.534199999999998</v>
+      </c>
+      <c r="F75">
+        <v>22.9658</v>
+      </c>
+      <c r="G75">
+        <v>1.17</v>
+      </c>
+      <c r="H75">
+        <v>2.96</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>7.17</v>
+      </c>
+      <c r="K75">
+        <v>2.81</v>
+      </c>
+      <c r="L75">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M75">
+        <v>2.09907412</v>
+      </c>
+      <c r="N75">
+        <v>2.260925879999999</v>
+      </c>
+      <c r="O75">
+        <v>0.2260925879999998</v>
+      </c>
+      <c r="P75">
+        <v>2.034833291999999</v>
+      </c>
+      <c r="Q75">
+        <v>4.844833291999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2540085443686383</v>
+      </c>
+      <c r="T75">
+        <v>2.481330328662611</v>
+      </c>
+      <c r="U75">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W75">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.077106262450608</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1290040248792308</v>
+      </c>
+      <c r="C76">
+        <v>27.74153020337983</v>
+      </c>
+      <c r="D76">
+        <v>49.85193020337983</v>
+      </c>
+      <c r="E76">
+        <v>-5.2196</v>
+      </c>
+      <c r="F76">
+        <v>23.2804</v>
+      </c>
+      <c r="G76">
+        <v>1.17</v>
+      </c>
+      <c r="H76">
+        <v>2.96</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>7.17</v>
+      </c>
+      <c r="K76">
+        <v>2.81</v>
+      </c>
+      <c r="L76">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M76">
+        <v>2.12782856</v>
+      </c>
+      <c r="N76">
+        <v>2.232171439999999</v>
+      </c>
+      <c r="O76">
+        <v>0.2232171439999999</v>
+      </c>
+      <c r="P76">
+        <v>2.008954295999999</v>
+      </c>
+      <c r="Q76">
+        <v>4.818954295999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2620447110739646</v>
+      </c>
+      <c r="T76">
+        <v>2.573986427567115</v>
+      </c>
+      <c r="U76">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W76">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.049037258903978</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1293759427789293</v>
+      </c>
+      <c r="C77">
+        <v>27.26468753960904</v>
+      </c>
+      <c r="D77">
+        <v>49.68968753960904</v>
+      </c>
+      <c r="E77">
+        <v>-4.905000000000001</v>
+      </c>
+      <c r="F77">
+        <v>23.595</v>
+      </c>
+      <c r="G77">
+        <v>1.17</v>
+      </c>
+      <c r="H77">
+        <v>2.96</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>7.17</v>
+      </c>
+      <c r="K77">
+        <v>2.81</v>
+      </c>
+      <c r="L77">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M77">
+        <v>2.156583</v>
+      </c>
+      <c r="N77">
+        <v>2.203417</v>
+      </c>
+      <c r="O77">
+        <v>0.2203416999999999</v>
+      </c>
+      <c r="P77">
+        <v>1.9830753</v>
+      </c>
+      <c r="Q77">
+        <v>4.7930753</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.270723771115717</v>
+      </c>
+      <c r="T77">
+        <v>2.674055014383979</v>
+      </c>
+      <c r="U77">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W77">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.021716762118592</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1441802606786277</v>
+      </c>
+      <c r="C78">
+        <v>21.25124432293113</v>
+      </c>
+      <c r="D78">
+        <v>43.99084432293113</v>
+      </c>
+      <c r="E78">
+        <v>-4.590399999999999</v>
+      </c>
+      <c r="F78">
+        <v>23.9096</v>
+      </c>
+      <c r="G78">
+        <v>1.17</v>
+      </c>
+      <c r="H78">
+        <v>2.96</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>7.17</v>
+      </c>
+      <c r="K78">
+        <v>2.81</v>
+      </c>
+      <c r="L78">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M78">
+        <v>2.68983</v>
+      </c>
+      <c r="N78">
+        <v>1.670169999999999</v>
+      </c>
+      <c r="O78">
+        <v>0.1670169999999999</v>
+      </c>
+      <c r="P78">
+        <v>1.503152999999999</v>
+      </c>
+      <c r="Q78">
+        <v>4.313153</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2801260861609488</v>
+      </c>
+      <c r="T78">
+        <v>2.782462650102249</v>
+      </c>
+      <c r="U78">
+        <v>0.1125</v>
+      </c>
+      <c r="V78">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W78">
+        <v>0.10125</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>1.620920281207362</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1447420785783262</v>
+      </c>
+      <c r="C79">
+        <v>20.74600881592574</v>
+      </c>
+      <c r="D79">
+        <v>43.80020881592574</v>
+      </c>
+      <c r="E79">
+        <v>-4.2758</v>
+      </c>
+      <c r="F79">
+        <v>24.2242</v>
+      </c>
+      <c r="G79">
+        <v>1.17</v>
+      </c>
+      <c r="H79">
+        <v>2.96</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>7.17</v>
+      </c>
+      <c r="K79">
+        <v>2.81</v>
+      </c>
+      <c r="L79">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M79">
+        <v>2.7252225</v>
+      </c>
+      <c r="N79">
+        <v>1.634777499999999</v>
+      </c>
+      <c r="O79">
+        <v>0.1634777499999999</v>
+      </c>
+      <c r="P79">
+        <v>1.471299749999999</v>
+      </c>
+      <c r="Q79">
+        <v>4.28129975</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2903459938188094</v>
+      </c>
+      <c r="T79">
+        <v>2.900297036752542</v>
+      </c>
+      <c r="U79">
+        <v>0.1125</v>
+      </c>
+      <c r="V79">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W79">
+        <v>0.10125</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>1.59986936846441</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1453038964780246</v>
+      </c>
+      <c r="C80">
+        <v>20.24241842794627</v>
+      </c>
+      <c r="D80">
+        <v>43.61121842794627</v>
+      </c>
+      <c r="E80">
+        <v>-3.961199999999998</v>
+      </c>
+      <c r="F80">
+        <v>24.5388</v>
+      </c>
+      <c r="G80">
+        <v>1.17</v>
+      </c>
+      <c r="H80">
+        <v>2.96</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>7.17</v>
+      </c>
+      <c r="K80">
+        <v>2.81</v>
+      </c>
+      <c r="L80">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M80">
+        <v>2.760615</v>
+      </c>
+      <c r="N80">
+        <v>1.599384999999999</v>
+      </c>
+      <c r="O80">
+        <v>0.1599384999999999</v>
+      </c>
+      <c r="P80">
+        <v>1.439446499999999</v>
+      </c>
+      <c r="Q80">
+        <v>4.249446499999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.301494983991021</v>
+      </c>
+      <c r="T80">
+        <v>3.028843640371043</v>
+      </c>
+      <c r="U80">
+        <v>0.1125</v>
+      </c>
+      <c r="V80">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W80">
+        <v>0.10125</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>1.579358222714866</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1458657143777231</v>
+      </c>
+      <c r="C81">
+        <v>19.74045195526398</v>
+      </c>
+      <c r="D81">
+        <v>43.42385195526398</v>
+      </c>
+      <c r="E81">
+        <v>-3.646599999999999</v>
+      </c>
+      <c r="F81">
+        <v>24.8534</v>
+      </c>
+      <c r="G81">
+        <v>1.17</v>
+      </c>
+      <c r="H81">
+        <v>2.96</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>7.17</v>
+      </c>
+      <c r="K81">
+        <v>2.81</v>
+      </c>
+      <c r="L81">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M81">
+        <v>2.7960075</v>
+      </c>
+      <c r="N81">
+        <v>1.563992499999999</v>
+      </c>
+      <c r="O81">
+        <v>0.1563992499999999</v>
+      </c>
+      <c r="P81">
+        <v>1.407593249999999</v>
+      </c>
+      <c r="Q81">
+        <v>4.217593249999999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3137057827510623</v>
+      </c>
+      <c r="T81">
+        <v>3.169632777667497</v>
+      </c>
+      <c r="U81">
+        <v>0.1125</v>
+      </c>
+      <c r="V81">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W81">
+        <v>0.10125</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.559366346477969</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1464275322774216</v>
+      </c>
+      <c r="C82">
+        <v>19.24008855698076</v>
+      </c>
+      <c r="D82">
+        <v>43.23808855698076</v>
+      </c>
+      <c r="E82">
+        <v>-3.331999999999997</v>
+      </c>
+      <c r="F82">
+        <v>25.168</v>
+      </c>
+      <c r="G82">
+        <v>1.17</v>
+      </c>
+      <c r="H82">
+        <v>2.96</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>7.17</v>
+      </c>
+      <c r="K82">
+        <v>2.81</v>
+      </c>
+      <c r="L82">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M82">
+        <v>2.8314</v>
+      </c>
+      <c r="N82">
+        <v>1.528599999999999</v>
+      </c>
+      <c r="O82">
+        <v>0.1528599999999999</v>
+      </c>
+      <c r="P82">
+        <v>1.375739999999999</v>
+      </c>
+      <c r="Q82">
+        <v>4.185739999999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3271376613871078</v>
+      </c>
+      <c r="T82">
+        <v>3.324500828693597</v>
+      </c>
+      <c r="U82">
+        <v>0.1125</v>
+      </c>
+      <c r="V82">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W82">
+        <v>0.10125</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>1.539874267146994</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.14698935017712</v>
+      </c>
+      <c r="C83">
+        <v>18.74130774730157</v>
+      </c>
+      <c r="D83">
+        <v>43.05390774730157</v>
+      </c>
+      <c r="E83">
+        <v>-3.017399999999999</v>
+      </c>
+      <c r="F83">
+        <v>25.4826</v>
+      </c>
+      <c r="G83">
+        <v>1.17</v>
+      </c>
+      <c r="H83">
+        <v>2.96</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>7.17</v>
+      </c>
+      <c r="K83">
+        <v>2.81</v>
+      </c>
+      <c r="L83">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M83">
+        <v>2.8667925</v>
+      </c>
+      <c r="N83">
+        <v>1.493207499999999</v>
+      </c>
+      <c r="O83">
+        <v>0.1493207499999999</v>
+      </c>
+      <c r="P83">
+        <v>1.343886749999999</v>
+      </c>
+      <c r="Q83">
+        <v>4.15388675</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3419834219848421</v>
+      </c>
+      <c r="T83">
+        <v>3.495670779827706</v>
+      </c>
+      <c r="U83">
+        <v>0.1125</v>
+      </c>
+      <c r="V83">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W83">
+        <v>0.10125</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>1.520863473725426</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1475511680768185</v>
+      </c>
+      <c r="C84">
+        <v>18.24408938800319</v>
+      </c>
+      <c r="D84">
+        <v>42.87128938800319</v>
+      </c>
+      <c r="E84">
+        <v>-2.702799999999996</v>
+      </c>
+      <c r="F84">
+        <v>25.7972</v>
+      </c>
+      <c r="G84">
+        <v>1.17</v>
+      </c>
+      <c r="H84">
+        <v>2.96</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>7.17</v>
+      </c>
+      <c r="K84">
+        <v>2.81</v>
+      </c>
+      <c r="L84">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M84">
+        <v>2.902185000000001</v>
+      </c>
+      <c r="N84">
+        <v>1.457814999999999</v>
+      </c>
+      <c r="O84">
+        <v>0.1457814999999998</v>
+      </c>
+      <c r="P84">
+        <v>1.312033499999999</v>
+      </c>
+      <c r="Q84">
+        <v>4.122033499999999</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3584787115378803</v>
+      </c>
+      <c r="T84">
+        <v>3.685859614421161</v>
+      </c>
+      <c r="U84">
+        <v>0.1125</v>
+      </c>
+      <c r="V84">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W84">
+        <v>0.10125</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>1.502316358192189</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2141786002625036</v>
+      </c>
+      <c r="C85">
+        <v>3.581542032663222</v>
+      </c>
+      <c r="D85">
+        <v>28.52334203266323</v>
+      </c>
+      <c r="E85">
+        <v>-2.388199999999998</v>
+      </c>
+      <c r="F85">
+        <v>26.1118</v>
+      </c>
+      <c r="G85">
+        <v>1.17</v>
+      </c>
+      <c r="H85">
+        <v>2.96</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>7.17</v>
+      </c>
+      <c r="K85">
+        <v>2.81</v>
+      </c>
+      <c r="L85">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M85">
+        <v>5.13357988</v>
+      </c>
+      <c r="N85">
+        <v>-0.7735798800000007</v>
+      </c>
+      <c r="O85">
+        <v>-0.07735798800000004</v>
+      </c>
+      <c r="P85">
+        <v>-0.6962218920000006</v>
+      </c>
+      <c r="Q85">
+        <v>2.113778108</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3815262862754502</v>
+      </c>
+      <c r="T85">
+        <v>3.951595560762073</v>
+      </c>
+      <c r="U85">
+        <v>0.1966</v>
+      </c>
+      <c r="V85">
+        <v>0.08493098582114589</v>
+      </c>
+      <c r="W85">
+        <v>0.1799025681875627</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.8493098582114591</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2157566002625035</v>
+      </c>
+      <c r="C86">
+        <v>3.042631982755907</v>
+      </c>
+      <c r="D86">
+        <v>28.29903198275591</v>
+      </c>
+      <c r="E86">
+        <v>-2.073599999999999</v>
+      </c>
+      <c r="F86">
+        <v>26.4264</v>
+      </c>
+      <c r="G86">
+        <v>1.17</v>
+      </c>
+      <c r="H86">
+        <v>2.96</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>7.17</v>
+      </c>
+      <c r="K86">
+        <v>2.81</v>
+      </c>
+      <c r="L86">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M86">
+        <v>5.19543024</v>
+      </c>
+      <c r="N86">
+        <v>-0.8354302400000009</v>
+      </c>
+      <c r="O86">
+        <v>-0.08354302400000006</v>
+      </c>
+      <c r="P86">
+        <v>-0.7518872160000009</v>
+      </c>
+      <c r="Q86">
+        <v>2.058112783999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4029466791676655</v>
+      </c>
+      <c r="T86">
+        <v>4.1985702833097</v>
+      </c>
+      <c r="U86">
+        <v>0.1966</v>
+      </c>
+      <c r="V86">
+        <v>0.08391990265660844</v>
+      </c>
+      <c r="W86">
+        <v>0.1801013471377108</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.8391990265660846</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2173346002625036</v>
+      </c>
+      <c r="C87">
+        <v>2.507222392527517</v>
+      </c>
+      <c r="D87">
+        <v>28.07822239252751</v>
+      </c>
+      <c r="E87">
+        <v>-1.759</v>
+      </c>
+      <c r="F87">
+        <v>26.741</v>
+      </c>
+      <c r="G87">
+        <v>1.17</v>
+      </c>
+      <c r="H87">
+        <v>2.96</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>7.17</v>
+      </c>
+      <c r="K87">
+        <v>2.81</v>
+      </c>
+      <c r="L87">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M87">
+        <v>5.2572806</v>
+      </c>
+      <c r="N87">
+        <v>-0.8972806000000002</v>
+      </c>
+      <c r="O87">
+        <v>-0.08972806</v>
+      </c>
+      <c r="P87">
+        <v>-0.8075525400000002</v>
+      </c>
+      <c r="Q87">
+        <v>2.00244746</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.42722312444551</v>
+      </c>
+      <c r="T87">
+        <v>4.478474968863681</v>
+      </c>
+      <c r="U87">
+        <v>0.1966</v>
+      </c>
+      <c r="V87">
+        <v>0.08293260968417776</v>
+      </c>
+      <c r="W87">
+        <v>0.1802954489360906</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.8293260968417778</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2189126002625035</v>
+      </c>
+      <c r="C88">
+        <v>1.975231956996179</v>
+      </c>
+      <c r="D88">
+        <v>27.86083195699618</v>
+      </c>
+      <c r="E88">
+        <v>-1.444399999999998</v>
+      </c>
+      <c r="F88">
+        <v>27.0556</v>
+      </c>
+      <c r="G88">
+        <v>1.17</v>
+      </c>
+      <c r="H88">
+        <v>2.96</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>7.17</v>
+      </c>
+      <c r="K88">
+        <v>2.81</v>
+      </c>
+      <c r="L88">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M88">
+        <v>5.31913096</v>
+      </c>
+      <c r="N88">
+        <v>-0.9591309600000004</v>
+      </c>
+      <c r="O88">
+        <v>-0.09591309600000002</v>
+      </c>
+      <c r="P88">
+        <v>-0.8632178640000004</v>
+      </c>
+      <c r="Q88">
+        <v>1.946782135999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4549676333344749</v>
+      </c>
+      <c r="T88">
+        <v>4.798366038068229</v>
+      </c>
+      <c r="U88">
+        <v>0.1966</v>
+      </c>
+      <c r="V88">
+        <v>0.0819682770134315</v>
+      </c>
+      <c r="W88">
+        <v>0.1804850367391594</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.8196827701343152</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2204906002625035</v>
+      </c>
+      <c r="C89">
+        <v>1.446581869790062</v>
+      </c>
+      <c r="D89">
+        <v>27.64678186979006</v>
+      </c>
+      <c r="E89">
+        <v>-1.129799999999999</v>
+      </c>
+      <c r="F89">
+        <v>27.3702</v>
+      </c>
+      <c r="G89">
+        <v>1.17</v>
+      </c>
+      <c r="H89">
+        <v>2.96</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>7.17</v>
+      </c>
+      <c r="K89">
+        <v>2.81</v>
+      </c>
+      <c r="L89">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M89">
+        <v>5.38098132</v>
+      </c>
+      <c r="N89">
+        <v>-1.020981320000001</v>
+      </c>
+      <c r="O89">
+        <v>-0.102098132</v>
+      </c>
+      <c r="P89">
+        <v>-0.9188831880000006</v>
+      </c>
+      <c r="Q89">
+        <v>1.891116811999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4869805282063576</v>
+      </c>
+      <c r="T89">
+        <v>5.167471117919631</v>
+      </c>
+      <c r="U89">
+        <v>0.1966</v>
+      </c>
+      <c r="V89">
+        <v>0.08102611290982885</v>
+      </c>
+      <c r="W89">
+        <v>0.1806702662019276</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.8102611290982886</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2220686002625035</v>
+      </c>
+      <c r="C90">
+        <v>0.9211957278971035</v>
+      </c>
+      <c r="D90">
+        <v>27.4359957278971</v>
+      </c>
+      <c r="E90">
+        <v>-0.8152000000000008</v>
+      </c>
+      <c r="F90">
+        <v>27.6848</v>
+      </c>
+      <c r="G90">
+        <v>1.17</v>
+      </c>
+      <c r="H90">
+        <v>2.96</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>7.17</v>
+      </c>
+      <c r="K90">
+        <v>2.81</v>
+      </c>
+      <c r="L90">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M90">
+        <v>5.442831679999999</v>
+      </c>
+      <c r="N90">
+        <v>-1.08283168</v>
+      </c>
+      <c r="O90">
+        <v>-0.108283168</v>
+      </c>
+      <c r="P90">
+        <v>-0.974548512</v>
+      </c>
+      <c r="Q90">
+        <v>1.835451488</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5243289055568875</v>
+      </c>
+      <c r="T90">
+        <v>5.598093711079602</v>
+      </c>
+      <c r="U90">
+        <v>0.1966</v>
+      </c>
+      <c r="V90">
+        <v>0.08010536162676261</v>
+      </c>
+      <c r="W90">
+        <v>0.1808512859041785</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.8010536162676263</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2393100748374201</v>
+      </c>
+      <c r="C91">
+        <v>-1.503175334037472</v>
+      </c>
+      <c r="D91">
+        <v>25.32622466596253</v>
+      </c>
+      <c r="E91">
+        <v>-0.5005999999999986</v>
+      </c>
+      <c r="F91">
+        <v>27.9994</v>
+      </c>
+      <c r="G91">
+        <v>1.17</v>
+      </c>
+      <c r="H91">
+        <v>2.96</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>7.17</v>
+      </c>
+      <c r="K91">
+        <v>2.81</v>
+      </c>
+      <c r="L91">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M91">
+        <v>5.98627172</v>
+      </c>
+      <c r="N91">
+        <v>-1.626271720000001</v>
+      </c>
+      <c r="O91">
+        <v>-0.1626271720000001</v>
+      </c>
+      <c r="P91">
+        <v>-1.463644548000001</v>
+      </c>
+      <c r="Q91">
+        <v>1.346355451999999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.571699484015846</v>
+      </c>
+      <c r="T91">
+        <v>6.144271156595723</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.07283331268497778</v>
+      </c>
+      <c r="W91">
+        <v>0.1982282377479517</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.7283331268497781</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2410600748374201</v>
+      </c>
+      <c r="C92">
+        <v>-2.013918035410711</v>
+      </c>
+      <c r="D92">
+        <v>25.13008196458929</v>
+      </c>
+      <c r="E92">
+        <v>-0.1859999999999999</v>
+      </c>
+      <c r="F92">
+        <v>28.314</v>
+      </c>
+      <c r="G92">
+        <v>1.17</v>
+      </c>
+      <c r="H92">
+        <v>2.96</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>7.17</v>
+      </c>
+      <c r="K92">
+        <v>2.81</v>
+      </c>
+      <c r="L92">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M92">
+        <v>6.0535332</v>
+      </c>
+      <c r="N92">
+        <v>-1.6935332</v>
+      </c>
+      <c r="O92">
+        <v>-0.16935332</v>
+      </c>
+      <c r="P92">
+        <v>-1.52417988</v>
+      </c>
+      <c r="Q92">
+        <v>1.28582012</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6249894324174308</v>
+      </c>
+      <c r="T92">
+        <v>6.758698272255296</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.07202405365514471</v>
+      </c>
+      <c r="W92">
+        <v>0.19840125732853</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.7202405365514473</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2428100748374201</v>
+      </c>
+      <c r="C93">
+        <v>-2.521645972616643</v>
+      </c>
+      <c r="D93">
+        <v>24.93695402738336</v>
+      </c>
+      <c r="E93">
+        <v>0.1286000000000023</v>
+      </c>
+      <c r="F93">
+        <v>28.6286</v>
+      </c>
+      <c r="G93">
+        <v>1.17</v>
+      </c>
+      <c r="H93">
+        <v>2.96</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>7.17</v>
+      </c>
+      <c r="K93">
+        <v>2.81</v>
+      </c>
+      <c r="L93">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M93">
+        <v>6.12079468</v>
+      </c>
+      <c r="N93">
+        <v>-1.760794680000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.176079468</v>
+      </c>
+      <c r="P93">
+        <v>-1.584715212000001</v>
+      </c>
+      <c r="Q93">
+        <v>1.225284787999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.690121591574923</v>
+      </c>
+      <c r="T93">
+        <v>7.509664746950328</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.0712325805380552</v>
+      </c>
+      <c r="W93">
+        <v>0.1985704742809638</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.7123258053805521</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2445600748374201</v>
+      </c>
+      <c r="C94">
+        <v>-3.026428122122351</v>
+      </c>
+      <c r="D94">
+        <v>24.74677187787765</v>
+      </c>
+      <c r="E94">
+        <v>0.4432000000000009</v>
+      </c>
+      <c r="F94">
+        <v>28.9432</v>
+      </c>
+      <c r="G94">
+        <v>1.17</v>
+      </c>
+      <c r="H94">
+        <v>2.96</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>7.17</v>
+      </c>
+      <c r="K94">
+        <v>2.81</v>
+      </c>
+      <c r="L94">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M94">
+        <v>6.188056159999999</v>
+      </c>
+      <c r="N94">
+        <v>-1.82805616</v>
+      </c>
+      <c r="O94">
+        <v>-0.182805616</v>
+      </c>
+      <c r="P94">
+        <v>-1.645250544</v>
+      </c>
+      <c r="Q94">
+        <v>1.164749456</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7715367905217887</v>
+      </c>
+      <c r="T94">
+        <v>8.448372840319122</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.07045831335829374</v>
+      </c>
+      <c r="W94">
+        <v>0.1987360126039968</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.7045831335829376</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2463100748374201</v>
+      </c>
+      <c r="C95">
+        <v>-3.528331372119894</v>
+      </c>
+      <c r="D95">
+        <v>24.55946862788011</v>
+      </c>
+      <c r="E95">
+        <v>0.7578000000000031</v>
+      </c>
+      <c r="F95">
+        <v>29.2578</v>
+      </c>
+      <c r="G95">
+        <v>1.17</v>
+      </c>
+      <c r="H95">
+        <v>2.96</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>7.17</v>
+      </c>
+      <c r="K95">
+        <v>2.81</v>
+      </c>
+      <c r="L95">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M95">
+        <v>6.25531764</v>
+      </c>
+      <c r="N95">
+        <v>-1.895317640000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.189531764</v>
+      </c>
+      <c r="P95">
+        <v>-1.705785876000001</v>
+      </c>
+      <c r="Q95">
+        <v>1.104214123999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8762134748820443</v>
+      </c>
+      <c r="T95">
+        <v>9.655283246078998</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.0697006970856239</v>
+      </c>
+      <c r="W95">
+        <v>0.1988979909630936</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.6970069708562392</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2480600748374201</v>
+      </c>
+      <c r="C96">
+        <v>-4.027420600961264</v>
+      </c>
+      <c r="D96">
+        <v>24.37497939903874</v>
+      </c>
+      <c r="E96">
+        <v>1.072400000000002</v>
+      </c>
+      <c r="F96">
+        <v>29.5724</v>
+      </c>
+      <c r="G96">
+        <v>1.17</v>
+      </c>
+      <c r="H96">
+        <v>2.96</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>7.17</v>
+      </c>
+      <c r="K96">
+        <v>2.81</v>
+      </c>
+      <c r="L96">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M96">
+        <v>6.32257912</v>
+      </c>
+      <c r="N96">
+        <v>-1.962579120000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.196257912</v>
+      </c>
+      <c r="P96">
+        <v>-1.766321208000001</v>
+      </c>
+      <c r="Q96">
+        <v>1.043678791999999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.015782387362385</v>
+      </c>
+      <c r="T96">
+        <v>11.2644971204255</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.06895920030811727</v>
+      </c>
+      <c r="W96">
+        <v>0.1990565229741245</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.6895920030811729</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2498100748374201</v>
+      </c>
+      <c r="C97">
+        <v>-4.523758752084557</v>
+      </c>
+      <c r="D97">
+        <v>24.19324124791545</v>
+      </c>
+      <c r="E97">
+        <v>1.387000000000004</v>
+      </c>
+      <c r="F97">
+        <v>29.887</v>
+      </c>
+      <c r="G97">
+        <v>1.17</v>
+      </c>
+      <c r="H97">
+        <v>2.96</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>7.17</v>
+      </c>
+      <c r="K97">
+        <v>2.81</v>
+      </c>
+      <c r="L97">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M97">
+        <v>6.3898406</v>
+      </c>
+      <c r="N97">
+        <v>-2.029840600000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.20298406</v>
+      </c>
+      <c r="P97">
+        <v>-1.826856540000001</v>
+      </c>
+      <c r="Q97">
+        <v>0.9831434599999993</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.211178864834862</v>
+      </c>
+      <c r="T97">
+        <v>13.51739654451061</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.06823331398908446</v>
+      </c>
+      <c r="W97">
+        <v>0.1992117174691337</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.6823331398908448</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2515600748374201</v>
+      </c>
+      <c r="C98">
+        <v>-5.017406905612987</v>
+      </c>
+      <c r="D98">
+        <v>24.01419309438701</v>
+      </c>
+      <c r="E98">
+        <v>1.701599999999999</v>
+      </c>
+      <c r="F98">
+        <v>30.2016</v>
+      </c>
+      <c r="G98">
+        <v>1.17</v>
+      </c>
+      <c r="H98">
+        <v>2.96</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>7.17</v>
+      </c>
+      <c r="K98">
+        <v>2.81</v>
+      </c>
+      <c r="L98">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M98">
+        <v>6.457102079999999</v>
+      </c>
+      <c r="N98">
+        <v>-2.09710208</v>
+      </c>
+      <c r="O98">
+        <v>-0.209710208</v>
+      </c>
+      <c r="P98">
+        <v>-1.887391872</v>
+      </c>
+      <c r="Q98">
+        <v>0.922608128</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.504273581043575</v>
+      </c>
+      <c r="T98">
+        <v>16.89674568063822</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.06752255030169817</v>
+      </c>
+      <c r="W98">
+        <v>0.1993636787454969</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.6752255030169818</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2533100748374201</v>
+      </c>
+      <c r="C99">
+        <v>-5.508424346798083</v>
+      </c>
+      <c r="D99">
+        <v>23.83777565320192</v>
+      </c>
+      <c r="E99">
+        <v>2.016200000000001</v>
+      </c>
+      <c r="F99">
+        <v>30.5162</v>
+      </c>
+      <c r="G99">
+        <v>1.17</v>
+      </c>
+      <c r="H99">
+        <v>2.96</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>7.17</v>
+      </c>
+      <c r="K99">
+        <v>2.81</v>
+      </c>
+      <c r="L99">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M99">
+        <v>6.52436356</v>
+      </c>
+      <c r="N99">
+        <v>-2.164363560000001</v>
+      </c>
+      <c r="O99">
+        <v>-0.216436356</v>
+      </c>
+      <c r="P99">
+        <v>-1.947927204000001</v>
+      </c>
+      <c r="Q99">
+        <v>0.8620727959999992</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.992764774724767</v>
+      </c>
+      <c r="T99">
+        <v>22.52899424085096</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.06682644153570128</v>
+      </c>
+      <c r="W99">
+        <v>0.1995125067996671</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.6682644153570129</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2550600748374201</v>
+      </c>
+      <c r="C100">
+        <v>-5.996868631467873</v>
+      </c>
+      <c r="D100">
+        <v>23.66393136853213</v>
+      </c>
+      <c r="E100">
+        <v>2.3308</v>
+      </c>
+      <c r="F100">
+        <v>30.8308</v>
+      </c>
+      <c r="G100">
+        <v>1.17</v>
+      </c>
+      <c r="H100">
+        <v>2.96</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>7.17</v>
+      </c>
+      <c r="K100">
+        <v>2.81</v>
+      </c>
+      <c r="L100">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M100">
+        <v>6.591625039999999</v>
+      </c>
+      <c r="N100">
+        <v>-2.23162504</v>
+      </c>
+      <c r="O100">
+        <v>-0.223162504</v>
+      </c>
+      <c r="P100">
+        <v>-2.008462536</v>
+      </c>
+      <c r="Q100">
+        <v>0.8015374639999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.96974716208715</v>
+      </c>
+      <c r="T100">
+        <v>33.79349136127644</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.06614453907105128</v>
+      </c>
+      <c r="W100">
+        <v>0.1996582975466092</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.6614453907105129</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2568100748374201</v>
+      </c>
+      <c r="C101">
+        <v>-6.482795648632141</v>
+      </c>
+      <c r="D101">
+        <v>23.49260435136786</v>
+      </c>
+      <c r="E101">
+        <v>2.645400000000002</v>
+      </c>
+      <c r="F101">
+        <v>31.1454</v>
+      </c>
+      <c r="G101">
+        <v>1.17</v>
+      </c>
+      <c r="H101">
+        <v>2.96</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>7.17</v>
+      </c>
+      <c r="K101">
+        <v>2.81</v>
+      </c>
+      <c r="L101">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="M101">
+        <v>6.65888652</v>
+      </c>
+      <c r="N101">
+        <v>-2.298886520000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.229888652</v>
+      </c>
+      <c r="P101">
+        <v>-2.068997868000001</v>
+      </c>
+      <c r="Q101">
+        <v>0.7410021319999993</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.9006943241743</v>
+      </c>
+      <c r="T101">
+        <v>67.58698272255288</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.06547641241376791</v>
+      </c>
+      <c r="W101">
+        <v>0.1998011430259364</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.6547641241376794</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_retail_automotive.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0917449395069494</v>
+        <v>0.09169369456744243</v>
       </c>
       <c r="C2">
-        <v>216.5201025366814</v>
+        <v>215.1152611673501</v>
       </c>
       <c r="D2">
-        <v>215.0801025366814</v>
+        <v>215.3202611673501</v>
       </c>
       <c r="E2">
-        <v>-151.9</v>
+        <v>-150.255</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.645</v>
       </c>
       <c r="G2">
         <v>1.44</v>
@@ -1445,28 +1445,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0827435</v>
       </c>
       <c r="N2">
-        <v>5.633333333333334</v>
+        <v>5.550589833333333</v>
       </c>
       <c r="O2">
-        <v>0.5633333333333334</v>
+        <v>0.5550589833333334</v>
       </c>
       <c r="P2">
-        <v>5.07</v>
+        <v>4.99553085</v>
       </c>
       <c r="Q2">
-        <v>8.52</v>
+        <v>8.445530850000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0917449395069494</v>
+        <v>0.09216262077519438</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7172149983119495</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>68.08188357192206</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09169369456744243</v>
+        <v>0.09164244962793548</v>
       </c>
       <c r="C3">
-        <v>215.1152611673501</v>
+        <v>213.7109567202208</v>
       </c>
       <c r="D3">
-        <v>215.3202611673501</v>
+        <v>215.5609567202208</v>
       </c>
       <c r="E3">
-        <v>-150.255</v>
+        <v>-148.61</v>
       </c>
       <c r="F3">
-        <v>1.645</v>
+        <v>3.29</v>
       </c>
       <c r="G3">
         <v>1.44</v>
@@ -1527,28 +1527,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M3">
-        <v>0.0827435</v>
+        <v>0.165487</v>
       </c>
       <c r="N3">
-        <v>5.550589833333333</v>
+        <v>5.467846333333334</v>
       </c>
       <c r="O3">
-        <v>0.5550589833333334</v>
+        <v>0.5467846333333334</v>
       </c>
       <c r="P3">
-        <v>4.99553085</v>
+        <v>4.921061700000001</v>
       </c>
       <c r="Q3">
-        <v>8.445530850000001</v>
+        <v>8.371061700000002</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09216262077519438</v>
+        <v>0.09258882615095458</v>
       </c>
       <c r="T3">
-        <v>0.7172149983119495</v>
+        <v>0.7238082599254074</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>68.08188357192206</v>
+        <v>34.04094178596104</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09164244962793548</v>
+        <v>0.09159120468842853</v>
       </c>
       <c r="C4">
-        <v>213.7109567202208</v>
+        <v>212.3071909979024</v>
       </c>
       <c r="D4">
-        <v>215.5609567202208</v>
+        <v>215.8021909979024</v>
       </c>
       <c r="E4">
-        <v>-148.61</v>
+        <v>-146.965</v>
       </c>
       <c r="F4">
-        <v>3.29</v>
+        <v>4.935</v>
       </c>
       <c r="G4">
         <v>1.44</v>
@@ -1609,28 +1609,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M4">
-        <v>0.165487</v>
+        <v>0.2482305</v>
       </c>
       <c r="N4">
-        <v>5.467846333333334</v>
+        <v>5.385102833333334</v>
       </c>
       <c r="O4">
-        <v>0.5467846333333334</v>
+        <v>0.5385102833333334</v>
       </c>
       <c r="P4">
-        <v>4.921061700000001</v>
+        <v>4.84659255</v>
       </c>
       <c r="Q4">
-        <v>8.371061700000002</v>
+        <v>8.29659255</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09258882615095458</v>
+        <v>0.09302381926642117</v>
       </c>
       <c r="T4">
-        <v>0.7238082599254074</v>
+        <v>0.730537465077287</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.04094178596104</v>
+        <v>22.69396119064069</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09159120468842853</v>
+        <v>0.0915399597489216</v>
       </c>
       <c r="C5">
-        <v>212.3071909979024</v>
+        <v>210.9039658110823</v>
       </c>
       <c r="D5">
-        <v>215.8021909979024</v>
+        <v>216.0439658110823</v>
       </c>
       <c r="E5">
-        <v>-146.965</v>
+        <v>-145.32</v>
       </c>
       <c r="F5">
-        <v>4.935</v>
+        <v>6.58</v>
       </c>
       <c r="G5">
         <v>1.44</v>
@@ -1691,28 +1691,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M5">
-        <v>0.2482305</v>
+        <v>0.330974</v>
       </c>
       <c r="N5">
-        <v>5.385102833333334</v>
+        <v>5.302359333333333</v>
       </c>
       <c r="O5">
-        <v>0.5385102833333334</v>
+        <v>0.5302359333333334</v>
       </c>
       <c r="P5">
-        <v>4.84659255</v>
+        <v>4.7721234</v>
       </c>
       <c r="Q5">
-        <v>8.29659255</v>
+        <v>8.222123400000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09302381926642117</v>
+        <v>0.09346787473845999</v>
       </c>
       <c r="T5">
-        <v>0.730537465077287</v>
+        <v>0.7374068620031643</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.69396119064069</v>
+        <v>17.02047089298052</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0915399597489216</v>
+        <v>0.09148871480941465</v>
       </c>
       <c r="C6">
-        <v>210.9039658110823</v>
+        <v>209.5012829785713</v>
       </c>
       <c r="D6">
-        <v>216.0439658110823</v>
+        <v>216.2862829785713</v>
       </c>
       <c r="E6">
-        <v>-145.32</v>
+        <v>-143.675</v>
       </c>
       <c r="F6">
-        <v>6.58</v>
+        <v>8.225</v>
       </c>
       <c r="G6">
         <v>1.44</v>
@@ -1773,28 +1773,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M6">
-        <v>0.330974</v>
+        <v>0.4137175</v>
       </c>
       <c r="N6">
-        <v>5.302359333333333</v>
+        <v>5.219615833333334</v>
       </c>
       <c r="O6">
-        <v>0.5302359333333334</v>
+        <v>0.5219615833333334</v>
       </c>
       <c r="P6">
-        <v>4.7721234</v>
+        <v>4.69765425</v>
       </c>
       <c r="Q6">
-        <v>8.222123400000001</v>
+        <v>8.14765425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09346787473845999</v>
+        <v>0.09392127874675225</v>
       </c>
       <c r="T6">
-        <v>0.7374068620031643</v>
+        <v>0.7444208778116915</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.02047089298052</v>
+        <v>13.61637671438442</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09148871480941465</v>
+        <v>0.09151846986990769</v>
       </c>
       <c r="C7">
-        <v>209.5012829785713</v>
+        <v>207.715516862554</v>
       </c>
       <c r="D7">
-        <v>216.2862829785713</v>
+        <v>216.145516862554</v>
       </c>
       <c r="E7">
-        <v>-143.675</v>
+        <v>-142.03</v>
       </c>
       <c r="F7">
-        <v>8.225</v>
+        <v>9.870000000000001</v>
       </c>
       <c r="G7">
         <v>1.44</v>
@@ -1855,45 +1855,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M7">
-        <v>0.4137175</v>
+        <v>0.511266</v>
       </c>
       <c r="N7">
-        <v>5.219615833333334</v>
+        <v>5.122067333333334</v>
       </c>
       <c r="O7">
-        <v>0.5219615833333334</v>
+        <v>0.5122067333333334</v>
       </c>
       <c r="P7">
-        <v>4.69765425</v>
+        <v>4.6098606</v>
       </c>
       <c r="Q7">
-        <v>8.14765425</v>
+        <v>8.0598606</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09392127874675225</v>
+        <v>0.09438432964883797</v>
       </c>
       <c r="T7">
-        <v>0.7444208778116915</v>
+        <v>0.7515841279991237</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.1</v>
       </c>
       <c r="W7">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.61637671438442</v>
+        <v>11.01840007615084</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09151846986990769</v>
+        <v>0.09158782493040074</v>
       </c>
       <c r="C8">
-        <v>207.715516862554</v>
+        <v>205.7431201054447</v>
       </c>
       <c r="D8">
-        <v>216.145516862554</v>
+        <v>215.8181201054446</v>
       </c>
       <c r="E8">
-        <v>-142.03</v>
+        <v>-140.385</v>
       </c>
       <c r="F8">
-        <v>9.869999999999999</v>
+        <v>11.515</v>
       </c>
       <c r="G8">
         <v>1.44</v>
@@ -1937,45 +1937,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M8">
-        <v>0.511266</v>
+        <v>0.6160524999999999</v>
       </c>
       <c r="N8">
-        <v>5.122067333333334</v>
+        <v>5.017280833333334</v>
       </c>
       <c r="O8">
-        <v>0.5122067333333334</v>
+        <v>0.5017280833333334</v>
       </c>
       <c r="P8">
-        <v>4.6098606</v>
+        <v>4.515552750000001</v>
       </c>
       <c r="Q8">
-        <v>8.0598606</v>
+        <v>7.965552750000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09438432964883797</v>
+        <v>0.0948573386348395</v>
       </c>
       <c r="T8">
-        <v>0.7515841279991237</v>
+        <v>0.7589014265776832</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.01840007615084</v>
+        <v>9.144242306188735</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09158782493040074</v>
+        <v>0.09156537999089379</v>
       </c>
       <c r="C9">
-        <v>205.7431201054446</v>
+        <v>204.2039648433499</v>
       </c>
       <c r="D9">
-        <v>215.8181201054446</v>
+        <v>215.9239648433499</v>
       </c>
       <c r="E9">
-        <v>-140.385</v>
+        <v>-138.74</v>
       </c>
       <c r="F9">
-        <v>11.515</v>
+        <v>13.16</v>
       </c>
       <c r="G9">
         <v>1.44</v>
@@ -2019,28 +2019,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M9">
-        <v>0.6160525</v>
+        <v>0.70406</v>
       </c>
       <c r="N9">
-        <v>5.017280833333333</v>
+        <v>4.929273333333334</v>
       </c>
       <c r="O9">
-        <v>0.5017280833333334</v>
+        <v>0.4929273333333334</v>
       </c>
       <c r="P9">
-        <v>4.51555275</v>
+        <v>4.436346</v>
       </c>
       <c r="Q9">
-        <v>7.965552750000001</v>
+        <v>7.886346000000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09485733863483951</v>
+        <v>0.09534063042488455</v>
       </c>
       <c r="T9">
-        <v>0.7589014265776833</v>
+        <v>0.7663777968644725</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.144242306188731</v>
+        <v>8.00121201791514</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09156537999089379</v>
+        <v>0.09160773505138683</v>
       </c>
       <c r="C10">
-        <v>204.2039648433499</v>
+        <v>202.3593157538985</v>
       </c>
       <c r="D10">
-        <v>215.9239648433499</v>
+        <v>215.7243157538985</v>
       </c>
       <c r="E10">
-        <v>-138.74</v>
+        <v>-137.095</v>
       </c>
       <c r="F10">
-        <v>13.16</v>
+        <v>14.805</v>
       </c>
       <c r="G10">
         <v>1.44</v>
@@ -2101,45 +2101,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M10">
-        <v>0.70406</v>
+        <v>0.8039115</v>
       </c>
       <c r="N10">
-        <v>4.929273333333334</v>
+        <v>4.829421833333334</v>
       </c>
       <c r="O10">
-        <v>0.4929273333333334</v>
+        <v>0.4829421833333334</v>
       </c>
       <c r="P10">
-        <v>4.436346</v>
+        <v>4.346479650000001</v>
       </c>
       <c r="Q10">
-        <v>7.886346000000001</v>
+        <v>7.796479650000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09534063042488455</v>
+        <v>0.09583454401251301</v>
       </c>
       <c r="T10">
-        <v>0.7663777968644725</v>
+        <v>0.7740184829817405</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.00121201791514</v>
+        <v>7.007404836643503</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09160773505138683</v>
+        <v>0.09159249011187991</v>
       </c>
       <c r="C11">
-        <v>202.3593157538985</v>
+        <v>200.7861332972514</v>
       </c>
       <c r="D11">
-        <v>215.7243157538985</v>
+        <v>215.7961332972513</v>
       </c>
       <c r="E11">
-        <v>-137.095</v>
+        <v>-135.45</v>
       </c>
       <c r="F11">
-        <v>14.805</v>
+        <v>16.45</v>
       </c>
       <c r="G11">
         <v>1.44</v>
@@ -2183,28 +2183,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M11">
-        <v>0.8039115</v>
+        <v>0.893235</v>
       </c>
       <c r="N11">
-        <v>4.829421833333334</v>
+        <v>4.740098333333334</v>
       </c>
       <c r="O11">
-        <v>0.4829421833333334</v>
+        <v>0.4740098333333334</v>
       </c>
       <c r="P11">
-        <v>4.346479650000001</v>
+        <v>4.2660885</v>
       </c>
       <c r="Q11">
-        <v>7.796479650000001</v>
+        <v>7.716088500000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09583454401251301</v>
+        <v>0.09633943345764434</v>
       </c>
       <c r="T11">
-        <v>0.7740184829817405</v>
+        <v>0.7818289621238369</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.007404836643503</v>
+        <v>6.306664352979153</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09159249011187991</v>
+        <v>0.09167624517237294</v>
       </c>
       <c r="C12">
-        <v>200.7861332972514</v>
+        <v>198.7471599428374</v>
       </c>
       <c r="D12">
-        <v>215.7961332972513</v>
+        <v>215.4021599428374</v>
       </c>
       <c r="E12">
-        <v>-135.45</v>
+        <v>-133.805</v>
       </c>
       <c r="F12">
-        <v>16.45</v>
+        <v>18.095</v>
       </c>
       <c r="G12">
         <v>1.44</v>
@@ -2265,45 +2265,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M12">
-        <v>0.893235</v>
+        <v>1.0006535</v>
       </c>
       <c r="N12">
-        <v>4.740098333333334</v>
+        <v>4.632679833333334</v>
       </c>
       <c r="O12">
-        <v>0.4740098333333334</v>
+        <v>0.4632679833333335</v>
       </c>
       <c r="P12">
-        <v>4.2660885</v>
+        <v>4.169411850000001</v>
       </c>
       <c r="Q12">
-        <v>7.716088500000001</v>
+        <v>7.619411850000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09633943345764434</v>
+        <v>0.0968556687330033</v>
       </c>
       <c r="T12">
-        <v>0.7818289621238369</v>
+        <v>0.7898149576511487</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.306664352979153</v>
+        <v>5.629654354212857</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09167624517237294</v>
+        <v>0.09167000023286601</v>
       </c>
       <c r="C13">
-        <v>198.7471599428374</v>
+        <v>197.1314857211604</v>
       </c>
       <c r="D13">
-        <v>215.4021599428374</v>
+        <v>215.4314857211604</v>
       </c>
       <c r="E13">
-        <v>-133.805</v>
+        <v>-132.16</v>
       </c>
       <c r="F13">
-        <v>18.095</v>
+        <v>19.74</v>
       </c>
       <c r="G13">
         <v>1.44</v>
@@ -2347,28 +2347,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M13">
-        <v>1.0006535</v>
+        <v>1.091622</v>
       </c>
       <c r="N13">
-        <v>4.632679833333334</v>
+        <v>4.541711333333334</v>
       </c>
       <c r="O13">
-        <v>0.4632679833333335</v>
+        <v>0.4541711333333334</v>
       </c>
       <c r="P13">
-        <v>4.169411850000001</v>
+        <v>4.0875402</v>
       </c>
       <c r="Q13">
-        <v>7.619411850000001</v>
+        <v>7.5375402</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0968556687330033</v>
+        <v>0.09738363662825682</v>
       </c>
       <c r="T13">
-        <v>0.7898149576511487</v>
+        <v>0.7979824530768087</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.629654354212857</v>
+        <v>5.160516491361784</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09167000023286601</v>
+        <v>0.09166375529335904</v>
       </c>
       <c r="C14">
-        <v>197.1314857211604</v>
+        <v>195.5158194856465</v>
       </c>
       <c r="D14">
-        <v>215.4314857211604</v>
+        <v>215.4608194856465</v>
       </c>
       <c r="E14">
-        <v>-132.16</v>
+        <v>-130.515</v>
       </c>
       <c r="F14">
-        <v>19.74</v>
+        <v>21.385</v>
       </c>
       <c r="G14">
         <v>1.44</v>
@@ -2429,28 +2429,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M14">
-        <v>1.091622</v>
+        <v>1.1825905</v>
       </c>
       <c r="N14">
-        <v>4.541711333333334</v>
+        <v>4.450742833333334</v>
       </c>
       <c r="O14">
-        <v>0.4541711333333334</v>
+        <v>0.4450742833333334</v>
       </c>
       <c r="P14">
-        <v>4.0875402</v>
+        <v>4.00566855</v>
       </c>
       <c r="Q14">
-        <v>7.5375402</v>
+        <v>7.45566855</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09738363662825682</v>
+        <v>0.09792374171650464</v>
       </c>
       <c r="T14">
-        <v>0.7979824530768087</v>
+        <v>0.806337707018001</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.160516491361784</v>
+        <v>4.763553684333955</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09166375529335904</v>
+        <v>0.09197251035385209</v>
       </c>
       <c r="C15">
-        <v>195.5158194856465</v>
+        <v>192.430035394759</v>
       </c>
       <c r="D15">
-        <v>215.4608194856465</v>
+        <v>214.020035394759</v>
       </c>
       <c r="E15">
-        <v>-130.515</v>
+        <v>-128.87</v>
       </c>
       <c r="F15">
-        <v>21.385</v>
+        <v>23.03</v>
       </c>
       <c r="G15">
         <v>1.44</v>
@@ -2511,45 +2511,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M15">
-        <v>1.1825905</v>
+        <v>1.331134</v>
       </c>
       <c r="N15">
-        <v>4.450742833333334</v>
+        <v>4.302199333333333</v>
       </c>
       <c r="O15">
-        <v>0.4450742833333334</v>
+        <v>0.4302199333333334</v>
       </c>
       <c r="P15">
-        <v>4.00566855</v>
+        <v>3.8719794</v>
       </c>
       <c r="Q15">
-        <v>7.45566855</v>
+        <v>7.3219794</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09792374171650464</v>
+        <v>0.0984764073882001</v>
       </c>
       <c r="T15">
-        <v>0.806337707018001</v>
+        <v>0.8148872691903838</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.763553684333955</v>
+        <v>4.231980652085614</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09197251035385209</v>
+        <v>0.09246126541434516</v>
       </c>
       <c r="C16">
-        <v>192.430035394759</v>
+        <v>188.5432750306276</v>
       </c>
       <c r="D16">
-        <v>214.020035394759</v>
+        <v>211.7782750306276</v>
       </c>
       <c r="E16">
-        <v>-128.87</v>
+        <v>-127.225</v>
       </c>
       <c r="F16">
-        <v>23.03</v>
+        <v>24.675</v>
       </c>
       <c r="G16">
         <v>1.44</v>
@@ -2593,45 +2593,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M16">
-        <v>1.331134</v>
+        <v>1.5125775</v>
       </c>
       <c r="N16">
-        <v>4.302199333333333</v>
+        <v>4.120755833333334</v>
       </c>
       <c r="O16">
-        <v>0.4302199333333334</v>
+        <v>0.4120755833333334</v>
       </c>
       <c r="P16">
-        <v>3.8719794</v>
+        <v>3.70868025</v>
       </c>
       <c r="Q16">
-        <v>7.3219794</v>
+        <v>7.158680250000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0984764073882001</v>
+        <v>0.09904207695805312</v>
       </c>
       <c r="T16">
-        <v>0.8148872691903838</v>
+        <v>0.8236379975315287</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.231980652085614</v>
+        <v>3.724327073048047</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09246126541434516</v>
+        <v>0.0929122204748382</v>
       </c>
       <c r="C17">
-        <v>188.5432750306276</v>
+        <v>184.871147379564</v>
       </c>
       <c r="D17">
-        <v>211.7782750306276</v>
+        <v>209.751147379564</v>
       </c>
       <c r="E17">
-        <v>-127.225</v>
+        <v>-125.58</v>
       </c>
       <c r="F17">
-        <v>24.675</v>
+        <v>26.32</v>
       </c>
       <c r="G17">
         <v>1.44</v>
@@ -2675,45 +2675,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M17">
-        <v>1.5125775</v>
+        <v>1.687112</v>
       </c>
       <c r="N17">
-        <v>4.120755833333334</v>
+        <v>3.946221333333334</v>
       </c>
       <c r="O17">
-        <v>0.4120755833333334</v>
+        <v>0.3946221333333334</v>
       </c>
       <c r="P17">
-        <v>3.70868025</v>
+        <v>3.551599200000001</v>
       </c>
       <c r="Q17">
-        <v>7.158680250000001</v>
+        <v>7.001599200000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09904207695805312</v>
+        <v>0.09962121485099786</v>
       </c>
       <c r="T17">
-        <v>0.8236379975315287</v>
+        <v>0.8325970765474626</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.724327073048048</v>
+        <v>3.339039336649454</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0929122204748382</v>
+        <v>0.09298517553533125</v>
       </c>
       <c r="C18">
-        <v>184.871147379564</v>
+        <v>182.9018419706733</v>
       </c>
       <c r="D18">
-        <v>209.751147379564</v>
+        <v>209.4268419706733</v>
       </c>
       <c r="E18">
-        <v>-125.58</v>
+        <v>-123.935</v>
       </c>
       <c r="F18">
-        <v>26.32</v>
+        <v>27.965</v>
       </c>
       <c r="G18">
         <v>1.44</v>
@@ -2757,28 +2757,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M18">
-        <v>1.687112</v>
+        <v>1.7925565</v>
       </c>
       <c r="N18">
-        <v>3.946221333333334</v>
+        <v>3.840776833333333</v>
       </c>
       <c r="O18">
-        <v>0.3946221333333334</v>
+        <v>0.3840776833333334</v>
       </c>
       <c r="P18">
-        <v>3.551599200000001</v>
+        <v>3.45669915</v>
       </c>
       <c r="Q18">
-        <v>7.001599200000001</v>
+        <v>6.90669915</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09962121485099786</v>
+        <v>0.1002143078738931</v>
       </c>
       <c r="T18">
-        <v>0.8325970765474626</v>
+        <v>0.8417720369854673</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.339039336649454</v>
+        <v>3.142625258023015</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09298517553533125</v>
+        <v>0.0943217305958243</v>
       </c>
       <c r="C19">
-        <v>182.9018419706733</v>
+        <v>175.4880760589507</v>
       </c>
       <c r="D19">
-        <v>209.4268419706733</v>
+        <v>203.6580760589507</v>
       </c>
       <c r="E19">
-        <v>-123.935</v>
+        <v>-122.29</v>
       </c>
       <c r="F19">
-        <v>27.965</v>
+        <v>29.61</v>
       </c>
       <c r="G19">
         <v>1.44</v>
@@ -2839,45 +2839,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M19">
-        <v>1.7925565</v>
+        <v>2.128959</v>
       </c>
       <c r="N19">
-        <v>3.840776833333333</v>
+        <v>3.504374333333333</v>
       </c>
       <c r="O19">
-        <v>0.3840776833333334</v>
+        <v>0.3504374333333333</v>
       </c>
       <c r="P19">
-        <v>3.45669915</v>
+        <v>3.1539369</v>
       </c>
       <c r="Q19">
-        <v>6.90669915</v>
+        <v>6.6039369</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1002143078738931</v>
+        <v>0.1008218665802735</v>
       </c>
       <c r="T19">
-        <v>0.8417720369854673</v>
+        <v>0.85117077694635</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.142625258023015</v>
+        <v>2.646050644156761</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0943217305958243</v>
+        <v>0.09446488565631735</v>
       </c>
       <c r="C20">
-        <v>175.4880760589507</v>
+        <v>173.2439852811769</v>
       </c>
       <c r="D20">
-        <v>203.6580760589507</v>
+        <v>203.0589852811769</v>
       </c>
       <c r="E20">
-        <v>-122.29</v>
+        <v>-120.645</v>
       </c>
       <c r="F20">
-        <v>29.61</v>
+        <v>31.255</v>
       </c>
       <c r="G20">
         <v>1.44</v>
@@ -2921,28 +2921,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M20">
-        <v>2.128959</v>
+        <v>2.2472345</v>
       </c>
       <c r="N20">
-        <v>3.504374333333334</v>
+        <v>3.386098833333334</v>
       </c>
       <c r="O20">
-        <v>0.3504374333333334</v>
+        <v>0.3386098833333334</v>
       </c>
       <c r="P20">
-        <v>3.1539369</v>
+        <v>3.04748895</v>
       </c>
       <c r="Q20">
-        <v>6.603936900000001</v>
+        <v>6.49748895</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1008218665802735</v>
+        <v>0.1014444267361942</v>
       </c>
       <c r="T20">
-        <v>0.85117077694635</v>
+        <v>0.860801584560588</v>
       </c>
       <c r="U20">
         <v>0.07190000000000001</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.646050644156761</v>
+        <v>2.506784820780089</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09446488565631735</v>
+        <v>0.09531004071681042</v>
       </c>
       <c r="C21">
-        <v>173.2439852811769</v>
+        <v>168.1326918484853</v>
       </c>
       <c r="D21">
-        <v>203.0589852811769</v>
+        <v>199.5926918484853</v>
       </c>
       <c r="E21">
-        <v>-120.645</v>
+        <v>-119</v>
       </c>
       <c r="F21">
-        <v>31.255</v>
+        <v>32.9</v>
       </c>
       <c r="G21">
         <v>1.44</v>
@@ -3003,45 +3003,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M21">
-        <v>2.2472345</v>
+        <v>2.49382</v>
       </c>
       <c r="N21">
-        <v>3.386098833333334</v>
+        <v>3.139513333333334</v>
       </c>
       <c r="O21">
-        <v>0.3386098833333334</v>
+        <v>0.3139513333333334</v>
       </c>
       <c r="P21">
-        <v>3.04748895</v>
+        <v>2.825562000000001</v>
       </c>
       <c r="Q21">
-        <v>6.49748895</v>
+        <v>6.275562000000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1014444267361942</v>
+        <v>0.102082550896013</v>
       </c>
       <c r="T21">
-        <v>0.860801584560588</v>
+        <v>0.870673162365182</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.506784820780089</v>
+        <v>2.258917377089499</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09531004071681042</v>
+        <v>0.09548829577730346</v>
       </c>
       <c r="C22">
-        <v>168.1326918484853</v>
+        <v>165.7716598976436</v>
       </c>
       <c r="D22">
-        <v>199.5926918484853</v>
+        <v>198.8766598976436</v>
       </c>
       <c r="E22">
-        <v>-119</v>
+        <v>-117.355</v>
       </c>
       <c r="F22">
-        <v>32.9</v>
+        <v>34.545</v>
       </c>
       <c r="G22">
         <v>1.44</v>
@@ -3085,28 +3085,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M22">
-        <v>2.49382</v>
+        <v>2.618511</v>
       </c>
       <c r="N22">
-        <v>3.139513333333334</v>
+        <v>3.014822333333333</v>
       </c>
       <c r="O22">
-        <v>0.3139513333333334</v>
+        <v>0.3014822333333333</v>
       </c>
       <c r="P22">
-        <v>2.825562000000001</v>
+        <v>2.7133401</v>
       </c>
       <c r="Q22">
-        <v>6.275562000000001</v>
+        <v>6.1633401</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.102082550896013</v>
+        <v>0.1027368300978525</v>
       </c>
       <c r="T22">
-        <v>0.870673162365182</v>
+        <v>0.8807946535319174</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.258917377089499</v>
+        <v>2.151349882942379</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09548829577730346</v>
+        <v>0.09566655083779652</v>
       </c>
       <c r="C23">
-        <v>165.7716598976436</v>
+        <v>163.415747062384</v>
       </c>
       <c r="D23">
-        <v>198.8766598976436</v>
+        <v>198.165747062384</v>
       </c>
       <c r="E23">
-        <v>-117.355</v>
+        <v>-115.71</v>
       </c>
       <c r="F23">
-        <v>34.545</v>
+        <v>36.19</v>
       </c>
       <c r="G23">
         <v>1.44</v>
@@ -3167,28 +3167,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M23">
-        <v>2.618511</v>
+        <v>2.743202</v>
       </c>
       <c r="N23">
-        <v>3.014822333333333</v>
+        <v>2.890131333333334</v>
       </c>
       <c r="O23">
-        <v>0.3014822333333333</v>
+        <v>0.2890131333333334</v>
       </c>
       <c r="P23">
-        <v>2.7133401</v>
+        <v>2.6011182</v>
       </c>
       <c r="Q23">
-        <v>6.1633401</v>
+        <v>6.0511182</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1027368300978525</v>
+        <v>0.1034078856894827</v>
       </c>
       <c r="T23">
-        <v>0.8807946535319174</v>
+        <v>0.8911756701131847</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.151349882942379</v>
+        <v>2.053561251899544</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09566655083779652</v>
+        <v>0.09878420589828957</v>
       </c>
       <c r="C24">
-        <v>163.415747062384</v>
+        <v>150.1104336978428</v>
       </c>
       <c r="D24">
-        <v>198.165747062384</v>
+        <v>186.5054336978428</v>
       </c>
       <c r="E24">
-        <v>-115.71</v>
+        <v>-114.065</v>
       </c>
       <c r="F24">
-        <v>36.19</v>
+        <v>37.835</v>
       </c>
       <c r="G24">
         <v>1.44</v>
@@ -3249,45 +3249,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M24">
-        <v>2.743202</v>
+        <v>3.40515</v>
       </c>
       <c r="N24">
-        <v>2.890131333333334</v>
+        <v>2.228183333333334</v>
       </c>
       <c r="O24">
-        <v>0.2890131333333334</v>
+        <v>0.2228183333333334</v>
       </c>
       <c r="P24">
-        <v>2.6011182</v>
+        <v>2.005365</v>
       </c>
       <c r="Q24">
-        <v>6.0511182</v>
+        <v>5.455365</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1034078856894827</v>
+        <v>0.1040963712964799</v>
       </c>
       <c r="T24">
-        <v>0.8911756701131847</v>
+        <v>0.9018263234887705</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.053561251899544</v>
+        <v>1.654356880998879</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09878420589828957</v>
+        <v>0.09909026095878261</v>
       </c>
       <c r="C25">
-        <v>150.1104336978428</v>
+        <v>147.3943011725804</v>
       </c>
       <c r="D25">
-        <v>186.5054336978428</v>
+        <v>185.4343011725804</v>
       </c>
       <c r="E25">
-        <v>-114.065</v>
+        <v>-112.42</v>
       </c>
       <c r="F25">
-        <v>37.835</v>
+        <v>39.48</v>
       </c>
       <c r="G25">
         <v>1.44</v>
@@ -3331,28 +3331,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M25">
-        <v>3.40515</v>
+        <v>3.5532</v>
       </c>
       <c r="N25">
-        <v>2.228183333333334</v>
+        <v>2.080133333333333</v>
       </c>
       <c r="O25">
-        <v>0.2228183333333334</v>
+        <v>0.2080133333333334</v>
       </c>
       <c r="P25">
-        <v>2.005365</v>
+        <v>1.87212</v>
       </c>
       <c r="Q25">
-        <v>5.455365</v>
+        <v>5.32212</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1040963712964799</v>
+        <v>0.1048029749457666</v>
       </c>
       <c r="T25">
-        <v>0.9018263234887705</v>
+        <v>0.9127572572163454</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.654356880998879</v>
+        <v>1.585425344290592</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09909026095878261</v>
+        <v>0.09939631601927566</v>
       </c>
       <c r="C26">
-        <v>147.3943011725804</v>
+        <v>144.6904017840021</v>
       </c>
       <c r="D26">
-        <v>185.4343011725804</v>
+        <v>184.3754017840021</v>
       </c>
       <c r="E26">
-        <v>-112.42</v>
+        <v>-110.775</v>
       </c>
       <c r="F26">
-        <v>39.48</v>
+        <v>41.125</v>
       </c>
       <c r="G26">
         <v>1.44</v>
@@ -3413,28 +3413,28 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M26">
-        <v>3.553199999999999</v>
+        <v>3.70125</v>
       </c>
       <c r="N26">
-        <v>2.080133333333334</v>
+        <v>1.932083333333334</v>
       </c>
       <c r="O26">
-        <v>0.2080133333333334</v>
+        <v>0.1932083333333334</v>
       </c>
       <c r="P26">
-        <v>1.872120000000001</v>
+        <v>1.738875</v>
       </c>
       <c r="Q26">
-        <v>5.322120000000001</v>
+        <v>5.188875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1048029749457666</v>
+        <v>0.1055284213590342</v>
       </c>
       <c r="T26">
-        <v>0.9127572572163454</v>
+        <v>0.923979682509989</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.585425344290593</v>
+        <v>1.522008330518969</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09939631601927566</v>
+        <v>0.1135086271221494</v>
       </c>
       <c r="C27">
-        <v>144.6904017840021</v>
+        <v>104.6165760894696</v>
       </c>
       <c r="D27">
-        <v>184.3754017840021</v>
+        <v>145.9465760894696</v>
       </c>
       <c r="E27">
-        <v>-110.775</v>
+        <v>-109.13</v>
       </c>
       <c r="F27">
-        <v>41.125</v>
+        <v>42.77</v>
       </c>
       <c r="G27">
         <v>1.44</v>
@@ -3495,45 +3495,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M27">
-        <v>3.70125</v>
+        <v>6.278636000000001</v>
       </c>
       <c r="N27">
-        <v>1.932083333333334</v>
+        <v>-0.6453026666666677</v>
       </c>
       <c r="O27">
-        <v>0.1932083333333334</v>
+        <v>-0.06453026666666677</v>
       </c>
       <c r="P27">
-        <v>1.738875</v>
+        <v>-0.580772400000001</v>
       </c>
       <c r="Q27">
-        <v>5.188875</v>
+        <v>2.869227599999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1055284213590342</v>
+        <v>0.1064393863051582</v>
       </c>
       <c r="T27">
-        <v>0.923979682509989</v>
+        <v>0.9380720205049569</v>
       </c>
       <c r="U27">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1</v>
+        <v>0.08972224752849717</v>
       </c>
       <c r="W27">
-        <v>0.081</v>
+        <v>0.1336287740628166</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.522008330518969</v>
+        <v>0.8972224752849716</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1135086271221494</v>
+        <v>0.1145186271221494</v>
       </c>
       <c r="C28">
-        <v>104.6165760894696</v>
+        <v>100.8265093437626</v>
       </c>
       <c r="D28">
-        <v>145.9465760894696</v>
+        <v>143.8015093437626</v>
       </c>
       <c r="E28">
-        <v>-109.13</v>
+        <v>-107.485</v>
       </c>
       <c r="F28">
-        <v>42.77</v>
+        <v>44.41500000000001</v>
       </c>
       <c r="G28">
         <v>1.44</v>
@@ -3577,37 +3577,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M28">
-        <v>6.278636000000001</v>
+        <v>6.520122000000002</v>
       </c>
       <c r="N28">
-        <v>-0.6453026666666677</v>
+        <v>-0.8867886666666678</v>
       </c>
       <c r="O28">
-        <v>-0.06453026666666677</v>
+        <v>-0.08867886666666679</v>
       </c>
       <c r="P28">
-        <v>-0.580772400000001</v>
+        <v>-0.798109800000001</v>
       </c>
       <c r="Q28">
-        <v>2.869227599999999</v>
+        <v>2.651890199999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1064393863051582</v>
+        <v>0.1072700628298864</v>
       </c>
       <c r="T28">
-        <v>0.9380720205049569</v>
+        <v>0.9509223221557097</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.08972224752849717</v>
+        <v>0.086399201323738</v>
       </c>
       <c r="W28">
-        <v>0.1336287740628166</v>
+        <v>0.1341165972456753</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.8972224752849716</v>
+        <v>0.86399201323738</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1145186271221494</v>
+        <v>0.1155286271221494</v>
       </c>
       <c r="C29">
-        <v>100.8265093437626</v>
+        <v>97.09858400260001</v>
       </c>
       <c r="D29">
-        <v>143.8015093437626</v>
+        <v>141.7185840026</v>
       </c>
       <c r="E29">
-        <v>-107.485</v>
+        <v>-105.84</v>
       </c>
       <c r="F29">
-        <v>44.41500000000001</v>
+        <v>46.06</v>
       </c>
       <c r="G29">
         <v>1.44</v>
@@ -3659,37 +3659,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M29">
-        <v>6.520122000000002</v>
+        <v>6.761608000000001</v>
       </c>
       <c r="N29">
-        <v>-0.8867886666666678</v>
+        <v>-1.128274666666667</v>
       </c>
       <c r="O29">
-        <v>-0.08867886666666679</v>
+        <v>-0.1128274666666667</v>
       </c>
       <c r="P29">
-        <v>-0.798109800000001</v>
+        <v>-1.0154472</v>
       </c>
       <c r="Q29">
-        <v>2.651890199999999</v>
+        <v>2.4345528</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1072700628298864</v>
+        <v>0.1081238137025237</v>
       </c>
       <c r="T29">
-        <v>0.9509223221557097</v>
+        <v>0.9641295766300946</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.086399201323738</v>
+        <v>0.08331351556217594</v>
       </c>
       <c r="W29">
-        <v>0.1341165972456753</v>
+        <v>0.1345695759154726</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.86399201323738</v>
+        <v>0.8331351556217594</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1155286271221494</v>
+        <v>0.1165386271221494</v>
       </c>
       <c r="C30">
-        <v>97.09858400260001</v>
+        <v>93.43013831718309</v>
       </c>
       <c r="D30">
-        <v>141.7185840026</v>
+        <v>139.6951383171831</v>
       </c>
       <c r="E30">
-        <v>-105.84</v>
+        <v>-104.195</v>
       </c>
       <c r="F30">
-        <v>46.06</v>
+        <v>47.70500000000001</v>
       </c>
       <c r="G30">
         <v>1.44</v>
@@ -3741,37 +3741,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M30">
-        <v>6.761608000000001</v>
+        <v>7.003094000000002</v>
       </c>
       <c r="N30">
-        <v>-1.128274666666667</v>
+        <v>-1.369760666666668</v>
       </c>
       <c r="O30">
-        <v>-0.1128274666666667</v>
+        <v>-0.1369760666666668</v>
       </c>
       <c r="P30">
-        <v>-1.0154472</v>
+        <v>-1.232784600000001</v>
       </c>
       <c r="Q30">
-        <v>2.4345528</v>
+        <v>2.217215399999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1081238137025237</v>
+        <v>0.109001613895517</v>
       </c>
       <c r="T30">
-        <v>0.9641295766300946</v>
+        <v>0.977708866441786</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.08331351556217594</v>
+        <v>0.08044063571520435</v>
       </c>
       <c r="W30">
-        <v>0.1345695759154726</v>
+        <v>0.134991314677008</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8331351556217594</v>
+        <v>0.8044063571520434</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1165386271221494</v>
+        <v>0.1340368584798244</v>
       </c>
       <c r="C31">
-        <v>93.43013831718311</v>
+        <v>64.08222717630875</v>
       </c>
       <c r="D31">
-        <v>139.6951383171831</v>
+        <v>111.9922271763088</v>
       </c>
       <c r="E31">
-        <v>-104.195</v>
+        <v>-102.55</v>
       </c>
       <c r="F31">
-        <v>47.705</v>
+        <v>49.35</v>
       </c>
       <c r="G31">
         <v>1.44</v>
@@ -3823,45 +3823,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M31">
-        <v>7.003094000000001</v>
+        <v>9.90948</v>
       </c>
       <c r="N31">
-        <v>-1.369760666666667</v>
+        <v>-4.276146666666667</v>
       </c>
       <c r="O31">
-        <v>-0.1369760666666667</v>
+        <v>-0.4276146666666667</v>
       </c>
       <c r="P31">
-        <v>-1.2327846</v>
+        <v>-3.848532</v>
       </c>
       <c r="Q31">
-        <v>2.2172154</v>
+        <v>-0.3985319999999994</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.109001613895517</v>
+        <v>0.1103162531764173</v>
       </c>
       <c r="T31">
-        <v>0.977708866441786</v>
+        <v>0.9980459180119207</v>
       </c>
       <c r="U31">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.08044063571520436</v>
+        <v>0.05684792071161487</v>
       </c>
       <c r="W31">
-        <v>0.134991314677008</v>
+        <v>0.1893849375211077</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.8044063571520436</v>
+        <v>0.5684792071161487</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1340368584798244</v>
+        <v>0.1355868584798244</v>
       </c>
       <c r="C32">
-        <v>64.08222717630875</v>
+        <v>60.50389355641953</v>
       </c>
       <c r="D32">
-        <v>111.9922271763088</v>
+        <v>110.0588935564195</v>
       </c>
       <c r="E32">
-        <v>-102.55</v>
+        <v>-100.905</v>
       </c>
       <c r="F32">
-        <v>49.35</v>
+        <v>50.995</v>
       </c>
       <c r="G32">
         <v>1.44</v>
@@ -3905,37 +3905,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M32">
-        <v>9.90948</v>
+        <v>10.239796</v>
       </c>
       <c r="N32">
-        <v>-4.276146666666667</v>
+        <v>-4.606462666666666</v>
       </c>
       <c r="O32">
-        <v>-0.4276146666666667</v>
+        <v>-0.4606462666666666</v>
       </c>
       <c r="P32">
-        <v>-3.848532</v>
+        <v>-4.145816399999999</v>
       </c>
       <c r="Q32">
-        <v>-0.3985319999999994</v>
+        <v>-0.6958163999999991</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1103162531764173</v>
+        <v>0.1112512713383943</v>
       </c>
       <c r="T32">
-        <v>0.9980459180119207</v>
+        <v>1.012510351606296</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.05684792071161487</v>
+        <v>0.05501411681769182</v>
       </c>
       <c r="W32">
-        <v>0.1893849375211077</v>
+        <v>0.1897531653430075</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5684792071161487</v>
+        <v>0.5501411681769182</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1355868584798244</v>
+        <v>0.1371368584798244</v>
       </c>
       <c r="C33">
-        <v>60.50389355641953</v>
+        <v>56.99117785159117</v>
       </c>
       <c r="D33">
-        <v>110.0588935564195</v>
+        <v>108.1911778515912</v>
       </c>
       <c r="E33">
-        <v>-100.905</v>
+        <v>-99.26000000000001</v>
       </c>
       <c r="F33">
-        <v>50.995</v>
+        <v>52.64</v>
       </c>
       <c r="G33">
         <v>1.44</v>
@@ -3987,37 +3987,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M33">
-        <v>10.239796</v>
+        <v>10.570112</v>
       </c>
       <c r="N33">
-        <v>-4.606462666666666</v>
+        <v>-4.936778666666666</v>
       </c>
       <c r="O33">
-        <v>-0.4606462666666666</v>
+        <v>-0.4936778666666666</v>
       </c>
       <c r="P33">
-        <v>-4.145816399999999</v>
+        <v>-4.4431008</v>
       </c>
       <c r="Q33">
-        <v>-0.6958163999999991</v>
+        <v>-0.9931007999999997</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1112512713383943</v>
+        <v>0.1122137900345472</v>
       </c>
       <c r="T33">
-        <v>1.012510351606296</v>
+        <v>1.027400209718154</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.05501411681769182</v>
+        <v>0.05329492566713895</v>
       </c>
       <c r="W33">
-        <v>0.1897531653430075</v>
+        <v>0.1900983789260385</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5501411681769182</v>
+        <v>0.5329492566713895</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1371368584798244</v>
+        <v>0.1386868584798244</v>
       </c>
       <c r="C34">
-        <v>56.99117785159117</v>
+        <v>53.54079516975153</v>
       </c>
       <c r="D34">
-        <v>108.1911778515912</v>
+        <v>106.3857951697515</v>
       </c>
       <c r="E34">
-        <v>-99.26000000000001</v>
+        <v>-97.61500000000001</v>
       </c>
       <c r="F34">
-        <v>52.64</v>
+        <v>54.285</v>
       </c>
       <c r="G34">
         <v>1.44</v>
@@ -4069,37 +4069,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M34">
-        <v>10.570112</v>
+        <v>10.900428</v>
       </c>
       <c r="N34">
-        <v>-4.936778666666666</v>
+        <v>-5.267094666666668</v>
       </c>
       <c r="O34">
-        <v>-0.4936778666666666</v>
+        <v>-0.5267094666666668</v>
       </c>
       <c r="P34">
-        <v>-4.4431008</v>
+        <v>-4.740385200000001</v>
       </c>
       <c r="Q34">
-        <v>-0.9931007999999997</v>
+        <v>-1.290385200000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1122137900345472</v>
+        <v>0.1132050406320778</v>
       </c>
       <c r="T34">
-        <v>1.027400209718154</v>
+        <v>1.042734541206484</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.05329492566713895</v>
+        <v>0.05167992791964988</v>
       </c>
       <c r="W34">
-        <v>0.1900983789260385</v>
+        <v>0.1904226704737343</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5329492566713895</v>
+        <v>0.5167992791964988</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1386868584798244</v>
+        <v>0.1402368584798244</v>
       </c>
       <c r="C35">
-        <v>53.54079516975153</v>
+        <v>50.14967627965373</v>
       </c>
       <c r="D35">
-        <v>106.3857951697515</v>
+        <v>104.6396762796537</v>
       </c>
       <c r="E35">
-        <v>-97.61500000000001</v>
+        <v>-95.97</v>
       </c>
       <c r="F35">
-        <v>54.285</v>
+        <v>55.93000000000001</v>
       </c>
       <c r="G35">
         <v>1.44</v>
@@ -4151,37 +4151,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M35">
-        <v>10.900428</v>
+        <v>11.230744</v>
       </c>
       <c r="N35">
-        <v>-5.267094666666668</v>
+        <v>-5.597410666666668</v>
       </c>
       <c r="O35">
-        <v>-0.5267094666666668</v>
+        <v>-0.5597410666666668</v>
       </c>
       <c r="P35">
-        <v>-4.740385200000001</v>
+        <v>-5.037669600000001</v>
       </c>
       <c r="Q35">
-        <v>-1.290385200000001</v>
+        <v>-1.587669600000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1132050406320778</v>
+        <v>0.1142263291265032</v>
       </c>
       <c r="T35">
-        <v>1.042734541206484</v>
+        <v>1.058533549406582</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.05167992791964988</v>
+        <v>0.05015993003966018</v>
       </c>
       <c r="W35">
-        <v>0.1904226704737343</v>
+        <v>0.1907278860480362</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5167992791964988</v>
+        <v>0.5015993003966017</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1402368584798244</v>
+        <v>0.154153163314095</v>
       </c>
       <c r="C36">
-        <v>50.14967627965373</v>
+        <v>35.06531199782083</v>
       </c>
       <c r="D36">
-        <v>104.6396762796537</v>
+        <v>91.20031199782083</v>
       </c>
       <c r="E36">
-        <v>-95.97</v>
+        <v>-94.325</v>
       </c>
       <c r="F36">
-        <v>55.93000000000001</v>
+        <v>57.575</v>
       </c>
       <c r="G36">
         <v>1.44</v>
@@ -4233,45 +4233,45 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M36">
-        <v>11.230744</v>
+        <v>13.576185</v>
       </c>
       <c r="N36">
-        <v>-5.597410666666668</v>
+        <v>-7.942851666666667</v>
       </c>
       <c r="O36">
-        <v>-0.5597410666666668</v>
+        <v>-0.7942851666666667</v>
       </c>
       <c r="P36">
-        <v>-5.037669600000001</v>
+        <v>-7.1485665</v>
       </c>
       <c r="Q36">
-        <v>-1.587669600000001</v>
+        <v>-3.6985665</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1142263291265032</v>
+        <v>0.115457972396558</v>
       </c>
       <c r="T36">
-        <v>1.058533549406582</v>
+        <v>1.077586679084832</v>
       </c>
       <c r="U36">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05015993003966018</v>
+        <v>0.04149422929441027</v>
       </c>
       <c r="W36">
-        <v>0.1907278860480362</v>
+        <v>0.2260156607323781</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.5015993003966017</v>
+        <v>0.4149422929441028</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.154153163314095</v>
+        <v>0.156053163314095</v>
       </c>
       <c r="C37">
-        <v>35.06531199782083</v>
+        <v>31.84865103511257</v>
       </c>
       <c r="D37">
-        <v>91.20031199782083</v>
+        <v>89.62865103511258</v>
       </c>
       <c r="E37">
-        <v>-94.325</v>
+        <v>-92.68000000000001</v>
       </c>
       <c r="F37">
-        <v>57.575</v>
+        <v>59.22000000000001</v>
       </c>
       <c r="G37">
         <v>1.44</v>
@@ -4315,37 +4315,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M37">
-        <v>13.576185</v>
+        <v>13.964076</v>
       </c>
       <c r="N37">
-        <v>-7.942851666666667</v>
+        <v>-8.330742666666669</v>
       </c>
       <c r="O37">
-        <v>-0.7942851666666667</v>
+        <v>-0.833074266666667</v>
       </c>
       <c r="P37">
-        <v>-7.1485665</v>
+        <v>-7.497668400000002</v>
       </c>
       <c r="Q37">
-        <v>-3.6985665</v>
+        <v>-4.047668400000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.115457972396558</v>
+        <v>0.1165463782152542</v>
       </c>
       <c r="T37">
-        <v>1.077586679084832</v>
+        <v>1.094423970945533</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04149422929441027</v>
+        <v>0.04034161181400999</v>
       </c>
       <c r="W37">
-        <v>0.2260156607323781</v>
+        <v>0.2262874479342565</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4149422929441028</v>
+        <v>0.4034161181400998</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.156053163314095</v>
+        <v>0.157953163314095</v>
       </c>
       <c r="C38">
-        <v>31.8486510351126</v>
+        <v>28.68524146078975</v>
       </c>
       <c r="D38">
-        <v>89.6286510351126</v>
+        <v>88.11024146078975</v>
       </c>
       <c r="E38">
-        <v>-92.68000000000001</v>
+        <v>-91.035</v>
       </c>
       <c r="F38">
-        <v>59.22</v>
+        <v>60.865</v>
       </c>
       <c r="G38">
         <v>1.44</v>
@@ -4397,37 +4397,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M38">
-        <v>13.964076</v>
+        <v>14.351967</v>
       </c>
       <c r="N38">
-        <v>-8.330742666666666</v>
+        <v>-8.718633666666669</v>
       </c>
       <c r="O38">
-        <v>-0.8330742666666666</v>
+        <v>-0.871863366666667</v>
       </c>
       <c r="P38">
-        <v>-7.497668399999999</v>
+        <v>-7.846770300000002</v>
       </c>
       <c r="Q38">
-        <v>-4.047668399999999</v>
+        <v>-4.396770300000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1165463782152542</v>
+        <v>0.1176693365996233</v>
       </c>
       <c r="T38">
-        <v>1.094423970945532</v>
+        <v>1.11179578000816</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04034161181401</v>
+        <v>0.03925129798119891</v>
       </c>
       <c r="W38">
-        <v>0.2262874479342565</v>
+        <v>0.2265445439360333</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4034161181400999</v>
+        <v>0.392512979811989</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.157953163314095</v>
+        <v>0.159853163314095</v>
       </c>
       <c r="C39">
-        <v>28.68524146078975</v>
+        <v>25.57242194652985</v>
       </c>
       <c r="D39">
-        <v>88.11024146078975</v>
+        <v>86.64242194652985</v>
       </c>
       <c r="E39">
-        <v>-91.035</v>
+        <v>-89.39000000000001</v>
       </c>
       <c r="F39">
-        <v>60.865</v>
+        <v>62.51</v>
       </c>
       <c r="G39">
         <v>1.44</v>
@@ -4479,37 +4479,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M39">
-        <v>14.351967</v>
+        <v>14.739858</v>
       </c>
       <c r="N39">
-        <v>-8.718633666666669</v>
+        <v>-9.106524666666665</v>
       </c>
       <c r="O39">
-        <v>-0.871863366666667</v>
+        <v>-0.9106524666666665</v>
       </c>
       <c r="P39">
-        <v>-7.846770300000002</v>
+        <v>-8.195872199999998</v>
       </c>
       <c r="Q39">
-        <v>-4.396770300000002</v>
+        <v>-4.745872199999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1176693365996233</v>
+        <v>0.1188285194480043</v>
       </c>
       <c r="T39">
-        <v>1.11179578000816</v>
+        <v>1.129727970008292</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03925129798119891</v>
+        <v>0.03821836908695683</v>
       </c>
       <c r="W39">
-        <v>0.2265445439360333</v>
+        <v>0.2267881085692956</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.392512979811989</v>
+        <v>0.3821836908695684</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.159853163314095</v>
+        <v>0.161753163314095</v>
       </c>
       <c r="C40">
-        <v>25.57242194652985</v>
+        <v>22.50770559733046</v>
       </c>
       <c r="D40">
-        <v>86.64242194652985</v>
+        <v>85.22270559733046</v>
       </c>
       <c r="E40">
-        <v>-89.39000000000001</v>
+        <v>-87.745</v>
       </c>
       <c r="F40">
-        <v>62.51</v>
+        <v>64.155</v>
       </c>
       <c r="G40">
         <v>1.44</v>
@@ -4561,37 +4561,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M40">
-        <v>14.739858</v>
+        <v>15.127749</v>
       </c>
       <c r="N40">
-        <v>-9.106524666666665</v>
+        <v>-9.494415666666669</v>
       </c>
       <c r="O40">
-        <v>-0.9106524666666665</v>
+        <v>-0.9494415666666669</v>
       </c>
       <c r="P40">
-        <v>-8.195872199999998</v>
+        <v>-8.544974100000001</v>
       </c>
       <c r="Q40">
-        <v>-4.745872199999998</v>
+        <v>-5.094974100000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1188285194480043</v>
+        <v>0.1200257082914142</v>
       </c>
       <c r="T40">
-        <v>1.129727970008292</v>
+        <v>1.148248100664165</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03821836908695683</v>
+        <v>0.03723841090523999</v>
       </c>
       <c r="W40">
-        <v>0.2267881085692956</v>
+        <v>0.2270191827085444</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3821836908695684</v>
+        <v>0.3723841090523998</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.161753163314095</v>
+        <v>0.163653163314095</v>
       </c>
       <c r="C41">
-        <v>22.50770559733046</v>
+        <v>19.48876589065172</v>
       </c>
       <c r="D41">
-        <v>85.22270559733046</v>
+        <v>83.84876589065172</v>
       </c>
       <c r="E41">
-        <v>-87.745</v>
+        <v>-86.10000000000001</v>
       </c>
       <c r="F41">
-        <v>64.155</v>
+        <v>65.8</v>
       </c>
       <c r="G41">
         <v>1.44</v>
@@ -4643,37 +4643,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M41">
-        <v>15.127749</v>
+        <v>15.51564</v>
       </c>
       <c r="N41">
-        <v>-9.494415666666669</v>
+        <v>-9.882306666666665</v>
       </c>
       <c r="O41">
-        <v>-0.9494415666666669</v>
+        <v>-0.9882306666666665</v>
       </c>
       <c r="P41">
-        <v>-8.544974100000001</v>
+        <v>-8.894075999999998</v>
       </c>
       <c r="Q41">
-        <v>-5.094974100000001</v>
+        <v>-5.444075999999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1200257082914142</v>
+        <v>0.1212628034296045</v>
       </c>
       <c r="T41">
-        <v>1.148248100664165</v>
+        <v>1.167385569008568</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03723841090523999</v>
+        <v>0.036307450632609</v>
       </c>
       <c r="W41">
-        <v>0.2270191827085444</v>
+        <v>0.2272387031408308</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3723841090523998</v>
+        <v>0.36307450632609</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.163653163314095</v>
+        <v>0.165553163314095</v>
       </c>
       <c r="C42">
-        <v>19.48876589065172</v>
+        <v>16.51342395409358</v>
       </c>
       <c r="D42">
-        <v>83.84876589065172</v>
+        <v>82.51842395409359</v>
       </c>
       <c r="E42">
-        <v>-86.10000000000001</v>
+        <v>-84.455</v>
       </c>
       <c r="F42">
-        <v>65.8</v>
+        <v>67.44500000000001</v>
       </c>
       <c r="G42">
         <v>1.44</v>
@@ -4725,37 +4725,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M42">
-        <v>15.51564</v>
+        <v>15.903531</v>
       </c>
       <c r="N42">
-        <v>-9.882306666666665</v>
+        <v>-10.27019766666667</v>
       </c>
       <c r="O42">
-        <v>-0.9882306666666665</v>
+        <v>-1.027019766666667</v>
       </c>
       <c r="P42">
-        <v>-8.894075999999998</v>
+        <v>-9.243177900000001</v>
       </c>
       <c r="Q42">
-        <v>-5.444075999999998</v>
+        <v>-5.793177900000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1212628034296045</v>
+        <v>0.1225418339962079</v>
       </c>
       <c r="T42">
-        <v>1.167385569008568</v>
+        <v>1.187171765093459</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.036307450632609</v>
+        <v>0.03542190305620389</v>
       </c>
       <c r="W42">
-        <v>0.2272387031408308</v>
+        <v>0.2274475152593471</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.36307450632609</v>
+        <v>0.354219030562039</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.165553163314095</v>
+        <v>0.167453163314095</v>
       </c>
       <c r="C43">
-        <v>16.51342395409358</v>
+        <v>13.5796370352695</v>
       </c>
       <c r="D43">
-        <v>82.51842395409359</v>
+        <v>81.2296370352695</v>
       </c>
       <c r="E43">
-        <v>-84.455</v>
+        <v>-82.81</v>
       </c>
       <c r="F43">
-        <v>67.44500000000001</v>
+        <v>69.09</v>
       </c>
       <c r="G43">
         <v>1.44</v>
@@ -4807,37 +4807,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M43">
-        <v>15.903531</v>
+        <v>16.291422</v>
       </c>
       <c r="N43">
-        <v>-10.27019766666667</v>
+        <v>-10.65808866666667</v>
       </c>
       <c r="O43">
-        <v>-1.027019766666667</v>
+        <v>-1.065808866666667</v>
       </c>
       <c r="P43">
-        <v>-9.243177900000001</v>
+        <v>-9.592279800000002</v>
       </c>
       <c r="Q43">
-        <v>-5.793177900000001</v>
+        <v>-6.142279800000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1225418339962079</v>
+        <v>0.1238649690651081</v>
       </c>
       <c r="T43">
-        <v>1.187171765093459</v>
+        <v>1.207640243801967</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03542190305620389</v>
+        <v>0.03457852441200856</v>
       </c>
       <c r="W43">
-        <v>0.2274475152593471</v>
+        <v>0.2276463839436484</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.354219030562039</v>
+        <v>0.3457852441200856</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.167453163314095</v>
+        <v>0.169353163314095</v>
       </c>
       <c r="C44">
-        <v>13.5796370352695</v>
+        <v>10.68548803554165</v>
       </c>
       <c r="D44">
-        <v>81.2296370352695</v>
+        <v>79.98048803554165</v>
       </c>
       <c r="E44">
-        <v>-82.81</v>
+        <v>-81.16500000000001</v>
       </c>
       <c r="F44">
-        <v>69.09</v>
+        <v>70.735</v>
       </c>
       <c r="G44">
         <v>1.44</v>
@@ -4889,37 +4889,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M44">
-        <v>16.291422</v>
+        <v>16.679313</v>
       </c>
       <c r="N44">
-        <v>-10.65808866666667</v>
+        <v>-11.04597966666667</v>
       </c>
       <c r="O44">
-        <v>-1.065808866666667</v>
+        <v>-1.104597966666667</v>
       </c>
       <c r="P44">
-        <v>-9.592279800000002</v>
+        <v>-9.941381700000001</v>
       </c>
       <c r="Q44">
-        <v>-6.142279800000002</v>
+        <v>-6.491381700000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1238649690651081</v>
+        <v>0.1252345299258994</v>
       </c>
       <c r="T44">
-        <v>1.207640243801967</v>
+        <v>1.228826914745861</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03457852441200856</v>
+        <v>0.03377437268149674</v>
       </c>
       <c r="W44">
-        <v>0.2276463839436484</v>
+        <v>0.2278360029217031</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3457852441200856</v>
+        <v>0.3377437268149673</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.169353163314095</v>
+        <v>0.171253163314095</v>
       </c>
       <c r="C45">
-        <v>10.68548803554165</v>
+        <v>7.829175994831573</v>
       </c>
       <c r="D45">
-        <v>79.98048803554165</v>
+        <v>78.76917599483157</v>
       </c>
       <c r="E45">
-        <v>-81.16500000000001</v>
+        <v>-79.52000000000001</v>
       </c>
       <c r="F45">
-        <v>70.735</v>
+        <v>72.38</v>
       </c>
       <c r="G45">
         <v>1.44</v>
@@ -4971,37 +4971,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M45">
-        <v>16.679313</v>
+        <v>17.067204</v>
       </c>
       <c r="N45">
-        <v>-11.04597966666667</v>
+        <v>-11.43387066666667</v>
       </c>
       <c r="O45">
-        <v>-1.104597966666667</v>
+        <v>-1.143387066666667</v>
       </c>
       <c r="P45">
-        <v>-9.941381700000001</v>
+        <v>-10.2904836</v>
       </c>
       <c r="Q45">
-        <v>-6.491381700000001</v>
+        <v>-6.8404836</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1252345299258994</v>
+        <v>0.1266530036745762</v>
       </c>
       <c r="T45">
-        <v>1.228826914745861</v>
+        <v>1.25077025250918</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03377437268149674</v>
+        <v>0.03300677330237181</v>
       </c>
       <c r="W45">
-        <v>0.2278360029217031</v>
+        <v>0.2280170028553007</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3377437268149673</v>
+        <v>0.3300677330237181</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.171253163314095</v>
+        <v>0.173153163314095</v>
       </c>
       <c r="C46">
-        <v>7.829175994831573</v>
+        <v>5.009007428181476</v>
       </c>
       <c r="D46">
-        <v>78.76917599483157</v>
+        <v>77.59400742818148</v>
       </c>
       <c r="E46">
-        <v>-79.52000000000001</v>
+        <v>-77.875</v>
       </c>
       <c r="F46">
-        <v>72.38</v>
+        <v>74.02500000000001</v>
       </c>
       <c r="G46">
         <v>1.44</v>
@@ -5053,37 +5053,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M46">
-        <v>17.067204</v>
+        <v>17.455095</v>
       </c>
       <c r="N46">
-        <v>-11.43387066666667</v>
+        <v>-11.82176166666667</v>
       </c>
       <c r="O46">
-        <v>-1.143387066666667</v>
+        <v>-1.182176166666667</v>
       </c>
       <c r="P46">
-        <v>-10.2904836</v>
+        <v>-10.6395855</v>
       </c>
       <c r="Q46">
-        <v>-6.8404836</v>
+        <v>-7.189585500000004</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1266530036745762</v>
+        <v>0.1281230582868412</v>
       </c>
       <c r="T46">
-        <v>1.25077025250918</v>
+        <v>1.273511529827529</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03300677330237181</v>
+        <v>0.03227328945120799</v>
       </c>
       <c r="W46">
-        <v>0.2280170028553007</v>
+        <v>0.2281899583474052</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3300677330237181</v>
+        <v>0.3227328945120798</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.173153163314095</v>
+        <v>0.175053163314095</v>
       </c>
       <c r="C47">
-        <v>5.009007428181476</v>
+        <v>2.223388426422275</v>
       </c>
       <c r="D47">
-        <v>77.59400742818148</v>
+        <v>76.45338842642228</v>
       </c>
       <c r="E47">
-        <v>-77.875</v>
+        <v>-76.23</v>
       </c>
       <c r="F47">
-        <v>74.02500000000001</v>
+        <v>75.67</v>
       </c>
       <c r="G47">
         <v>1.44</v>
@@ -5135,37 +5135,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M47">
-        <v>17.455095</v>
+        <v>17.842986</v>
       </c>
       <c r="N47">
-        <v>-11.82176166666667</v>
+        <v>-12.20965266666667</v>
       </c>
       <c r="O47">
-        <v>-1.182176166666667</v>
+        <v>-1.220965266666667</v>
       </c>
       <c r="P47">
-        <v>-10.6395855</v>
+        <v>-10.9886874</v>
       </c>
       <c r="Q47">
-        <v>-7.189585500000004</v>
+        <v>-7.5386874</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1281230582868412</v>
+        <v>0.1296475593662272</v>
       </c>
       <c r="T47">
-        <v>1.273511529827529</v>
+        <v>1.297095076676186</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03227328945120799</v>
+        <v>0.03157169620226869</v>
       </c>
       <c r="W47">
-        <v>0.2281899583474052</v>
+        <v>0.228355394035505</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3227328945120798</v>
+        <v>0.3157169620226868</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.175053163314095</v>
+        <v>0.176953163314095</v>
       </c>
       <c r="C48">
-        <v>2.223388426422275</v>
+        <v>-0.5291825565384585</v>
       </c>
       <c r="D48">
-        <v>76.45338842642228</v>
+        <v>75.34581744346154</v>
       </c>
       <c r="E48">
-        <v>-76.23</v>
+        <v>-74.58500000000001</v>
       </c>
       <c r="F48">
-        <v>75.67</v>
+        <v>77.315</v>
       </c>
       <c r="G48">
         <v>1.44</v>
@@ -5217,37 +5217,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M48">
-        <v>17.842986</v>
+        <v>18.230877</v>
       </c>
       <c r="N48">
-        <v>-12.20965266666667</v>
+        <v>-12.59754366666667</v>
       </c>
       <c r="O48">
-        <v>-1.220965266666667</v>
+        <v>-1.259754366666667</v>
       </c>
       <c r="P48">
-        <v>-10.9886874</v>
+        <v>-11.3377893</v>
       </c>
       <c r="Q48">
-        <v>-7.5386874</v>
+        <v>-7.887789300000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1296475593662272</v>
+        <v>0.1312295887882315</v>
       </c>
       <c r="T48">
-        <v>1.297095076676186</v>
+        <v>1.321568568688945</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03157169620226869</v>
+        <v>0.03089995798519915</v>
       </c>
       <c r="W48">
-        <v>0.228355394035505</v>
+        <v>0.22851378990709</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3157169620226868</v>
+        <v>0.3089995798519913</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.176953163314095</v>
+        <v>0.178853163314095</v>
       </c>
       <c r="C49">
-        <v>-0.5291825565384585</v>
+        <v>-3.250121298442949</v>
       </c>
       <c r="D49">
-        <v>75.34581744346154</v>
+        <v>74.26987870155706</v>
       </c>
       <c r="E49">
-        <v>-74.58500000000001</v>
+        <v>-72.94</v>
       </c>
       <c r="F49">
-        <v>77.315</v>
+        <v>78.96000000000001</v>
       </c>
       <c r="G49">
         <v>1.44</v>
@@ -5299,37 +5299,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M49">
-        <v>18.230877</v>
+        <v>18.618768</v>
       </c>
       <c r="N49">
-        <v>-12.59754366666667</v>
+        <v>-12.98543466666667</v>
       </c>
       <c r="O49">
-        <v>-1.259754366666667</v>
+        <v>-1.298543466666667</v>
       </c>
       <c r="P49">
-        <v>-11.3377893</v>
+        <v>-11.6868912</v>
       </c>
       <c r="Q49">
-        <v>-7.887789300000001</v>
+        <v>-8.236891200000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1312295887882315</v>
+        <v>0.1328724654956975</v>
       </c>
       <c r="T49">
-        <v>1.321568568688945</v>
+        <v>1.34698334885604</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03089995798519915</v>
+        <v>0.03025620886050749</v>
       </c>
       <c r="W49">
-        <v>0.22851378990709</v>
+        <v>0.2286655859506923</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3089995798519913</v>
+        <v>0.3025620886050748</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.178853163314095</v>
+        <v>0.180753163314095</v>
       </c>
       <c r="C50">
-        <v>-3.250121298442934</v>
+        <v>-5.940763846328451</v>
       </c>
       <c r="D50">
-        <v>74.26987870155706</v>
+        <v>73.22423615367155</v>
       </c>
       <c r="E50">
-        <v>-72.94000000000001</v>
+        <v>-71.295</v>
       </c>
       <c r="F50">
-        <v>78.95999999999999</v>
+        <v>80.605</v>
       </c>
       <c r="G50">
         <v>1.44</v>
@@ -5381,37 +5381,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M50">
-        <v>18.618768</v>
+        <v>19.006659</v>
       </c>
       <c r="N50">
-        <v>-12.98543466666667</v>
+        <v>-13.37332566666667</v>
       </c>
       <c r="O50">
-        <v>-1.298543466666667</v>
+        <v>-1.337332566666667</v>
       </c>
       <c r="P50">
-        <v>-11.6868912</v>
+        <v>-12.0359931</v>
       </c>
       <c r="Q50">
-        <v>-8.236891199999999</v>
+        <v>-8.585993100000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1328724654956975</v>
+        <v>0.1345797687407111</v>
       </c>
       <c r="T50">
-        <v>1.34698334885604</v>
+        <v>1.373394787068903</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03025620886050749</v>
+        <v>0.02963873521029305</v>
       </c>
       <c r="W50">
-        <v>0.2286655859506923</v>
+        <v>0.2288111862374129</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3025620886050749</v>
+        <v>0.2963873521029304</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.180753163314095</v>
+        <v>0.182653163314095</v>
       </c>
       <c r="C51">
-        <v>-5.940763846328451</v>
+        <v>-8.602372051230972</v>
       </c>
       <c r="D51">
-        <v>73.22423615367155</v>
+        <v>72.20762794876903</v>
       </c>
       <c r="E51">
-        <v>-71.295</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="F51">
-        <v>80.605</v>
+        <v>82.25</v>
       </c>
       <c r="G51">
         <v>1.44</v>
@@ -5463,37 +5463,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M51">
-        <v>19.006659</v>
+        <v>19.39455</v>
       </c>
       <c r="N51">
-        <v>-13.37332566666667</v>
+        <v>-13.76121666666667</v>
       </c>
       <c r="O51">
-        <v>-1.337332566666667</v>
+        <v>-1.376121666666667</v>
       </c>
       <c r="P51">
-        <v>-12.0359931</v>
+        <v>-12.385095</v>
       </c>
       <c r="Q51">
-        <v>-8.585993100000003</v>
+        <v>-8.935095000000004</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1345797687407111</v>
+        <v>0.1363553641155254</v>
       </c>
       <c r="T51">
-        <v>1.373394787068903</v>
+        <v>1.400862682810281</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02963873521029305</v>
+        <v>0.02904596050608719</v>
       </c>
       <c r="W51">
-        <v>0.2288111862374129</v>
+        <v>0.2289509625126646</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2963873521029304</v>
+        <v>0.2904596050608719</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.182653163314095</v>
+        <v>0.184553163314095</v>
       </c>
       <c r="C52">
-        <v>-8.602372051230972</v>
+        <v>-11.236138648156</v>
       </c>
       <c r="D52">
-        <v>72.20762794876903</v>
+        <v>71.218861351844</v>
       </c>
       <c r="E52">
-        <v>-69.65000000000001</v>
+        <v>-68.00500000000001</v>
       </c>
       <c r="F52">
-        <v>82.25</v>
+        <v>83.895</v>
       </c>
       <c r="G52">
         <v>1.44</v>
@@ -5545,37 +5545,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M52">
-        <v>19.39455</v>
+        <v>19.782441</v>
       </c>
       <c r="N52">
-        <v>-13.76121666666667</v>
+        <v>-14.14910766666667</v>
       </c>
       <c r="O52">
-        <v>-1.376121666666667</v>
+        <v>-1.414910766666667</v>
       </c>
       <c r="P52">
-        <v>-12.385095</v>
+        <v>-12.7341969</v>
       </c>
       <c r="Q52">
-        <v>-8.935095000000004</v>
+        <v>-9.284196899999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1363553641155254</v>
+        <v>0.1382034327709442</v>
       </c>
       <c r="T52">
-        <v>1.400862682810281</v>
+        <v>1.429451717153348</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02904596050608719</v>
+        <v>0.02847643186871294</v>
       </c>
       <c r="W52">
-        <v>0.2289509625126646</v>
+        <v>0.2290852573653575</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2904596050608719</v>
+        <v>0.2847643186871294</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.184553163314095</v>
+        <v>0.186453163314095</v>
       </c>
       <c r="C53">
-        <v>-11.236138648156</v>
+        <v>-13.84319192431538</v>
       </c>
       <c r="D53">
-        <v>71.218861351844</v>
+        <v>70.25680807568463</v>
       </c>
       <c r="E53">
-        <v>-68.00500000000001</v>
+        <v>-66.36</v>
       </c>
       <c r="F53">
-        <v>83.895</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="G53">
         <v>1.44</v>
@@ -5627,37 +5627,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M53">
-        <v>19.782441</v>
+        <v>20.170332</v>
       </c>
       <c r="N53">
-        <v>-14.14910766666667</v>
+        <v>-14.53699866666667</v>
       </c>
       <c r="O53">
-        <v>-1.414910766666667</v>
+        <v>-1.453699866666667</v>
       </c>
       <c r="P53">
-        <v>-12.7341969</v>
+        <v>-13.0832988</v>
       </c>
       <c r="Q53">
-        <v>-9.284196899999998</v>
+        <v>-9.633298800000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1382034327709442</v>
+        <v>0.1401285042870056</v>
       </c>
       <c r="T53">
-        <v>1.429451717153348</v>
+        <v>1.45923196126071</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02847643186871294</v>
+        <v>0.02792880817893</v>
       </c>
       <c r="W53">
-        <v>0.2290852573653575</v>
+        <v>0.2292143870314083</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2847643186871294</v>
+        <v>0.2792880817892999</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.186453163314095</v>
+        <v>0.188353163314095</v>
       </c>
       <c r="C54">
-        <v>-13.84319192431538</v>
+        <v>-16.42460001404451</v>
       </c>
       <c r="D54">
-        <v>70.25680807568463</v>
+        <v>69.32039998595549</v>
       </c>
       <c r="E54">
-        <v>-66.36</v>
+        <v>-64.715</v>
       </c>
       <c r="F54">
-        <v>85.54000000000001</v>
+        <v>87.185</v>
       </c>
       <c r="G54">
         <v>1.44</v>
@@ -5709,37 +5709,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M54">
-        <v>20.170332</v>
+        <v>20.558223</v>
       </c>
       <c r="N54">
-        <v>-14.53699866666667</v>
+        <v>-14.92488966666667</v>
       </c>
       <c r="O54">
-        <v>-1.453699866666667</v>
+        <v>-1.492488966666667</v>
       </c>
       <c r="P54">
-        <v>-13.0832988</v>
+        <v>-13.4324007</v>
       </c>
       <c r="Q54">
-        <v>-9.633298800000002</v>
+        <v>-9.982400700000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1401285042870056</v>
+        <v>0.1421354937399206</v>
       </c>
       <c r="T54">
-        <v>1.45923196126071</v>
+        <v>1.490279449798172</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02792880817893</v>
+        <v>0.02740184953404452</v>
       </c>
       <c r="W54">
-        <v>0.2292143870314083</v>
+        <v>0.2293386438798723</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2792880817892999</v>
+        <v>0.2740184953404452</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.188353163314095</v>
+        <v>0.190253163314095</v>
       </c>
       <c r="C55">
-        <v>-16.42460001404451</v>
+        <v>-18.98137485477221</v>
       </c>
       <c r="D55">
-        <v>69.32039998595549</v>
+        <v>68.4086251452278</v>
       </c>
       <c r="E55">
-        <v>-64.715</v>
+        <v>-63.06999999999999</v>
       </c>
       <c r="F55">
-        <v>87.185</v>
+        <v>88.83000000000001</v>
       </c>
       <c r="G55">
         <v>1.44</v>
@@ -5791,37 +5791,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M55">
-        <v>20.558223</v>
+        <v>20.94611400000001</v>
       </c>
       <c r="N55">
-        <v>-14.92488966666667</v>
+        <v>-15.31278066666667</v>
       </c>
       <c r="O55">
-        <v>-1.492488966666667</v>
+        <v>-1.531278066666667</v>
       </c>
       <c r="P55">
-        <v>-13.4324007</v>
+        <v>-13.7815026</v>
       </c>
       <c r="Q55">
-        <v>-9.982400700000003</v>
+        <v>-10.3315026</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1421354937399206</v>
+        <v>0.1442297436038319</v>
       </c>
       <c r="T55">
-        <v>1.490279449798172</v>
+        <v>1.52267682914161</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02740184953404452</v>
+        <v>0.02689440787600665</v>
       </c>
       <c r="W55">
-        <v>0.2293386438798723</v>
+        <v>0.2294582986228376</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2740184953404452</v>
+        <v>0.2689440787600665</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.190253163314095</v>
+        <v>0.192153163314095</v>
       </c>
       <c r="C56">
-        <v>-18.98137485477221</v>
+        <v>-21.51447583484453</v>
       </c>
       <c r="D56">
-        <v>68.4086251452278</v>
+        <v>67.52052416515548</v>
       </c>
       <c r="E56">
-        <v>-63.06999999999999</v>
+        <v>-61.425</v>
       </c>
       <c r="F56">
-        <v>88.83000000000001</v>
+        <v>90.47500000000001</v>
       </c>
       <c r="G56">
         <v>1.44</v>
@@ -5873,37 +5873,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M56">
-        <v>20.94611400000001</v>
+        <v>21.334005</v>
       </c>
       <c r="N56">
-        <v>-15.31278066666667</v>
+        <v>-15.70067166666667</v>
       </c>
       <c r="O56">
-        <v>-1.531278066666667</v>
+        <v>-1.570067166666667</v>
       </c>
       <c r="P56">
-        <v>-13.7815026</v>
+        <v>-14.1306045</v>
       </c>
       <c r="Q56">
-        <v>-10.3315026</v>
+        <v>-10.6806045</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1442297436038319</v>
+        <v>0.1464170712394726</v>
       </c>
       <c r="T56">
-        <v>1.52267682914161</v>
+        <v>1.556514092011424</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02689440787600665</v>
+        <v>0.02640541864189745</v>
       </c>
       <c r="W56">
-        <v>0.2294582986228376</v>
+        <v>0.2295736022842406</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2689440787600665</v>
+        <v>0.2640541864189744</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.192153163314095</v>
+        <v>0.194053163314095</v>
       </c>
       <c r="C57">
-        <v>-21.51447583484453</v>
+        <v>-24.02481316084814</v>
       </c>
       <c r="D57">
-        <v>67.52052416515548</v>
+        <v>66.65518683915187</v>
       </c>
       <c r="E57">
-        <v>-61.425</v>
+        <v>-59.78</v>
       </c>
       <c r="F57">
-        <v>90.47500000000001</v>
+        <v>92.12</v>
       </c>
       <c r="G57">
         <v>1.44</v>
@@ -5955,37 +5955,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M57">
-        <v>21.334005</v>
+        <v>21.721896</v>
       </c>
       <c r="N57">
-        <v>-15.70067166666667</v>
+        <v>-16.08856266666667</v>
       </c>
       <c r="O57">
-        <v>-1.570067166666667</v>
+        <v>-1.608856266666667</v>
       </c>
       <c r="P57">
-        <v>-14.1306045</v>
+        <v>-14.4797064</v>
       </c>
       <c r="Q57">
-        <v>-10.6806045</v>
+        <v>-11.0297064</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1464170712394726</v>
+        <v>0.1487038228585515</v>
       </c>
       <c r="T57">
-        <v>1.556514092011424</v>
+        <v>1.591889412284411</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02640541864189745</v>
+        <v>0.02593389330900642</v>
       </c>
       <c r="W57">
-        <v>0.2295736022842406</v>
+        <v>0.2296847879577363</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2640541864189744</v>
+        <v>0.2593389330900642</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.194053163314095</v>
+        <v>0.195953163314095</v>
       </c>
       <c r="C58">
-        <v>-24.02481316084814</v>
+        <v>-26.51325096927758</v>
       </c>
       <c r="D58">
-        <v>66.65518683915187</v>
+        <v>65.81174903072244</v>
       </c>
       <c r="E58">
-        <v>-59.78</v>
+        <v>-58.13499999999999</v>
       </c>
       <c r="F58">
-        <v>92.12</v>
+        <v>93.76500000000001</v>
       </c>
       <c r="G58">
         <v>1.44</v>
@@ -6037,37 +6037,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M58">
-        <v>21.721896</v>
+        <v>22.109787</v>
       </c>
       <c r="N58">
-        <v>-16.08856266666667</v>
+        <v>-16.47645366666667</v>
       </c>
       <c r="O58">
-        <v>-1.608856266666667</v>
+        <v>-1.647645366666667</v>
       </c>
       <c r="P58">
-        <v>-14.4797064</v>
+        <v>-14.8288083</v>
       </c>
       <c r="Q58">
-        <v>-11.0297064</v>
+        <v>-11.3788083</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1487038228585515</v>
+        <v>0.1510969350180528</v>
       </c>
       <c r="T58">
-        <v>1.591889412284411</v>
+        <v>1.628910096291025</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02593389330900642</v>
+        <v>0.02547891272463789</v>
       </c>
       <c r="W58">
-        <v>0.2296847879577363</v>
+        <v>0.2297920723795304</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2593389330900642</v>
+        <v>0.2547891272463788</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.195953163314095</v>
+        <v>0.197853163314095</v>
       </c>
       <c r="C59">
-        <v>-26.51325096927758</v>
+        <v>-28.98061020490935</v>
       </c>
       <c r="D59">
-        <v>65.81174903072244</v>
+        <v>64.98938979509066</v>
       </c>
       <c r="E59">
-        <v>-58.13499999999999</v>
+        <v>-56.48999999999999</v>
       </c>
       <c r="F59">
-        <v>93.76500000000001</v>
+        <v>95.41000000000001</v>
       </c>
       <c r="G59">
         <v>1.44</v>
@@ -6119,37 +6119,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M59">
-        <v>22.109787</v>
+        <v>22.497678</v>
       </c>
       <c r="N59">
-        <v>-16.47645366666667</v>
+        <v>-16.86434466666667</v>
       </c>
       <c r="O59">
-        <v>-1.647645366666667</v>
+        <v>-1.686434466666667</v>
       </c>
       <c r="P59">
-        <v>-14.8288083</v>
+        <v>-15.1779102</v>
       </c>
       <c r="Q59">
-        <v>-11.3788083</v>
+        <v>-11.7279102</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1510969350180528</v>
+        <v>0.153604004899435</v>
       </c>
       <c r="T59">
-        <v>1.628910096291025</v>
+        <v>1.66769367001224</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02547891272463789</v>
+        <v>0.02503962112593723</v>
       </c>
       <c r="W59">
-        <v>0.2297920723795304</v>
+        <v>0.229895657338504</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2547891272463788</v>
+        <v>0.2503962112593723</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.197853163314095</v>
+        <v>0.199753163314095</v>
       </c>
       <c r="C60">
-        <v>-28.98061020490934</v>
+        <v>-31.42767128603666</v>
       </c>
       <c r="D60">
-        <v>64.98938979509066</v>
+        <v>64.18732871396334</v>
       </c>
       <c r="E60">
-        <v>-56.49000000000001</v>
+        <v>-54.84500000000001</v>
       </c>
       <c r="F60">
-        <v>95.41</v>
+        <v>97.05499999999999</v>
       </c>
       <c r="G60">
         <v>1.44</v>
@@ -6201,37 +6201,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M60">
-        <v>22.497678</v>
+        <v>22.885569</v>
       </c>
       <c r="N60">
-        <v>-16.86434466666667</v>
+        <v>-17.25223566666667</v>
       </c>
       <c r="O60">
-        <v>-1.686434466666667</v>
+        <v>-1.725223566666667</v>
       </c>
       <c r="P60">
-        <v>-15.1779102</v>
+        <v>-15.5270121</v>
       </c>
       <c r="Q60">
-        <v>-11.7279102</v>
+        <v>-12.0770121</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1536040048994349</v>
+        <v>0.1562333708725919</v>
       </c>
       <c r="T60">
-        <v>1.667693670012239</v>
+        <v>1.708369125378392</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02503962112593723</v>
+        <v>0.0246152207678705</v>
       </c>
       <c r="W60">
-        <v>0.229895657338504</v>
+        <v>0.2299957309429362</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2503962112593723</v>
+        <v>0.2461522076787049</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.199753163314095</v>
+        <v>0.201653163314095</v>
       </c>
       <c r="C61">
-        <v>-31.42767128603666</v>
+        <v>-33.8551765747535</v>
       </c>
       <c r="D61">
-        <v>64.18732871396334</v>
+        <v>63.40482342524651</v>
       </c>
       <c r="E61">
-        <v>-54.84500000000001</v>
+        <v>-53.2</v>
       </c>
       <c r="F61">
-        <v>97.05499999999999</v>
+        <v>98.7</v>
       </c>
       <c r="G61">
         <v>1.44</v>
@@ -6283,37 +6283,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M61">
-        <v>22.885569</v>
+        <v>23.27346</v>
       </c>
       <c r="N61">
-        <v>-17.25223566666667</v>
+        <v>-17.64012666666667</v>
       </c>
       <c r="O61">
-        <v>-1.725223566666667</v>
+        <v>-1.764012666666667</v>
       </c>
       <c r="P61">
-        <v>-15.5270121</v>
+        <v>-15.876114</v>
       </c>
       <c r="Q61">
-        <v>-12.0770121</v>
+        <v>-12.426114</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1562333708725919</v>
+        <v>0.1589942051444067</v>
       </c>
       <c r="T61">
-        <v>1.708369125378392</v>
+        <v>1.751078353512852</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0246152207678705</v>
+        <v>0.024204967088406</v>
       </c>
       <c r="W61">
-        <v>0.2299957309429362</v>
+        <v>0.2300924687605539</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2461522076787049</v>
+        <v>0.2420496708840599</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.201653163314095</v>
+        <v>0.203553163314095</v>
       </c>
       <c r="C62">
-        <v>-33.8551765747535</v>
+        <v>-36.26383266872423</v>
       </c>
       <c r="D62">
-        <v>63.40482342524651</v>
+        <v>62.64116733127576</v>
       </c>
       <c r="E62">
-        <v>-53.2</v>
+        <v>-51.55500000000001</v>
       </c>
       <c r="F62">
-        <v>98.7</v>
+        <v>100.345</v>
       </c>
       <c r="G62">
         <v>1.44</v>
@@ -6365,37 +6365,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M62">
-        <v>23.27346</v>
+        <v>23.661351</v>
       </c>
       <c r="N62">
-        <v>-17.64012666666667</v>
+        <v>-18.02801766666667</v>
       </c>
       <c r="O62">
-        <v>-1.764012666666667</v>
+        <v>-1.802801766666667</v>
       </c>
       <c r="P62">
-        <v>-15.876114</v>
+        <v>-16.2252159</v>
       </c>
       <c r="Q62">
-        <v>-12.426114</v>
+        <v>-12.7752159</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1589942051444067</v>
+        <v>0.1618966206609299</v>
       </c>
       <c r="T62">
-        <v>1.751078353512852</v>
+        <v>1.79597779847472</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.024204967088406</v>
+        <v>0.0238081643492518</v>
       </c>
       <c r="W62">
-        <v>0.2300924687605539</v>
+        <v>0.2301860348464464</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2420496708840599</v>
+        <v>0.2380816434925179</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.203553163314095</v>
+        <v>0.205453163314095</v>
       </c>
       <c r="C63">
-        <v>-36.26383266872423</v>
+        <v>-38.65431252930973</v>
       </c>
       <c r="D63">
-        <v>62.64116733127576</v>
+        <v>61.89568747069027</v>
       </c>
       <c r="E63">
-        <v>-51.55500000000001</v>
+        <v>-49.91000000000001</v>
       </c>
       <c r="F63">
-        <v>100.345</v>
+        <v>101.99</v>
       </c>
       <c r="G63">
         <v>1.44</v>
@@ -6447,37 +6447,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M63">
-        <v>23.661351</v>
+        <v>24.049242</v>
       </c>
       <c r="N63">
-        <v>-18.02801766666667</v>
+        <v>-18.41590866666667</v>
       </c>
       <c r="O63">
-        <v>-1.802801766666667</v>
+        <v>-1.841590866666667</v>
       </c>
       <c r="P63">
-        <v>-16.2252159</v>
+        <v>-16.5743178</v>
       </c>
       <c r="Q63">
-        <v>-12.7752159</v>
+        <v>-13.1243178</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1618966206609299</v>
+        <v>0.1649517948888491</v>
       </c>
       <c r="T63">
-        <v>1.79597779847472</v>
+        <v>1.843240372118791</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0238081643492518</v>
+        <v>0.02342416169845742</v>
       </c>
       <c r="W63">
-        <v>0.2301860348464464</v>
+        <v>0.2302765826715037</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2380816434925179</v>
+        <v>0.2342416169845741</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.205453163314095</v>
+        <v>0.207353163314095</v>
       </c>
       <c r="C64">
-        <v>-38.65431252930973</v>
+        <v>-41.02725745952238</v>
       </c>
       <c r="D64">
-        <v>61.89568747069027</v>
+        <v>61.16774254047763</v>
       </c>
       <c r="E64">
-        <v>-49.91000000000001</v>
+        <v>-48.265</v>
       </c>
       <c r="F64">
-        <v>101.99</v>
+        <v>103.635</v>
       </c>
       <c r="G64">
         <v>1.44</v>
@@ -6529,37 +6529,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M64">
-        <v>24.049242</v>
+        <v>24.437133</v>
       </c>
       <c r="N64">
-        <v>-18.41590866666667</v>
+        <v>-18.80379966666667</v>
       </c>
       <c r="O64">
-        <v>-1.841590866666667</v>
+        <v>-1.880379966666667</v>
       </c>
       <c r="P64">
-        <v>-16.5743178</v>
+        <v>-16.9234197</v>
       </c>
       <c r="Q64">
-        <v>-13.1243178</v>
+        <v>-13.4734197</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1649517948888491</v>
+        <v>0.1681721136696289</v>
       </c>
       <c r="T64">
-        <v>1.843240372118791</v>
+        <v>1.893057679473353</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02342416169845742</v>
+        <v>0.02305234960800571</v>
       </c>
       <c r="W64">
-        <v>0.2302765826715037</v>
+        <v>0.2303642559624323</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2342416169845741</v>
+        <v>0.2305234960800571</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.207353163314095</v>
+        <v>0.209253163314095</v>
       </c>
       <c r="C65">
-        <v>-41.02725745952238</v>
+        <v>-43.38327894402909</v>
       </c>
       <c r="D65">
-        <v>61.16774254047763</v>
+        <v>60.45672105597091</v>
       </c>
       <c r="E65">
-        <v>-48.265</v>
+        <v>-46.62</v>
       </c>
       <c r="F65">
-        <v>103.635</v>
+        <v>105.28</v>
       </c>
       <c r="G65">
         <v>1.44</v>
@@ -6611,37 +6611,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M65">
-        <v>24.437133</v>
+        <v>24.825024</v>
       </c>
       <c r="N65">
-        <v>-18.80379966666667</v>
+        <v>-19.19169066666667</v>
       </c>
       <c r="O65">
-        <v>-1.880379966666667</v>
+        <v>-1.919169066666667</v>
       </c>
       <c r="P65">
-        <v>-16.9234197</v>
+        <v>-17.2725216</v>
       </c>
       <c r="Q65">
-        <v>-13.4734197</v>
+        <v>-13.82252160000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1681721136696289</v>
+        <v>0.1715713390493408</v>
       </c>
       <c r="T65">
-        <v>1.893057679473353</v>
+        <v>1.94564261501428</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02305234960800571</v>
+        <v>0.02269215664538062</v>
       </c>
       <c r="W65">
-        <v>0.2303642559624323</v>
+        <v>0.2304491894630193</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2305234960800571</v>
+        <v>0.2269215664538061</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.209253163314095</v>
+        <v>0.211153163314095</v>
       </c>
       <c r="C66">
-        <v>-43.38327894402909</v>
+        <v>-45.72296036229835</v>
       </c>
       <c r="D66">
-        <v>60.45672105597091</v>
+        <v>59.76203963770165</v>
       </c>
       <c r="E66">
-        <v>-46.62</v>
+        <v>-44.97500000000001</v>
       </c>
       <c r="F66">
-        <v>105.28</v>
+        <v>106.925</v>
       </c>
       <c r="G66">
         <v>1.44</v>
@@ -6693,37 +6693,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M66">
-        <v>24.825024</v>
+        <v>25.212915</v>
       </c>
       <c r="N66">
-        <v>-19.19169066666667</v>
+        <v>-19.57958166666667</v>
       </c>
       <c r="O66">
-        <v>-1.919169066666667</v>
+        <v>-1.957958166666667</v>
       </c>
       <c r="P66">
-        <v>-17.2725216</v>
+        <v>-17.6216235</v>
       </c>
       <c r="Q66">
-        <v>-13.82252160000001</v>
+        <v>-14.1716235</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1715713390493408</v>
+        <v>0.175164805879322</v>
       </c>
       <c r="T66">
-        <v>1.94564261501428</v>
+        <v>2.001232404014688</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02269215664538062</v>
+        <v>0.022343046543144</v>
       </c>
       <c r="W66">
-        <v>0.2304491894630193</v>
+        <v>0.2305315096251266</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2269215664538061</v>
+        <v>0.22343046543144</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.211153163314095</v>
+        <v>0.213053163314095</v>
       </c>
       <c r="C67">
-        <v>-45.72296036229835</v>
+        <v>-48.04685858497888</v>
       </c>
       <c r="D67">
-        <v>59.76203963770165</v>
+        <v>59.08314141502113</v>
       </c>
       <c r="E67">
-        <v>-44.97500000000001</v>
+        <v>-43.33</v>
       </c>
       <c r="F67">
-        <v>106.925</v>
+        <v>108.57</v>
       </c>
       <c r="G67">
         <v>1.44</v>
@@ -6775,37 +6775,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M67">
-        <v>25.212915</v>
+        <v>25.600806</v>
       </c>
       <c r="N67">
-        <v>-19.57958166666667</v>
+        <v>-19.96747266666667</v>
       </c>
       <c r="O67">
-        <v>-1.957958166666667</v>
+        <v>-1.996747266666667</v>
       </c>
       <c r="P67">
-        <v>-17.6216235</v>
+        <v>-17.9707254</v>
       </c>
       <c r="Q67">
-        <v>-14.1716235</v>
+        <v>-14.5207254</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.175164805879322</v>
+        <v>0.1789696531110667</v>
       </c>
       <c r="T67">
-        <v>2.001232404014688</v>
+        <v>2.060092180603355</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.022343046543144</v>
+        <v>0.02200451553491454</v>
       </c>
       <c r="W67">
-        <v>0.2305315096251266</v>
+        <v>0.2306113352368672</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.22343046543144</v>
+        <v>0.2200451553491454</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.213053163314095</v>
+        <v>0.214953163314095</v>
       </c>
       <c r="C68">
-        <v>-48.04685858497888</v>
+        <v>-50.35550546269108</v>
       </c>
       <c r="D68">
-        <v>59.08314141502113</v>
+        <v>58.41949453730893</v>
       </c>
       <c r="E68">
-        <v>-43.33</v>
+        <v>-41.685</v>
       </c>
       <c r="F68">
-        <v>108.57</v>
+        <v>110.215</v>
       </c>
       <c r="G68">
         <v>1.44</v>
@@ -6857,37 +6857,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M68">
-        <v>25.600806</v>
+        <v>25.988697</v>
       </c>
       <c r="N68">
-        <v>-19.96747266666667</v>
+        <v>-20.35536366666667</v>
       </c>
       <c r="O68">
-        <v>-1.996747266666667</v>
+        <v>-2.035536366666667</v>
       </c>
       <c r="P68">
-        <v>-17.9707254</v>
+        <v>-18.3198273</v>
       </c>
       <c r="Q68">
-        <v>-14.5207254</v>
+        <v>-14.8698273</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1789696531110667</v>
+        <v>0.1830050971447354</v>
       </c>
       <c r="T68">
-        <v>2.060092180603355</v>
+        <v>2.122519216379215</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02200451553491454</v>
+        <v>0.02167608992991582</v>
       </c>
       <c r="W68">
-        <v>0.2306113352368672</v>
+        <v>0.2306887779945259</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2200451553491454</v>
+        <v>0.2167608992991581</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.214953163314095</v>
+        <v>0.216853163314095</v>
       </c>
       <c r="C69">
-        <v>-50.35550546269108</v>
+        <v>-52.64940921559668</v>
       </c>
       <c r="D69">
-        <v>58.41949453730893</v>
+        <v>57.77059078440333</v>
       </c>
       <c r="E69">
-        <v>-41.685</v>
+        <v>-40.03999999999999</v>
       </c>
       <c r="F69">
-        <v>110.215</v>
+        <v>111.86</v>
       </c>
       <c r="G69">
         <v>1.44</v>
@@ -6939,37 +6939,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M69">
-        <v>25.988697</v>
+        <v>26.37658800000001</v>
       </c>
       <c r="N69">
-        <v>-20.35536366666667</v>
+        <v>-20.74325466666667</v>
       </c>
       <c r="O69">
-        <v>-2.035536366666667</v>
+        <v>-2.074325466666668</v>
       </c>
       <c r="P69">
-        <v>-18.3198273</v>
+        <v>-18.6689292</v>
       </c>
       <c r="Q69">
-        <v>-14.8698273</v>
+        <v>-15.21892920000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1830050971447354</v>
+        <v>0.1872927564305084</v>
       </c>
       <c r="T69">
-        <v>2.122519216379215</v>
+        <v>2.188847941891065</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02167608992991582</v>
+        <v>0.0213573239015347</v>
       </c>
       <c r="W69">
-        <v>0.2306887779945259</v>
+        <v>0.2307639430240181</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2167608992991581</v>
+        <v>0.213573239015347</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.216853163314095</v>
+        <v>0.218753163314095</v>
       </c>
       <c r="C70">
-        <v>-52.64940921559668</v>
+        <v>-54.92905573137635</v>
       </c>
       <c r="D70">
-        <v>57.77059078440333</v>
+        <v>57.13594426862366</v>
       </c>
       <c r="E70">
-        <v>-40.03999999999999</v>
+        <v>-38.395</v>
       </c>
       <c r="F70">
-        <v>111.86</v>
+        <v>113.505</v>
       </c>
       <c r="G70">
         <v>1.44</v>
@@ -7021,37 +7021,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M70">
-        <v>26.37658800000001</v>
+        <v>26.76447900000001</v>
       </c>
       <c r="N70">
-        <v>-20.74325466666667</v>
+        <v>-21.13114566666667</v>
       </c>
       <c r="O70">
-        <v>-2.074325466666668</v>
+        <v>-2.113114566666667</v>
       </c>
       <c r="P70">
-        <v>-18.6689292</v>
+        <v>-19.01803110000001</v>
       </c>
       <c r="Q70">
-        <v>-15.21892920000001</v>
+        <v>-15.56803110000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1872927564305084</v>
+        <v>0.1918570388960087</v>
       </c>
       <c r="T70">
-        <v>2.188847941891065</v>
+        <v>2.259455940016583</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0213573239015347</v>
+        <v>0.02104779746817912</v>
       </c>
       <c r="W70">
-        <v>0.2307639430240181</v>
+        <v>0.2308369293570034</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.213573239015347</v>
+        <v>0.2104779746817912</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.218753163314095</v>
+        <v>0.220653163314095</v>
       </c>
       <c r="C71">
-        <v>-54.92905573137635</v>
+        <v>-57.19490977858267</v>
       </c>
       <c r="D71">
-        <v>57.13594426862366</v>
+        <v>56.51509022141734</v>
       </c>
       <c r="E71">
-        <v>-38.395</v>
+        <v>-36.75</v>
       </c>
       <c r="F71">
-        <v>113.505</v>
+        <v>115.15</v>
       </c>
       <c r="G71">
         <v>1.44</v>
@@ -7103,37 +7103,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M71">
-        <v>26.76447900000001</v>
+        <v>27.15237</v>
       </c>
       <c r="N71">
-        <v>-21.13114566666667</v>
+        <v>-21.51903666666667</v>
       </c>
       <c r="O71">
-        <v>-2.113114566666667</v>
+        <v>-2.151903666666667</v>
       </c>
       <c r="P71">
-        <v>-19.01803110000001</v>
+        <v>-19.367133</v>
       </c>
       <c r="Q71">
-        <v>-15.56803110000001</v>
+        <v>-15.917133</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1918570388960087</v>
+        <v>0.196725606859209</v>
       </c>
       <c r="T71">
-        <v>2.259455940016583</v>
+        <v>2.334771138017136</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02104779746817912</v>
+        <v>0.02074711464720514</v>
       </c>
       <c r="W71">
-        <v>0.2308369293570034</v>
+        <v>0.230907830366189</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2104779746817912</v>
+        <v>0.2074711464720513</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.220653163314095</v>
+        <v>0.2225531633140951</v>
       </c>
       <c r="C72">
-        <v>-57.19490977858267</v>
+        <v>-59.44741614173547</v>
       </c>
       <c r="D72">
-        <v>56.51509022141734</v>
+        <v>55.90758385826455</v>
       </c>
       <c r="E72">
-        <v>-36.75</v>
+        <v>-35.10499999999999</v>
       </c>
       <c r="F72">
-        <v>115.15</v>
+        <v>116.795</v>
       </c>
       <c r="G72">
         <v>1.44</v>
@@ -7185,37 +7185,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M72">
-        <v>27.15237</v>
+        <v>27.540261</v>
       </c>
       <c r="N72">
-        <v>-21.51903666666667</v>
+        <v>-21.90692766666667</v>
       </c>
       <c r="O72">
-        <v>-2.151903666666667</v>
+        <v>-2.190692766666667</v>
       </c>
       <c r="P72">
-        <v>-19.367133</v>
+        <v>-19.7162349</v>
       </c>
       <c r="Q72">
-        <v>-15.917133</v>
+        <v>-16.2662349</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.196725606859209</v>
+        <v>0.2019299381302162</v>
       </c>
       <c r="T72">
-        <v>2.334771138017136</v>
+        <v>2.415280487603934</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02074711464720514</v>
+        <v>0.02045490176485014</v>
       </c>
       <c r="W72">
-        <v>0.230907830366189</v>
+        <v>0.2309767341638484</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2074711464720513</v>
+        <v>0.2045490176485013</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.222553163314095</v>
+        <v>0.224453163314095</v>
       </c>
       <c r="C73">
-        <v>-59.44741614173544</v>
+        <v>-61.68700068398586</v>
       </c>
       <c r="D73">
-        <v>55.90758385826455</v>
+        <v>55.31299931601414</v>
       </c>
       <c r="E73">
-        <v>-35.10500000000002</v>
+        <v>-33.46000000000001</v>
       </c>
       <c r="F73">
-        <v>116.795</v>
+        <v>118.44</v>
       </c>
       <c r="G73">
         <v>1.44</v>
@@ -7267,37 +7267,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M73">
-        <v>27.540261</v>
+        <v>27.928152</v>
       </c>
       <c r="N73">
-        <v>-21.90692766666666</v>
+        <v>-22.29481866666667</v>
       </c>
       <c r="O73">
-        <v>-2.190692766666666</v>
+        <v>-2.229481866666667</v>
       </c>
       <c r="P73">
-        <v>-19.7162349</v>
+        <v>-20.0653368</v>
       </c>
       <c r="Q73">
-        <v>-16.2662349</v>
+        <v>-16.6153368</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2019299381302161</v>
+        <v>0.2075060073491524</v>
       </c>
       <c r="T73">
-        <v>2.415280487603933</v>
+        <v>2.501540505018359</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02045490176485014</v>
+        <v>0.020170805907005</v>
       </c>
       <c r="W73">
-        <v>0.2309767341638484</v>
+        <v>0.2310437239671282</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2045490176485013</v>
+        <v>0.20170805907005</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.224453163314095</v>
+        <v>0.226353163314095</v>
       </c>
       <c r="C74">
-        <v>-61.68700068398586</v>
+        <v>-63.91407134268489</v>
       </c>
       <c r="D74">
-        <v>55.31299931601414</v>
+        <v>54.7309286573151</v>
       </c>
       <c r="E74">
-        <v>-33.46000000000001</v>
+        <v>-31.81500000000001</v>
       </c>
       <c r="F74">
-        <v>118.44</v>
+        <v>120.085</v>
       </c>
       <c r="G74">
         <v>1.44</v>
@@ -7349,37 +7349,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M74">
-        <v>27.928152</v>
+        <v>28.316043</v>
       </c>
       <c r="N74">
-        <v>-22.29481866666667</v>
+        <v>-22.68270966666667</v>
       </c>
       <c r="O74">
-        <v>-2.229481866666667</v>
+        <v>-2.268270966666667</v>
       </c>
       <c r="P74">
-        <v>-20.0653368</v>
+        <v>-20.4144387</v>
       </c>
       <c r="Q74">
-        <v>-16.6153368</v>
+        <v>-16.9644387</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2075060073491524</v>
+        <v>0.2134951187324544</v>
       </c>
       <c r="T74">
-        <v>2.501540505018359</v>
+        <v>2.594190153352373</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.020170805907005</v>
+        <v>0.01989449349732</v>
       </c>
       <c r="W74">
-        <v>0.2310437239671282</v>
+        <v>0.231108878433332</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.20170805907005</v>
+        <v>0.1989449349731999</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.226353163314095</v>
+        <v>0.228253163314095</v>
       </c>
       <c r="C75">
-        <v>-63.91407134268489</v>
+        <v>-66.12901906274651</v>
       </c>
       <c r="D75">
-        <v>54.7309286573151</v>
+        <v>54.1609809372535</v>
       </c>
       <c r="E75">
-        <v>-31.81500000000001</v>
+        <v>-30.17</v>
       </c>
       <c r="F75">
-        <v>120.085</v>
+        <v>121.73</v>
       </c>
       <c r="G75">
         <v>1.44</v>
@@ -7431,37 +7431,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M75">
-        <v>28.316043</v>
+        <v>28.703934</v>
       </c>
       <c r="N75">
-        <v>-22.68270966666667</v>
+        <v>-23.07060066666667</v>
       </c>
       <c r="O75">
-        <v>-2.268270966666667</v>
+        <v>-2.307060066666667</v>
       </c>
       <c r="P75">
-        <v>-20.4144387</v>
+        <v>-20.7635406</v>
       </c>
       <c r="Q75">
-        <v>-16.9644387</v>
+        <v>-17.3135406</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2134951187324544</v>
+        <v>0.2199449309913949</v>
       </c>
       <c r="T75">
-        <v>2.594190153352373</v>
+        <v>2.693966697712079</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01989449349732</v>
+        <v>0.01962564899059946</v>
       </c>
       <c r="W75">
-        <v>0.231108878433332</v>
+        <v>0.2311722719680167</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1989449349731999</v>
+        <v>0.1962564899059945</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.228253163314095</v>
+        <v>0.230153163314095</v>
       </c>
       <c r="C76">
-        <v>-66.12901906274651</v>
+        <v>-68.33221867229405</v>
       </c>
       <c r="D76">
-        <v>54.1609809372535</v>
+        <v>53.60278132770596</v>
       </c>
       <c r="E76">
-        <v>-30.17</v>
+        <v>-28.52500000000001</v>
       </c>
       <c r="F76">
-        <v>121.73</v>
+        <v>123.375</v>
       </c>
       <c r="G76">
         <v>1.44</v>
@@ -7513,37 +7513,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M76">
-        <v>28.703934</v>
+        <v>29.091825</v>
       </c>
       <c r="N76">
-        <v>-23.07060066666667</v>
+        <v>-23.45849166666667</v>
       </c>
       <c r="O76">
-        <v>-2.307060066666667</v>
+        <v>-2.345849166666667</v>
       </c>
       <c r="P76">
-        <v>-20.7635406</v>
+        <v>-21.1126425</v>
       </c>
       <c r="Q76">
-        <v>-17.3135406</v>
+        <v>-17.6626425</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2199449309913949</v>
+        <v>0.2269107282310507</v>
       </c>
       <c r="T76">
-        <v>2.693966697712079</v>
+        <v>2.801725365620563</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01962564899059946</v>
+        <v>0.0193639736707248</v>
       </c>
       <c r="W76">
-        <v>0.2311722719680167</v>
+        <v>0.2312339750084431</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1962564899059945</v>
+        <v>0.1936397367072479</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.230153163314095</v>
+        <v>0.232053163314095</v>
       </c>
       <c r="C77">
-        <v>-68.33221867229405</v>
+        <v>-70.52402970471067</v>
       </c>
       <c r="D77">
-        <v>53.60278132770596</v>
+        <v>53.05597029528933</v>
       </c>
       <c r="E77">
-        <v>-28.52500000000001</v>
+        <v>-26.88000000000001</v>
       </c>
       <c r="F77">
-        <v>123.375</v>
+        <v>125.02</v>
       </c>
       <c r="G77">
         <v>1.44</v>
@@ -7595,37 +7595,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M77">
-        <v>29.091825</v>
+        <v>29.479716</v>
       </c>
       <c r="N77">
-        <v>-23.45849166666667</v>
+        <v>-23.84638266666667</v>
       </c>
       <c r="O77">
-        <v>-2.345849166666667</v>
+        <v>-2.384638266666667</v>
       </c>
       <c r="P77">
-        <v>-21.1126425</v>
+        <v>-21.4617444</v>
       </c>
       <c r="Q77">
-        <v>-17.6626425</v>
+        <v>-18.0117444</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2269107282310507</v>
+        <v>0.2344570085740112</v>
       </c>
       <c r="T77">
-        <v>2.801725365620563</v>
+        <v>2.91846392252142</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0193639736707248</v>
+        <v>0.01910918454347842</v>
       </c>
       <c r="W77">
-        <v>0.2312339750084431</v>
+        <v>0.2312940542846478</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1936397367072479</v>
+        <v>0.1910918454347842</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.232053163314095</v>
+        <v>0.233953163314095</v>
       </c>
       <c r="C78">
-        <v>-70.52402970471067</v>
+        <v>-72.70479717088273</v>
       </c>
       <c r="D78">
-        <v>53.05597029528933</v>
+        <v>52.52020282911729</v>
       </c>
       <c r="E78">
-        <v>-26.88000000000001</v>
+        <v>-25.235</v>
       </c>
       <c r="F78">
-        <v>125.02</v>
+        <v>126.665</v>
       </c>
       <c r="G78">
         <v>1.44</v>
@@ -7677,37 +7677,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M78">
-        <v>29.479716</v>
+        <v>29.867607</v>
       </c>
       <c r="N78">
-        <v>-23.84638266666667</v>
+        <v>-24.23427366666667</v>
       </c>
       <c r="O78">
-        <v>-2.384638266666667</v>
+        <v>-2.423427366666667</v>
       </c>
       <c r="P78">
-        <v>-21.4617444</v>
+        <v>-21.8108463</v>
       </c>
       <c r="Q78">
-        <v>-18.0117444</v>
+        <v>-18.3608463</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2344570085740112</v>
+        <v>0.2426594872076638</v>
       </c>
       <c r="T78">
-        <v>2.91846392252142</v>
+        <v>3.04535365828322</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01910918454347842</v>
+        <v>0.01886101331564103</v>
       </c>
       <c r="W78">
-        <v>0.2312940542846478</v>
+        <v>0.2313525730601718</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1910918454347842</v>
+        <v>0.1886101331564103</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.233953163314095</v>
+        <v>0.235853163314095</v>
       </c>
       <c r="C79">
-        <v>-72.70479717088273</v>
+        <v>-74.87485228512151</v>
       </c>
       <c r="D79">
-        <v>52.52020282911729</v>
+        <v>51.9951477148785</v>
       </c>
       <c r="E79">
-        <v>-25.235</v>
+        <v>-23.59</v>
       </c>
       <c r="F79">
-        <v>126.665</v>
+        <v>128.31</v>
       </c>
       <c r="G79">
         <v>1.44</v>
@@ -7759,37 +7759,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M79">
-        <v>29.867607</v>
+        <v>30.255498</v>
       </c>
       <c r="N79">
-        <v>-24.23427366666667</v>
+        <v>-24.62216466666667</v>
       </c>
       <c r="O79">
-        <v>-2.423427366666667</v>
+        <v>-2.462216466666667</v>
       </c>
       <c r="P79">
-        <v>-21.8108463</v>
+        <v>-22.1599482</v>
       </c>
       <c r="Q79">
-        <v>-18.3608463</v>
+        <v>-18.7099482</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2426594872076638</v>
+        <v>0.2516076457171031</v>
       </c>
       <c r="T79">
-        <v>3.04535365828322</v>
+        <v>3.183778824568822</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01886101331564103</v>
+        <v>0.01861920545261999</v>
       </c>
       <c r="W79">
-        <v>0.2313525730601718</v>
+        <v>0.2314095913542722</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1886101331564103</v>
+        <v>0.1861920545261999</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.235853163314095</v>
+        <v>0.237753163314095</v>
       </c>
       <c r="C80">
-        <v>-74.87485228512151</v>
+        <v>-77.03451314797282</v>
       </c>
       <c r="D80">
-        <v>51.9951477148785</v>
+        <v>51.4804868520272</v>
       </c>
       <c r="E80">
-        <v>-23.59</v>
+        <v>-21.94499999999999</v>
       </c>
       <c r="F80">
-        <v>128.31</v>
+        <v>129.955</v>
       </c>
       <c r="G80">
         <v>1.44</v>
@@ -7841,37 +7841,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M80">
-        <v>30.255498</v>
+        <v>30.643389</v>
       </c>
       <c r="N80">
-        <v>-24.62216466666667</v>
+        <v>-25.01005566666667</v>
       </c>
       <c r="O80">
-        <v>-2.462216466666667</v>
+        <v>-2.501005566666667</v>
       </c>
       <c r="P80">
-        <v>-22.1599482</v>
+        <v>-22.5090501</v>
       </c>
       <c r="Q80">
-        <v>-18.7099482</v>
+        <v>-19.0590501</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2516076457171031</v>
+        <v>0.2614080097988699</v>
       </c>
       <c r="T80">
-        <v>3.183778824568822</v>
+        <v>3.33538734002448</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01861920545261999</v>
+        <v>0.01838351930765012</v>
       </c>
       <c r="W80">
-        <v>0.2314095913542722</v>
+        <v>0.2314651661472561</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1861920545261999</v>
+        <v>0.1838351930765012</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.237753163314095</v>
+        <v>0.239653163314095</v>
       </c>
       <c r="C81">
-        <v>-77.03451314797282</v>
+        <v>-79.1840853888723</v>
       </c>
       <c r="D81">
-        <v>51.4804868520272</v>
+        <v>50.97591461112769</v>
       </c>
       <c r="E81">
-        <v>-21.94499999999999</v>
+        <v>-20.30000000000001</v>
       </c>
       <c r="F81">
-        <v>129.955</v>
+        <v>131.6</v>
       </c>
       <c r="G81">
         <v>1.44</v>
@@ -7923,37 +7923,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M81">
-        <v>30.643389</v>
+        <v>31.03128</v>
       </c>
       <c r="N81">
-        <v>-25.01005566666667</v>
+        <v>-25.39794666666667</v>
       </c>
       <c r="O81">
-        <v>-2.501005566666667</v>
+        <v>-2.539794666666667</v>
       </c>
       <c r="P81">
-        <v>-22.5090501</v>
+        <v>-22.858152</v>
       </c>
       <c r="Q81">
-        <v>-19.0590501</v>
+        <v>-19.408152</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2614080097988699</v>
+        <v>0.2721884102888135</v>
       </c>
       <c r="T81">
-        <v>3.33538734002448</v>
+        <v>3.502156707025704</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01838351930765012</v>
+        <v>0.0181537253163045</v>
       </c>
       <c r="W81">
-        <v>0.2314651661472561</v>
+        <v>0.2315193515704154</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1838351930765012</v>
+        <v>0.1815372531630449</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.239653163314095</v>
+        <v>0.241553163314095</v>
       </c>
       <c r="C82">
-        <v>-79.1840853888723</v>
+        <v>-81.32386277137488</v>
       </c>
       <c r="D82">
-        <v>50.97591461112769</v>
+        <v>50.48113722862514</v>
       </c>
       <c r="E82">
-        <v>-20.30000000000001</v>
+        <v>-18.655</v>
       </c>
       <c r="F82">
-        <v>131.6</v>
+        <v>133.245</v>
       </c>
       <c r="G82">
         <v>1.44</v>
@@ -8005,37 +8005,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M82">
-        <v>31.03128</v>
+        <v>31.419171</v>
       </c>
       <c r="N82">
-        <v>-25.39794666666667</v>
+        <v>-25.78583766666667</v>
       </c>
       <c r="O82">
-        <v>-2.539794666666667</v>
+        <v>-2.578583766666667</v>
       </c>
       <c r="P82">
-        <v>-22.858152</v>
+        <v>-23.2072539</v>
       </c>
       <c r="Q82">
-        <v>-19.408152</v>
+        <v>-19.7572539</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2721884102888135</v>
+        <v>0.2841035897776984</v>
       </c>
       <c r="T82">
-        <v>3.502156707025704</v>
+        <v>3.686480744237584</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0181537253163045</v>
+        <v>0.01792960525067111</v>
       </c>
       <c r="W82">
-        <v>0.2315193515704154</v>
+        <v>0.2315721990818917</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1815372531630449</v>
+        <v>0.179296052506711</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.241553163314095</v>
+        <v>0.243453163314095</v>
       </c>
       <c r="C83">
-        <v>-81.32386277137488</v>
+        <v>-83.45412776347605</v>
       </c>
       <c r="D83">
-        <v>50.48113722862514</v>
+        <v>49.99587223652397</v>
       </c>
       <c r="E83">
-        <v>-18.655</v>
+        <v>-17.00999999999999</v>
       </c>
       <c r="F83">
-        <v>133.245</v>
+        <v>134.89</v>
       </c>
       <c r="G83">
         <v>1.44</v>
@@ -8087,37 +8087,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M83">
-        <v>31.419171</v>
+        <v>31.80706200000001</v>
       </c>
       <c r="N83">
-        <v>-25.78583766666667</v>
+        <v>-26.17372866666667</v>
       </c>
       <c r="O83">
-        <v>-2.578583766666667</v>
+        <v>-2.617372866666667</v>
       </c>
       <c r="P83">
-        <v>-23.2072539</v>
+        <v>-23.55635580000001</v>
       </c>
       <c r="Q83">
-        <v>-19.7572539</v>
+        <v>-20.10635580000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2841035897776984</v>
+        <v>0.2973426780986816</v>
       </c>
       <c r="T83">
-        <v>3.686480744237584</v>
+        <v>3.89128523002856</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01792960525067111</v>
+        <v>0.01771095152810195</v>
       </c>
       <c r="W83">
-        <v>0.2315721990818917</v>
+        <v>0.2316237576296735</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.179296052506711</v>
+        <v>0.1771095152810194</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.243453163314095</v>
+        <v>0.245353163314095</v>
       </c>
       <c r="C84">
-        <v>-83.45412776347605</v>
+        <v>-85.57515207535269</v>
       </c>
       <c r="D84">
-        <v>49.99587223652397</v>
+        <v>49.51984792464734</v>
       </c>
       <c r="E84">
-        <v>-17.00999999999999</v>
+        <v>-15.36499999999998</v>
       </c>
       <c r="F84">
-        <v>134.89</v>
+        <v>136.535</v>
       </c>
       <c r="G84">
         <v>1.44</v>
@@ -8169,37 +8169,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M84">
-        <v>31.80706200000001</v>
+        <v>32.19495300000001</v>
       </c>
       <c r="N84">
-        <v>-26.17372866666667</v>
+        <v>-26.56161966666667</v>
       </c>
       <c r="O84">
-        <v>-2.617372866666667</v>
+        <v>-2.656161966666668</v>
       </c>
       <c r="P84">
-        <v>-23.55635580000001</v>
+        <v>-23.90545770000001</v>
       </c>
       <c r="Q84">
-        <v>-20.10635580000001</v>
+        <v>-20.45545770000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2973426780986816</v>
+        <v>0.3121393062221335</v>
       </c>
       <c r="T84">
-        <v>3.89128523002856</v>
+        <v>4.120184361206712</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01771095152810195</v>
+        <v>0.01749756656993204</v>
       </c>
       <c r="W84">
-        <v>0.2316237576296735</v>
+        <v>0.23167407380281</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1771095152810194</v>
+        <v>0.1749756656993204</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.245353163314095</v>
+        <v>0.247253163314095</v>
       </c>
       <c r="C85">
-        <v>-85.57515207535269</v>
+        <v>-87.68719716667314</v>
       </c>
       <c r="D85">
-        <v>49.51984792464734</v>
+        <v>49.05280283332686</v>
       </c>
       <c r="E85">
-        <v>-15.36499999999998</v>
+        <v>-13.72</v>
       </c>
       <c r="F85">
-        <v>136.535</v>
+        <v>138.18</v>
       </c>
       <c r="G85">
         <v>1.44</v>
@@ -8251,37 +8251,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M85">
-        <v>32.19495300000001</v>
+        <v>32.582844</v>
       </c>
       <c r="N85">
-        <v>-26.56161966666667</v>
+        <v>-26.94951066666667</v>
       </c>
       <c r="O85">
-        <v>-2.656161966666668</v>
+        <v>-2.694951066666667</v>
       </c>
       <c r="P85">
-        <v>-23.90545770000001</v>
+        <v>-24.2545596</v>
       </c>
       <c r="Q85">
-        <v>-20.45545770000001</v>
+        <v>-20.8045596</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3121393062221335</v>
+        <v>0.3287855128610169</v>
       </c>
       <c r="T85">
-        <v>4.120184361206712</v>
+        <v>4.377695883782132</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01749756656993204</v>
+        <v>0.01728926220600428</v>
       </c>
       <c r="W85">
-        <v>0.23167407380281</v>
+        <v>0.2317231919718242</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1749756656993204</v>
+        <v>0.1728926220600427</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.247253163314095</v>
+        <v>0.249153163314095</v>
       </c>
       <c r="C86">
-        <v>-87.68719716667314</v>
+        <v>-89.79051472546794</v>
       </c>
       <c r="D86">
-        <v>49.05280283332686</v>
+        <v>48.59448527453204</v>
       </c>
       <c r="E86">
-        <v>-13.72</v>
+        <v>-12.07500000000002</v>
       </c>
       <c r="F86">
-        <v>138.18</v>
+        <v>139.825</v>
       </c>
       <c r="G86">
         <v>1.44</v>
@@ -8333,37 +8333,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M86">
-        <v>32.582844</v>
+        <v>32.970735</v>
       </c>
       <c r="N86">
-        <v>-26.94951066666667</v>
+        <v>-27.33740166666666</v>
       </c>
       <c r="O86">
-        <v>-2.694951066666667</v>
+        <v>-2.733740166666667</v>
       </c>
       <c r="P86">
-        <v>-24.2545596</v>
+        <v>-24.6036615</v>
       </c>
       <c r="Q86">
-        <v>-20.8045596</v>
+        <v>-21.1536615</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3287855128610167</v>
+        <v>0.3476512137184178</v>
       </c>
       <c r="T86">
-        <v>4.377695883782128</v>
+        <v>4.669542276034271</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01728926220600428</v>
+        <v>0.01708585912122776</v>
       </c>
       <c r="W86">
-        <v>0.2317231919718242</v>
+        <v>0.2317711544192145</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1728926220600427</v>
+        <v>0.1708585912122776</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.249153163314095</v>
+        <v>0.251053163314095</v>
       </c>
       <c r="C87">
-        <v>-89.79051472546794</v>
+        <v>-91.88534712040318</v>
       </c>
       <c r="D87">
-        <v>48.59448527453204</v>
+        <v>48.14465287959682</v>
       </c>
       <c r="E87">
-        <v>-12.07500000000002</v>
+        <v>-10.43000000000001</v>
       </c>
       <c r="F87">
-        <v>139.825</v>
+        <v>141.47</v>
       </c>
       <c r="G87">
         <v>1.44</v>
@@ -8415,37 +8415,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M87">
-        <v>32.970735</v>
+        <v>33.358626</v>
       </c>
       <c r="N87">
-        <v>-27.33740166666666</v>
+        <v>-27.72529266666667</v>
       </c>
       <c r="O87">
-        <v>-2.733740166666667</v>
+        <v>-2.772529266666667</v>
       </c>
       <c r="P87">
-        <v>-24.6036615</v>
+        <v>-24.9527634</v>
       </c>
       <c r="Q87">
-        <v>-21.1536615</v>
+        <v>-21.5027634</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3476512137184178</v>
+        <v>0.3692120146983048</v>
       </c>
       <c r="T87">
-        <v>4.669542276034271</v>
+        <v>5.003081010036719</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01708585912122776</v>
+        <v>0.01688718634074837</v>
       </c>
       <c r="W87">
-        <v>0.2317711544192145</v>
+        <v>0.2318180014608515</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1708585912122776</v>
+        <v>0.1688718634074836</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.251053163314095</v>
+        <v>0.252953163314095</v>
       </c>
       <c r="C88">
-        <v>-91.88534712040318</v>
+        <v>-93.97192782816452</v>
       </c>
       <c r="D88">
-        <v>48.14465287959682</v>
+        <v>47.70307217183549</v>
       </c>
       <c r="E88">
-        <v>-10.43000000000001</v>
+        <v>-8.784999999999997</v>
       </c>
       <c r="F88">
-        <v>141.47</v>
+        <v>143.115</v>
       </c>
       <c r="G88">
         <v>1.44</v>
@@ -8497,37 +8497,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M88">
-        <v>33.358626</v>
+        <v>33.746517</v>
       </c>
       <c r="N88">
-        <v>-27.72529266666667</v>
+        <v>-28.11318366666667</v>
       </c>
       <c r="O88">
-        <v>-2.772529266666667</v>
+        <v>-2.811318366666667</v>
       </c>
       <c r="P88">
-        <v>-24.9527634</v>
+        <v>-25.3018653</v>
       </c>
       <c r="Q88">
-        <v>-21.5027634</v>
+        <v>-21.8518653</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3692120146983048</v>
+        <v>0.3940898619827898</v>
       </c>
       <c r="T88">
-        <v>5.003081010036719</v>
+        <v>5.387933395424159</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01688718634074837</v>
+        <v>0.01669308075062482</v>
       </c>
       <c r="W88">
-        <v>0.2318180014608515</v>
+        <v>0.2318637715590027</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1688718634074836</v>
+        <v>0.1669308075062482</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.252953163314095</v>
+        <v>0.254853163314095</v>
       </c>
       <c r="C89">
-        <v>-93.97192782816452</v>
+        <v>-96.05048183753537</v>
       </c>
       <c r="D89">
-        <v>47.70307217183549</v>
+        <v>47.26951816246462</v>
       </c>
       <c r="E89">
-        <v>-8.784999999999997</v>
+        <v>-7.140000000000015</v>
       </c>
       <c r="F89">
-        <v>143.115</v>
+        <v>144.76</v>
       </c>
       <c r="G89">
         <v>1.44</v>
@@ -8579,37 +8579,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M89">
-        <v>33.746517</v>
+        <v>34.134408</v>
       </c>
       <c r="N89">
-        <v>-28.11318366666667</v>
+        <v>-28.50107466666667</v>
       </c>
       <c r="O89">
-        <v>-2.811318366666667</v>
+        <v>-2.850107466666667</v>
       </c>
       <c r="P89">
-        <v>-25.3018653</v>
+        <v>-25.6509672</v>
       </c>
       <c r="Q89">
-        <v>-21.8518653</v>
+        <v>-22.2009672</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3940898619827898</v>
+        <v>0.4231140171480223</v>
       </c>
       <c r="T89">
-        <v>5.387933395424159</v>
+        <v>5.836927845042839</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01669308075062482</v>
+        <v>0.01650338665118591</v>
       </c>
       <c r="W89">
-        <v>0.2318637715590027</v>
+        <v>0.2319085014276504</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1669308075062482</v>
+        <v>0.165033866511859</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.254853163314095</v>
+        <v>0.256753163314095</v>
       </c>
       <c r="C90">
-        <v>-96.05048183753537</v>
+        <v>-98.12122603163859</v>
       </c>
       <c r="D90">
-        <v>47.26951816246462</v>
+        <v>46.84377396836142</v>
       </c>
       <c r="E90">
-        <v>-7.140000000000015</v>
+        <v>-5.495000000000005</v>
       </c>
       <c r="F90">
-        <v>144.76</v>
+        <v>146.405</v>
       </c>
       <c r="G90">
         <v>1.44</v>
@@ -8661,37 +8661,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M90">
-        <v>34.134408</v>
+        <v>34.522299</v>
       </c>
       <c r="N90">
-        <v>-28.50107466666667</v>
+        <v>-28.88896566666667</v>
       </c>
       <c r="O90">
-        <v>-2.850107466666667</v>
+        <v>-2.888896566666667</v>
       </c>
       <c r="P90">
-        <v>-25.6509672</v>
+        <v>-26.0000691</v>
       </c>
       <c r="Q90">
-        <v>-22.2009672</v>
+        <v>-22.55006910000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4231140171480223</v>
+        <v>0.4574152914342062</v>
       </c>
       <c r="T90">
-        <v>5.836927845042839</v>
+        <v>6.367557649137644</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01650338665118591</v>
+        <v>0.01631795534049842</v>
       </c>
       <c r="W90">
-        <v>0.2319085014276504</v>
+        <v>0.2319522261307105</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.165033866511859</v>
+        <v>0.1631795534049841</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.256753163314095</v>
+        <v>0.258653163314095</v>
       </c>
       <c r="C91">
-        <v>-98.12122603163859</v>
+        <v>-100.1843695497058</v>
       </c>
       <c r="D91">
-        <v>46.84377396836142</v>
+        <v>46.42563045029421</v>
       </c>
       <c r="E91">
-        <v>-5.495000000000005</v>
+        <v>-3.849999999999994</v>
       </c>
       <c r="F91">
-        <v>146.405</v>
+        <v>148.05</v>
       </c>
       <c r="G91">
         <v>1.44</v>
@@ -8743,37 +8743,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M91">
-        <v>34.522299</v>
+        <v>34.91019000000001</v>
       </c>
       <c r="N91">
-        <v>-28.88896566666667</v>
+        <v>-29.27685666666667</v>
       </c>
       <c r="O91">
-        <v>-2.888896566666667</v>
+        <v>-2.927685666666668</v>
       </c>
       <c r="P91">
-        <v>-26.0000691</v>
+        <v>-26.34917100000001</v>
       </c>
       <c r="Q91">
-        <v>-22.55006910000001</v>
+        <v>-22.89917100000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4574152914342062</v>
+        <v>0.4985768205776269</v>
       </c>
       <c r="T91">
-        <v>6.367557649137644</v>
+        <v>7.004313414051409</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01631795534049842</v>
+        <v>0.016136644725604</v>
       </c>
       <c r="W91">
-        <v>0.2319522261307105</v>
+        <v>0.2319949791737026</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1631795534049841</v>
+        <v>0.1613664472560399</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.258653163314095</v>
+        <v>0.260553163314095</v>
       </c>
       <c r="C92">
-        <v>-100.1843695497058</v>
+        <v>-102.2401141296426</v>
       </c>
       <c r="D92">
-        <v>46.42563045029421</v>
+        <v>46.01488587035736</v>
       </c>
       <c r="E92">
-        <v>-3.849999999999994</v>
+        <v>-2.205000000000013</v>
       </c>
       <c r="F92">
-        <v>148.05</v>
+        <v>149.695</v>
       </c>
       <c r="G92">
         <v>1.44</v>
@@ -8825,37 +8825,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M92">
-        <v>34.91019000000001</v>
+        <v>35.298081</v>
       </c>
       <c r="N92">
-        <v>-29.27685666666667</v>
+        <v>-29.66474766666667</v>
       </c>
       <c r="O92">
-        <v>-2.927685666666668</v>
+        <v>-2.966474766666667</v>
       </c>
       <c r="P92">
-        <v>-26.34917100000001</v>
+        <v>-26.6982729</v>
       </c>
       <c r="Q92">
-        <v>-22.89917100000001</v>
+        <v>-23.2482729</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4985768205776269</v>
+        <v>0.5488853561973632</v>
       </c>
       <c r="T92">
-        <v>7.004313414051409</v>
+        <v>7.782570460057122</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.016136644725604</v>
+        <v>0.01595931895938857</v>
       </c>
       <c r="W92">
-        <v>0.2319949791737026</v>
+        <v>0.2320367925893762</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1613664472560399</v>
+        <v>0.1595931895938857</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.260553163314095</v>
+        <v>0.262453163314095</v>
       </c>
       <c r="C93">
-        <v>-102.2401141296426</v>
+        <v>-104.2886544325688</v>
       </c>
       <c r="D93">
-        <v>46.01488587035736</v>
+        <v>45.61134556743121</v>
       </c>
       <c r="E93">
-        <v>-2.205000000000013</v>
+        <v>-0.5600000000000023</v>
       </c>
       <c r="F93">
-        <v>149.695</v>
+        <v>151.34</v>
       </c>
       <c r="G93">
         <v>1.44</v>
@@ -8907,37 +8907,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M93">
-        <v>35.298081</v>
+        <v>35.685972</v>
       </c>
       <c r="N93">
-        <v>-29.66474766666667</v>
+        <v>-30.05263866666667</v>
       </c>
       <c r="O93">
-        <v>-2.966474766666667</v>
+        <v>-3.005263866666667</v>
       </c>
       <c r="P93">
-        <v>-26.6982729</v>
+        <v>-27.0473748</v>
       </c>
       <c r="Q93">
-        <v>-23.2482729</v>
+        <v>-23.5973748</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5488853561973632</v>
+        <v>0.6117710257220338</v>
       </c>
       <c r="T93">
-        <v>7.782570460057122</v>
+        <v>8.755391767564264</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01595931895938857</v>
+        <v>0.01578584810113435</v>
       </c>
       <c r="W93">
-        <v>0.2320367925893762</v>
+        <v>0.2320776970177525</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1595931895938857</v>
+        <v>0.1578584810113434</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.262453163314095</v>
+        <v>0.264353163314095</v>
       </c>
       <c r="C94">
-        <v>-104.2886544325688</v>
+        <v>-106.3301783504293</v>
       </c>
       <c r="D94">
-        <v>45.61134556743121</v>
+        <v>45.21482164957067</v>
       </c>
       <c r="E94">
-        <v>-0.5600000000000023</v>
+        <v>1.085000000000008</v>
       </c>
       <c r="F94">
-        <v>151.34</v>
+        <v>152.985</v>
       </c>
       <c r="G94">
         <v>1.44</v>
@@ -8989,37 +8989,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M94">
-        <v>35.685972</v>
+        <v>36.073863</v>
       </c>
       <c r="N94">
-        <v>-30.05263866666667</v>
+        <v>-30.44052966666667</v>
       </c>
       <c r="O94">
-        <v>-3.005263866666667</v>
+        <v>-3.044052966666667</v>
       </c>
       <c r="P94">
-        <v>-27.0473748</v>
+        <v>-27.3964767</v>
       </c>
       <c r="Q94">
-        <v>-23.5973748</v>
+        <v>-23.9464767</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6117710257220338</v>
+        <v>0.6926240293966101</v>
       </c>
       <c r="T94">
-        <v>8.755391767564264</v>
+        <v>10.00616202007344</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01578584810113435</v>
+        <v>0.01561610779897161</v>
       </c>
       <c r="W94">
-        <v>0.2320776970177525</v>
+        <v>0.2321177217810025</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1578584810113434</v>
+        <v>0.156161077989716</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.264353163314095</v>
+        <v>0.266253163314095</v>
       </c>
       <c r="C95">
-        <v>-106.3301783504293</v>
+        <v>-108.3648672976992</v>
       </c>
       <c r="D95">
-        <v>45.21482164957067</v>
+        <v>44.82513270230078</v>
       </c>
       <c r="E95">
-        <v>1.085000000000008</v>
+        <v>2.72999999999999</v>
       </c>
       <c r="F95">
-        <v>152.985</v>
+        <v>154.63</v>
       </c>
       <c r="G95">
         <v>1.44</v>
@@ -9071,37 +9071,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M95">
-        <v>36.073863</v>
+        <v>36.461754</v>
       </c>
       <c r="N95">
-        <v>-30.44052966666667</v>
+        <v>-30.82842066666667</v>
       </c>
       <c r="O95">
-        <v>-3.044052966666667</v>
+        <v>-3.082842066666667</v>
       </c>
       <c r="P95">
-        <v>-27.3964767</v>
+        <v>-27.7455786</v>
       </c>
       <c r="Q95">
-        <v>-23.9464767</v>
+        <v>-24.2955786</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6926240293966101</v>
+        <v>0.8004280342960454</v>
       </c>
       <c r="T95">
-        <v>10.00616202007344</v>
+        <v>11.67385569008569</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01561610779897161</v>
+        <v>0.01544997899259957</v>
       </c>
       <c r="W95">
-        <v>0.2321177217810025</v>
+        <v>0.232156894953545</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.156161077989716</v>
+        <v>0.1544997899259957</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.266253163314095</v>
+        <v>0.268153163314095</v>
       </c>
       <c r="C96">
-        <v>-108.3648672976992</v>
+        <v>-110.392896488132</v>
       </c>
       <c r="D96">
-        <v>44.82513270230078</v>
+        <v>44.44210351186799</v>
       </c>
       <c r="E96">
-        <v>2.72999999999999</v>
+        <v>4.375</v>
       </c>
       <c r="F96">
-        <v>154.63</v>
+        <v>156.275</v>
       </c>
       <c r="G96">
         <v>1.44</v>
@@ -9153,37 +9153,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M96">
-        <v>36.461754</v>
+        <v>36.849645</v>
       </c>
       <c r="N96">
-        <v>-30.82842066666667</v>
+        <v>-31.21631166666667</v>
       </c>
       <c r="O96">
-        <v>-3.082842066666667</v>
+        <v>-3.121631166666667</v>
       </c>
       <c r="P96">
-        <v>-27.7455786</v>
+        <v>-28.0946805</v>
       </c>
       <c r="Q96">
-        <v>-24.2955786</v>
+        <v>-24.6446805</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8004280342960454</v>
+        <v>0.9513536411552547</v>
       </c>
       <c r="T96">
-        <v>11.67385569008569</v>
+        <v>14.00862682810283</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01544997899259957</v>
+        <v>0.01528734763478273</v>
       </c>
       <c r="W96">
-        <v>0.232156894953545</v>
+        <v>0.2321952434277182</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1544997899259957</v>
+        <v>0.1528734763478273</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.268153163314095</v>
+        <v>0.270053163314095</v>
       </c>
       <c r="C97">
-        <v>-110.392896488132</v>
+        <v>-112.4144351974401</v>
       </c>
       <c r="D97">
-        <v>44.44210351186799</v>
+        <v>44.06556480255988</v>
       </c>
       <c r="E97">
-        <v>4.375</v>
+        <v>6.02000000000001</v>
       </c>
       <c r="F97">
-        <v>156.275</v>
+        <v>157.92</v>
       </c>
       <c r="G97">
         <v>1.44</v>
@@ -9235,37 +9235,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M97">
-        <v>36.849645</v>
+        <v>37.23753600000001</v>
       </c>
       <c r="N97">
-        <v>-31.21631166666667</v>
+        <v>-31.60420266666667</v>
       </c>
       <c r="O97">
-        <v>-3.121631166666667</v>
+        <v>-3.160420266666668</v>
       </c>
       <c r="P97">
-        <v>-28.0946805</v>
+        <v>-28.4437824</v>
       </c>
       <c r="Q97">
-        <v>-24.6446805</v>
+        <v>-24.9937824</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9513536411552547</v>
+        <v>1.177742051444069</v>
       </c>
       <c r="T97">
-        <v>14.00862682810283</v>
+        <v>17.51078353512855</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01528734763478273</v>
+        <v>0.01512810443025375</v>
       </c>
       <c r="W97">
-        <v>0.2321952434277182</v>
+        <v>0.2322327929753462</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1528734763478273</v>
+        <v>0.1512810443025374</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.270053163314095</v>
+        <v>0.271953163314095</v>
       </c>
       <c r="C98">
-        <v>-112.4144351974401</v>
+        <v>-114.4296470127336</v>
       </c>
       <c r="D98">
-        <v>44.06556480255988</v>
+        <v>43.69535298726645</v>
       </c>
       <c r="E98">
-        <v>6.019999999999982</v>
+        <v>7.664999999999992</v>
       </c>
       <c r="F98">
-        <v>157.92</v>
+        <v>159.565</v>
       </c>
       <c r="G98">
         <v>1.44</v>
@@ -9317,37 +9317,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M98">
-        <v>37.237536</v>
+        <v>37.625427</v>
       </c>
       <c r="N98">
-        <v>-31.60420266666667</v>
+        <v>-31.99209366666667</v>
       </c>
       <c r="O98">
-        <v>-3.160420266666667</v>
+        <v>-3.199209366666667</v>
       </c>
       <c r="P98">
-        <v>-28.4437824</v>
+        <v>-28.7928843</v>
       </c>
       <c r="Q98">
-        <v>-24.9937824</v>
+        <v>-25.3428843</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.177742051444066</v>
+        <v>1.555056068592088</v>
       </c>
       <c r="T98">
-        <v>17.5107835351285</v>
+        <v>23.34771138017134</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01512810443025375</v>
+        <v>0.01497214459076659</v>
       </c>
       <c r="W98">
-        <v>0.2322327929753462</v>
+        <v>0.2322695683054972</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1512810443025374</v>
+        <v>0.1497214459076659</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.271953163314095</v>
+        <v>0.273853163314095</v>
       </c>
       <c r="C99">
-        <v>-114.4296470127336</v>
+        <v>-116.4386900694899</v>
       </c>
       <c r="D99">
-        <v>43.69535298726645</v>
+        <v>43.33130993051015</v>
       </c>
       <c r="E99">
-        <v>7.664999999999992</v>
+        <v>9.310000000000002</v>
       </c>
       <c r="F99">
-        <v>159.565</v>
+        <v>161.21</v>
       </c>
       <c r="G99">
         <v>1.44</v>
@@ -9399,37 +9399,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M99">
-        <v>37.625427</v>
+        <v>38.01331800000001</v>
       </c>
       <c r="N99">
-        <v>-31.99209366666667</v>
+        <v>-32.37998466666667</v>
       </c>
       <c r="O99">
-        <v>-3.199209366666667</v>
+        <v>-3.237998466666667</v>
       </c>
       <c r="P99">
-        <v>-28.7928843</v>
+        <v>-29.14198620000001</v>
       </c>
       <c r="Q99">
-        <v>-25.3428843</v>
+        <v>-25.69198620000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.555056068592088</v>
+        <v>2.309684102888132</v>
       </c>
       <c r="T99">
-        <v>23.34771138017134</v>
+        <v>35.02156707025701</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01497214459076659</v>
+        <v>0.01481936760514652</v>
       </c>
       <c r="W99">
-        <v>0.2322695683054972</v>
+        <v>0.2323055931187064</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1497214459076659</v>
+        <v>0.1481936760514653</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.273853163314095</v>
+        <v>0.275753163314095</v>
       </c>
       <c r="C100">
-        <v>-116.4386900694899</v>
+        <v>-118.441717276776</v>
       </c>
       <c r="D100">
-        <v>43.33130993051015</v>
+        <v>42.97328272322397</v>
       </c>
       <c r="E100">
-        <v>9.310000000000002</v>
+        <v>10.95499999999998</v>
       </c>
       <c r="F100">
-        <v>161.21</v>
+        <v>162.855</v>
       </c>
       <c r="G100">
         <v>1.44</v>
@@ -9481,37 +9481,37 @@
         <v>5.633333333333334</v>
       </c>
       <c r="M100">
-        <v>38.01331800000001</v>
+        <v>38.401209</v>
       </c>
       <c r="N100">
-        <v>-32.37998466666667</v>
+        <v>-32.76787566666667</v>
       </c>
       <c r="O100">
-        <v>-3.237998466666667</v>
+        <v>-3.276787566666667</v>
       </c>
       <c r="P100">
-        <v>-29.14198620000001</v>
+        <v>-29.4910881</v>
       </c>
       <c r="Q100">
-        <v>-25.69198620000001</v>
+        <v>-26.0410881</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.309684102888132</v>
+        <v>4.573568205776264</v>
       </c>
       <c r="T100">
-        <v>35.02156707025701</v>
+        <v>70.04313414051401</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01481936760514652</v>
+        <v>0.01466967702327636</v>
       </c>
       <c r="W100">
-        <v>0.2323055931187064</v>
+        <v>0.2323408901579114</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1481936760514653</v>
+        <v>0.1466967702327636</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.275753163314095</v>
-      </c>
-      <c r="C101">
-        <v>-118.441717276776</v>
-      </c>
-      <c r="D101">
-        <v>42.97328272322397</v>
-      </c>
-      <c r="E101">
-        <v>10.95499999999998</v>
-      </c>
-      <c r="F101">
-        <v>162.855</v>
-      </c>
-      <c r="G101">
-        <v>1.44</v>
-      </c>
-      <c r="H101">
-        <v>12.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.083333333333334</v>
-      </c>
-      <c r="K101">
-        <v>3.45</v>
-      </c>
-      <c r="L101">
-        <v>5.633333333333334</v>
-      </c>
-      <c r="M101">
-        <v>38.401209</v>
-      </c>
-      <c r="N101">
-        <v>-32.76787566666667</v>
-      </c>
-      <c r="O101">
-        <v>-3.276787566666667</v>
-      </c>
-      <c r="P101">
-        <v>-29.4910881</v>
-      </c>
-      <c r="Q101">
-        <v>-26.0410881</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.573568205776264</v>
-      </c>
-      <c r="T101">
-        <v>70.04313414051401</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01466967702327636</v>
-      </c>
-      <c r="W101">
-        <v>0.2323408901579114</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1466967702327636</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
